--- a/Reporte_gastos/gastos desde 2025-05.xlsx
+++ b/Reporte_gastos/gastos desde 2025-05.xlsx
@@ -5,7 +5,7 @@
   <workbookPr hidePivotFieldList="1" defaultThemeVersion="164011"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\maval\Documents\Vale laburo\Castelli\Reportes\Reporte_gastos\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\PC\Documents\Valeria\Reportes\Reporte_gastos\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -21,9 +21,9 @@
   </definedNames>
   <calcPr calcId="162913"/>
   <pivotCaches>
-    <pivotCache cacheId="130" r:id="rId4"/>
-    <pivotCache cacheId="131" r:id="rId5"/>
-    <pivotCache cacheId="132" r:id="rId6"/>
+    <pivotCache cacheId="1" r:id="rId4"/>
+    <pivotCache cacheId="2" r:id="rId5"/>
+    <pivotCache cacheId="15" r:id="rId6"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3593" uniqueCount="561">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3593" uniqueCount="562">
   <si>
     <t>ITEM</t>
   </si>
@@ -1718,6 +1718,9 @@
   <si>
     <t>857200 cámaras</t>
   </si>
+  <si>
+    <t>750000 habilitación</t>
+  </si>
 </sst>
 </file>
 
@@ -1797,6 +1800,7 @@
       <sz val="10"/>
       <color theme="1"/>
       <name val="Calibri"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -2036,7 +2040,109 @@
     <cellStyle name="Moneda" xfId="1" builtinId="4"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="21">
+  <dxfs count="39">
+    <dxf>
+      <numFmt numFmtId="34" formatCode="_-&quot;$&quot;\ * #,##0.00_-;\-&quot;$&quot;\ * #,##0.00_-;_-&quot;$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="169" formatCode="_-&quot;$&quot;\ * #,##0.0_-;\-&quot;$&quot;\ * #,##0.0_-;_-&quot;$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="_-&quot;$&quot;\ * #,##0_-;\-&quot;$&quot;\ * #,##0_-;_-&quot;$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="34" formatCode="_-&quot;$&quot;\ * #,##0.00_-;\-&quot;$&quot;\ * #,##0.00_-;_-&quot;$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="169" formatCode="_-&quot;$&quot;\ * #,##0.0_-;\-&quot;$&quot;\ * #,##0.0_-;_-&quot;$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="_-&quot;$&quot;\ * #,##0_-;\-&quot;$&quot;\ * #,##0_-;_-&quot;$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <fill>
         <patternFill patternType="solid">
@@ -2431,7 +2537,7 @@
 </file>
 
 <file path=xl/pivotCache/pivotCacheDefinition3.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1" refreshedBy="Valeria Levite" refreshedDate="46185.53381296296" createdVersion="6" refreshedVersion="6" minRefreshableVersion="3" recordCount="889">
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1" refreshedBy="PC" refreshedDate="46189.458143171294" createdVersion="6" refreshedVersion="6" minRefreshableVersion="3" recordCount="889">
   <cacheSource type="worksheet">
     <worksheetSource ref="A1:H890" sheet="tabla"/>
   </cacheSource>
@@ -26036,7 +26142,7 @@
     <x v="4"/>
     <s v=" EDESUR"/>
     <s v=" FA 0501-03686273"/>
-    <n v="46087"/>
+    <d v="2026-03-06T00:00:00"/>
     <n v="15687.93"/>
     <x v="10"/>
     <x v="1"/>
@@ -26046,7 +26152,7 @@
     <x v="4"/>
     <s v=" EDESUR"/>
     <s v=" FA 9904-02615399"/>
-    <n v="46088"/>
+    <d v="2026-03-07T00:00:00"/>
     <n v="550977.36"/>
     <x v="10"/>
     <x v="1"/>
@@ -26056,7 +26162,7 @@
     <x v="4"/>
     <s v=" EDESUR"/>
     <s v=" FA 0501-03684384"/>
-    <n v="46087"/>
+    <d v="2026-03-06T00:00:00"/>
     <n v="148645.44"/>
     <x v="10"/>
     <x v="1"/>
@@ -26066,7 +26172,7 @@
     <x v="7"/>
     <s v=" TELECOM ARGENTINA SOCIEDAD ANONIMA"/>
     <s v=" FA 4264-06383443"/>
-    <n v="46070"/>
+    <d v="2026-02-17T00:00:00"/>
     <n v="49311"/>
     <x v="10"/>
     <x v="1"/>
@@ -26076,7 +26182,7 @@
     <x v="4"/>
     <s v=" EDESUR"/>
     <s v=" FA 0501-03695956"/>
-    <n v="46091"/>
+    <d v="2026-03-10T00:00:00"/>
     <n v="54655.34"/>
     <x v="10"/>
     <x v="1"/>
@@ -26086,7 +26192,7 @@
     <x v="4"/>
     <s v=" EDESUR"/>
     <s v=" FA 0501-03695957"/>
-    <n v="46091"/>
+    <d v="2026-03-10T00:00:00"/>
     <n v="145915.48000000001"/>
     <x v="10"/>
     <x v="1"/>
@@ -26096,7 +26202,7 @@
     <x v="7"/>
     <s v=" TELECOM ARGENTINA SOCIEDAD ANONIMA"/>
     <s v=" FA 4264-06354441"/>
-    <n v="46070"/>
+    <d v="2026-02-17T00:00:00"/>
     <n v="121750"/>
     <x v="10"/>
     <x v="1"/>
@@ -26106,7 +26212,7 @@
     <x v="7"/>
     <s v=" TELECOM ARGENTINA SOCIEDAD ANONIMA"/>
     <s v=" FA 4264-06336829"/>
-    <n v="46070"/>
+    <d v="2026-02-17T00:00:00"/>
     <n v="84050"/>
     <x v="10"/>
     <x v="1"/>
@@ -26116,7 +26222,7 @@
     <x v="4"/>
     <s v=" EDESUR"/>
     <s v=" FA 0501-03686272"/>
-    <n v="46087"/>
+    <d v="2026-03-06T00:00:00"/>
     <n v="110526.91"/>
     <x v="10"/>
     <x v="1"/>
@@ -26126,7 +26232,7 @@
     <x v="7"/>
     <s v=" TELECOM ARGENTINA SOCIEDAD ANONIMA"/>
     <s v=" FA 4264-06399709"/>
-    <n v="46070"/>
+    <d v="2026-02-17T00:00:00"/>
     <n v="19401"/>
     <x v="10"/>
     <x v="1"/>
@@ -27177,7 +27283,7 @@
     <s v="SANES JUAN MANUEL"/>
     <s v="FC 00001-00000144"/>
     <d v="2026-04-27T00:00:00"/>
-    <n v="857200"/>
+    <m/>
     <x v="11"/>
     <x v="1"/>
   </r>
@@ -27237,7 +27343,7 @@
     <s v="REGA JOSE MARIA"/>
     <s v=" FC 00003-00000138"/>
     <d v="2026-04-21T00:00:00"/>
-    <n v="750000"/>
+    <m/>
     <x v="11"/>
     <x v="1"/>
   </r>
@@ -27757,7 +27863,7 @@
     <s v="LABORALPRE"/>
     <s v="FA 0003-00000588"/>
     <d v="2026-05-03T00:00:00"/>
-    <n v="61800"/>
+    <m/>
     <x v="2"/>
     <x v="1"/>
   </r>
@@ -28365,7 +28471,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="TablaDinámica3" cacheId="130" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="6" minRefreshableVersion="3" useAutoFormatting="1" rowGrandTotals="0" colGrandTotals="0" itemPrintTitles="1" createdVersion="6" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="TablaDinámica3" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="6" minRefreshableVersion="3" useAutoFormatting="1" rowGrandTotals="0" colGrandTotals="0" itemPrintTitles="1" createdVersion="6" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="A3:AP16" firstHeaderRow="1" firstDataRow="3" firstDataCol="1" rowPageCount="1" colPageCount="1"/>
   <pivotFields count="9">
     <pivotField axis="axisRow" showAll="0">
@@ -28650,7 +28756,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="TablaDinámica4" cacheId="132" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="6" minRefreshableVersion="3" useAutoFormatting="1" colGrandTotals="0" itemPrintTitles="1" createdVersion="6" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="TablaDinámica4" cacheId="15" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="6" minRefreshableVersion="3" useAutoFormatting="1" colGrandTotals="0" itemPrintTitles="1" createdVersion="6" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="A22:AZ35" firstHeaderRow="1" firstDataRow="3" firstDataCol="1" rowPageCount="1" colPageCount="1"/>
   <pivotFields count="9">
     <pivotField axis="axisRow" showAll="0">
@@ -28958,16 +29064,16 @@
     <dataField name="Suma de IMPORTE" fld="5" baseField="0" baseItem="0" numFmtId="164"/>
   </dataFields>
   <formats count="9">
-    <format dxfId="20">
+    <format dxfId="38">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
-    <format dxfId="19">
+    <format dxfId="37">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
-    <format dxfId="18">
+    <format dxfId="36">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
-    <format dxfId="17">
+    <format dxfId="35">
       <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
         <references count="3">
           <reference field="0" count="10">
@@ -28991,7 +29097,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="16">
+    <format dxfId="34">
       <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
         <references count="3">
           <reference field="0" count="1">
@@ -29006,7 +29112,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="15">
+    <format dxfId="33">
       <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
         <references count="3">
           <reference field="0" count="1">
@@ -29021,7 +29127,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="14">
+    <format dxfId="32">
       <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
         <references count="3">
           <reference field="0" count="1">
@@ -29036,7 +29142,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="13">
+    <format dxfId="31">
       <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
         <references count="3">
           <reference field="0" count="1">
@@ -29051,7 +29157,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="12">
+    <format dxfId="30">
       <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
         <references count="3">
           <reference field="0" count="1">
@@ -29077,7 +29183,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable3.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="TablaDinámica2" cacheId="131" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="6" minRefreshableVersion="3" useAutoFormatting="1" rowGrandTotals="0" colGrandTotals="0" itemPrintTitles="1" createdVersion="6" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="TablaDinámica2" cacheId="2" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="6" minRefreshableVersion="3" useAutoFormatting="1" rowGrandTotals="0" colGrandTotals="0" itemPrintTitles="1" createdVersion="6" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="A4:K16" firstHeaderRow="1" firstDataRow="3" firstDataCol="1" rowPageCount="2" colPageCount="1"/>
   <pivotFields count="9">
     <pivotField axis="axisRow" showAll="0" defaultSubtotal="0">
@@ -29249,16 +29355,16 @@
     <dataField name="Suma de IMPORTE" fld="5" baseField="0" baseItem="0" numFmtId="164"/>
   </dataFields>
   <formats count="12">
-    <format dxfId="11">
+    <format dxfId="29">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
-    <format dxfId="10">
+    <format dxfId="28">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
-    <format dxfId="9">
+    <format dxfId="27">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
-    <format dxfId="8">
+    <format dxfId="26">
       <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
         <references count="3">
           <reference field="0" count="1">
@@ -29273,7 +29379,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="7">
+    <format dxfId="25">
       <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
         <references count="3">
           <reference field="0" count="1">
@@ -29288,7 +29394,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="6">
+    <format dxfId="24">
       <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
         <references count="3">
           <reference field="0" count="1">
@@ -29303,7 +29409,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="5">
+    <format dxfId="23">
       <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
         <references count="3">
           <reference field="0" count="1">
@@ -29320,7 +29426,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="4">
+    <format dxfId="22">
       <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
         <references count="3">
           <reference field="0" count="1">
@@ -29335,7 +29441,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="3">
+    <format dxfId="21">
       <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
         <references count="3">
           <reference field="0" count="1">
@@ -29354,7 +29460,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="2">
+    <format dxfId="20">
       <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
         <references count="3">
           <reference field="0" count="4">
@@ -29372,7 +29478,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="1">
+    <format dxfId="19">
       <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
         <references count="3">
           <reference field="0" count="1">
@@ -29387,7 +29493,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="0">
+    <format dxfId="18">
       <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
         <references count="3">
           <reference field="0" count="1">
@@ -51452,16 +51558,16 @@
       <c r="E778" s="45">
         <v>46133</v>
       </c>
-      <c r="F778" s="62">
-        <v>750000</v>
-      </c>
+      <c r="F778" s="57"/>
       <c r="G778" s="63">
         <v>4</v>
       </c>
       <c r="H778" s="19">
         <v>2026</v>
       </c>
-      <c r="I778" s="62"/>
+      <c r="I778" s="62" t="s">
+        <v>561</v>
+      </c>
       <c r="J778" s="44"/>
       <c r="K778" s="44"/>
       <c r="L778" s="61"/>
@@ -51527,7 +51633,9 @@
       <c r="H780" s="19">
         <v>2026</v>
       </c>
-      <c r="I780" s="62"/>
+      <c r="I780" s="47" t="s">
+        <v>559</v>
+      </c>
       <c r="J780" s="44"/>
       <c r="K780" s="44"/>
       <c r="L780" s="61"/>
@@ -54437,9 +54545,6 @@
       <c r="H880" s="19">
         <v>2026</v>
       </c>
-      <c r="I880" s="2" t="s">
-        <v>557</v>
-      </c>
       <c r="J880" s="31"/>
       <c r="M880" s="31"/>
       <c r="O880" s="2"/>
@@ -54665,6 +54770,9 @@
       <c r="H888" s="19">
         <v>2026</v>
       </c>
+      <c r="I888" s="47" t="s">
+        <v>558</v>
+      </c>
       <c r="J888" s="31"/>
       <c r="M888" s="31"/>
       <c r="O888" s="2"/>
@@ -54729,15 +54837,9 @@
       <c r="M891" s="31"/>
     </row>
     <row r="892" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A892" s="47" t="s">
-        <v>559</v>
-      </c>
       <c r="M892" s="31"/>
     </row>
     <row r="893" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A893" s="47" t="s">
-        <v>558</v>
-      </c>
       <c r="M893" s="31"/>
     </row>
     <row r="894" spans="1:15" x14ac:dyDescent="0.35">
@@ -54781,9 +54883,7 @@
   <cols>
     <col min="1" max="1" width="30.453125" customWidth="1"/>
     <col min="2" max="2" width="21.26953125" bestFit="1" customWidth="1"/>
-    <col min="3" max="9" width="10.08984375" customWidth="1"/>
-    <col min="10" max="10" width="11.6328125" customWidth="1"/>
-    <col min="11" max="11" width="10.08984375" customWidth="1"/>
+    <col min="3" max="11" width="10.08984375" customWidth="1"/>
     <col min="12" max="12" width="15.7265625" customWidth="1"/>
     <col min="13" max="14" width="6.1796875" customWidth="1"/>
     <col min="15" max="15" width="1.81640625" customWidth="1"/>
@@ -54801,8 +54901,7 @@
     <col min="42" max="42" width="13.54296875" customWidth="1"/>
     <col min="43" max="46" width="10.08984375" customWidth="1"/>
     <col min="47" max="47" width="11.26953125" customWidth="1"/>
-    <col min="48" max="48" width="6.1796875" customWidth="1"/>
-    <col min="49" max="49" width="10.08984375" customWidth="1"/>
+    <col min="48" max="49" width="6.1796875" customWidth="1"/>
     <col min="50" max="50" width="1.81640625" customWidth="1"/>
     <col min="51" max="51" width="12" customWidth="1"/>
     <col min="52" max="52" width="6.1796875" customWidth="1"/>
@@ -56752,9 +56851,7 @@
       <c r="G30" s="30"/>
       <c r="H30" s="30"/>
       <c r="I30" s="30"/>
-      <c r="J30" s="66">
-        <v>857200</v>
-      </c>
+      <c r="J30" s="66"/>
       <c r="K30" s="66"/>
       <c r="L30" s="30"/>
       <c r="M30" s="30"/>
@@ -56815,9 +56912,7 @@
       <c r="AV30" s="30">
         <v>0</v>
       </c>
-      <c r="AW30" s="66">
-        <v>750000</v>
-      </c>
+      <c r="AW30" s="66"/>
       <c r="AX30" s="30"/>
       <c r="AY30" s="30"/>
       <c r="AZ30" s="30"/>
@@ -57259,7 +57354,7 @@
         <v>240000</v>
       </c>
       <c r="J35" s="30">
-        <v>1277200</v>
+        <v>420000</v>
       </c>
       <c r="K35" s="30">
         <v>312000</v>
@@ -57374,7 +57469,7 @@
         <v>0</v>
       </c>
       <c r="AW35" s="30">
-        <v>750000</v>
+        <v>0</v>
       </c>
       <c r="AX35" s="30"/>
       <c r="AY35" s="30">

--- a/Reporte_gastos/gastos desde 2025-05.xlsx
+++ b/Reporte_gastos/gastos desde 2025-05.xlsx
@@ -5,7 +5,7 @@
   <workbookPr hidePivotFieldList="1" defaultThemeVersion="164011"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\PC\Documents\Valeria\Reportes\Reporte_gastos\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\maval\Documents\Vale laburo\Castelli\Reportes\Reporte_gastos\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -21,9 +21,9 @@
   </definedNames>
   <calcPr calcId="162913"/>
   <pivotCaches>
-    <pivotCache cacheId="1" r:id="rId4"/>
-    <pivotCache cacheId="2" r:id="rId5"/>
-    <pivotCache cacheId="15" r:id="rId6"/>
+    <pivotCache cacheId="2" r:id="rId4"/>
+    <pivotCache cacheId="3" r:id="rId5"/>
+    <pivotCache cacheId="4" r:id="rId6"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -2040,109 +2040,7 @@
     <cellStyle name="Moneda" xfId="1" builtinId="4"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="39">
-    <dxf>
-      <numFmt numFmtId="34" formatCode="_-&quot;$&quot;\ * #,##0.00_-;\-&quot;$&quot;\ * #,##0.00_-;_-&quot;$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="169" formatCode="_-&quot;$&quot;\ * #,##0.0_-;\-&quot;$&quot;\ * #,##0.0_-;_-&quot;$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="_-&quot;$&quot;\ * #,##0_-;\-&quot;$&quot;\ * #,##0_-;_-&quot;$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="none">
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="34" formatCode="_-&quot;$&quot;\ * #,##0.00_-;\-&quot;$&quot;\ * #,##0.00_-;_-&quot;$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="169" formatCode="_-&quot;$&quot;\ * #,##0.0_-;\-&quot;$&quot;\ * #,##0.0_-;_-&quot;$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="_-&quot;$&quot;\ * #,##0_-;\-&quot;$&quot;\ * #,##0_-;_-&quot;$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="none">
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="21">
     <dxf>
       <fill>
         <patternFill patternType="solid">
@@ -28471,7 +28369,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="TablaDinámica3" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="6" minRefreshableVersion="3" useAutoFormatting="1" rowGrandTotals="0" colGrandTotals="0" itemPrintTitles="1" createdVersion="6" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="TablaDinámica3" cacheId="2" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="6" minRefreshableVersion="3" useAutoFormatting="1" rowGrandTotals="0" colGrandTotals="0" itemPrintTitles="1" createdVersion="6" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="A3:AP16" firstHeaderRow="1" firstDataRow="3" firstDataCol="1" rowPageCount="1" colPageCount="1"/>
   <pivotFields count="9">
     <pivotField axis="axisRow" showAll="0">
@@ -28756,7 +28654,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="TablaDinámica4" cacheId="15" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="6" minRefreshableVersion="3" useAutoFormatting="1" colGrandTotals="0" itemPrintTitles="1" createdVersion="6" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="TablaDinámica4" cacheId="4" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="6" minRefreshableVersion="3" useAutoFormatting="1" colGrandTotals="0" itemPrintTitles="1" createdVersion="6" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="A22:AZ35" firstHeaderRow="1" firstDataRow="3" firstDataCol="1" rowPageCount="1" colPageCount="1"/>
   <pivotFields count="9">
     <pivotField axis="axisRow" showAll="0">
@@ -29064,16 +28962,16 @@
     <dataField name="Suma de IMPORTE" fld="5" baseField="0" baseItem="0" numFmtId="164"/>
   </dataFields>
   <formats count="9">
-    <format dxfId="38">
+    <format dxfId="20">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
-    <format dxfId="37">
+    <format dxfId="19">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
-    <format dxfId="36">
+    <format dxfId="18">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
-    <format dxfId="35">
+    <format dxfId="17">
       <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
         <references count="3">
           <reference field="0" count="10">
@@ -29097,7 +28995,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="34">
+    <format dxfId="16">
       <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
         <references count="3">
           <reference field="0" count="1">
@@ -29112,7 +29010,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="33">
+    <format dxfId="15">
       <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
         <references count="3">
           <reference field="0" count="1">
@@ -29127,7 +29025,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="32">
+    <format dxfId="14">
       <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
         <references count="3">
           <reference field="0" count="1">
@@ -29142,7 +29040,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="31">
+    <format dxfId="13">
       <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
         <references count="3">
           <reference field="0" count="1">
@@ -29157,7 +29055,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="30">
+    <format dxfId="12">
       <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
         <references count="3">
           <reference field="0" count="1">
@@ -29183,7 +29081,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable3.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="TablaDinámica2" cacheId="2" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="6" minRefreshableVersion="3" useAutoFormatting="1" rowGrandTotals="0" colGrandTotals="0" itemPrintTitles="1" createdVersion="6" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="TablaDinámica2" cacheId="3" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="6" minRefreshableVersion="3" useAutoFormatting="1" rowGrandTotals="0" colGrandTotals="0" itemPrintTitles="1" createdVersion="6" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="A4:K16" firstHeaderRow="1" firstDataRow="3" firstDataCol="1" rowPageCount="2" colPageCount="1"/>
   <pivotFields count="9">
     <pivotField axis="axisRow" showAll="0" defaultSubtotal="0">
@@ -29355,16 +29253,16 @@
     <dataField name="Suma de IMPORTE" fld="5" baseField="0" baseItem="0" numFmtId="164"/>
   </dataFields>
   <formats count="12">
-    <format dxfId="29">
+    <format dxfId="11">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
-    <format dxfId="28">
+    <format dxfId="10">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
-    <format dxfId="27">
+    <format dxfId="9">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
-    <format dxfId="26">
+    <format dxfId="8">
       <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
         <references count="3">
           <reference field="0" count="1">
@@ -29379,7 +29277,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="25">
+    <format dxfId="7">
       <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
         <references count="3">
           <reference field="0" count="1">
@@ -29394,7 +29292,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="24">
+    <format dxfId="6">
       <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
         <references count="3">
           <reference field="0" count="1">
@@ -29409,7 +29307,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="23">
+    <format dxfId="5">
       <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
         <references count="3">
           <reference field="0" count="1">
@@ -29426,7 +29324,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="22">
+    <format dxfId="4">
       <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
         <references count="3">
           <reference field="0" count="1">
@@ -29441,7 +29339,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="21">
+    <format dxfId="3">
       <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
         <references count="3">
           <reference field="0" count="1">
@@ -29460,7 +29358,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="20">
+    <format dxfId="2">
       <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
         <references count="3">
           <reference field="0" count="4">
@@ -29478,7 +29376,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="19">
+    <format dxfId="1">
       <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
         <references count="3">
           <reference field="0" count="1">
@@ -29493,7 +29391,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="18">
+    <format dxfId="0">
       <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
         <references count="3">
           <reference field="0" count="1">

--- a/Reporte_gastos/gastos desde 2025-05.xlsx
+++ b/Reporte_gastos/gastos desde 2025-05.xlsx
@@ -5,11 +5,11 @@
   <workbookPr hidePivotFieldList="1" defaultThemeVersion="164011"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\maval\Documents\Vale laburo\Castelli\Reportes\Reporte_gastos\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\PC\Documents\Valeria\Reportes\Reporte_gastos\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="7050"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="7050" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="tabla" sheetId="1" r:id="rId1"/>
@@ -21,9 +21,9 @@
   </definedNames>
   <calcPr calcId="162913"/>
   <pivotCaches>
-    <pivotCache cacheId="2" r:id="rId4"/>
-    <pivotCache cacheId="3" r:id="rId5"/>
-    <pivotCache cacheId="4" r:id="rId6"/>
+    <pivotCache cacheId="15" r:id="rId4"/>
+    <pivotCache cacheId="16" r:id="rId5"/>
+    <pivotCache cacheId="17" r:id="rId6"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3593" uniqueCount="562">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3779" uniqueCount="621">
   <si>
     <t>ITEM</t>
   </si>
@@ -1720,6 +1720,183 @@
   </si>
   <si>
     <t>750000 habilitación</t>
+  </si>
+  <si>
+    <t>FA 00003-00009248</t>
+  </si>
+  <si>
+    <t>$ 1,241,904.87</t>
+  </si>
+  <si>
+    <t>$ 260,800.02</t>
+  </si>
+  <si>
+    <t>$ 1,502,704.89</t>
+  </si>
+  <si>
+    <t>BBVA</t>
+  </si>
+  <si>
+    <t>$ 1,345,400.72</t>
+  </si>
+  <si>
+    <t>cargar odoo</t>
+  </si>
+  <si>
+    <t>ND 00002-00000088</t>
+  </si>
+  <si>
+    <t>$ 690,308.12</t>
+  </si>
+  <si>
+    <t>$ 1,869,253.94</t>
+  </si>
+  <si>
+    <t>FA 00002-00000261</t>
+  </si>
+  <si>
+    <t>$ 7,325,000.00</t>
+  </si>
+  <si>
+    <t>$ 1,538,250.00</t>
+  </si>
+  <si>
+    <t>$ 8,863,250.00</t>
+  </si>
+  <si>
+    <t>$ 8,424,422.00</t>
+  </si>
+  <si>
+    <t>$ 522,241.21</t>
+  </si>
+  <si>
+    <t>$ 141,005.13</t>
+  </si>
+  <si>
+    <t>$ 32,848.98</t>
+  </si>
+  <si>
+    <t>$ 696,095.32</t>
+  </si>
+  <si>
+    <t>$ 482,850.50</t>
+  </si>
+  <si>
+    <t>$ -</t>
+  </si>
+  <si>
+    <t>$ 300,750.00</t>
+  </si>
+  <si>
+    <t>EFECTIVO</t>
+  </si>
+  <si>
+    <t>FA 00003-00020841</t>
+  </si>
+  <si>
+    <t>$ 82,049.65</t>
+  </si>
+  <si>
+    <t>$ 17,230.43</t>
+  </si>
+  <si>
+    <t>$ 99,280.08</t>
+  </si>
+  <si>
+    <t>$ 94,357.10</t>
+  </si>
+  <si>
+    <t>COM LUCERO GUEMES GONDOLA 7 (LC 2)</t>
+  </si>
+  <si>
+    <t>FA 00003-00020844</t>
+  </si>
+  <si>
+    <t>$ 58,606.89</t>
+  </si>
+  <si>
+    <t>$ 12,307.45</t>
+  </si>
+  <si>
+    <t>$ 70,914.34</t>
+  </si>
+  <si>
+    <t>$ 67,397.93</t>
+  </si>
+  <si>
+    <t>FA 00003-00020824</t>
+  </si>
+  <si>
+    <t>$ 19,056.04</t>
+  </si>
+  <si>
+    <t>$ 4,001.77</t>
+  </si>
+  <si>
+    <t>$ 23,057.81</t>
+  </si>
+  <si>
+    <t>$ 21,914.45</t>
+  </si>
+  <si>
+    <t>MP</t>
+  </si>
+  <si>
+    <t>FA 00030-00095153</t>
+  </si>
+  <si>
+    <t>$ 3,180,189.88</t>
+  </si>
+  <si>
+    <t>$ 3,050,213.89</t>
+  </si>
+  <si>
+    <t>FA 00030-00094958</t>
+  </si>
+  <si>
+    <t>$ 3,057,715.01</t>
+  </si>
+  <si>
+    <t>ECHEQ</t>
+  </si>
+  <si>
+    <t>FA 03950-07242634</t>
+  </si>
+  <si>
+    <t>$ 31,368.69</t>
+  </si>
+  <si>
+    <t>FA 00003-00009246</t>
+  </si>
+  <si>
+    <t>$ 2,204,956.64</t>
+  </si>
+  <si>
+    <t>$ 463,040.89</t>
+  </si>
+  <si>
+    <t>$ 2,667,997.53</t>
+  </si>
+  <si>
+    <t>$ 672,700.36</t>
+  </si>
+  <si>
+    <t>FA 00003-00009247</t>
+  </si>
+  <si>
+    <t>$ 1,079,060.00</t>
+  </si>
+  <si>
+    <t>$ 226,602.60</t>
+  </si>
+  <si>
+    <t>$ 1,305,662.60</t>
+  </si>
+  <si>
+    <t>$ 5,205,481.73</t>
+  </si>
+  <si>
+    <t>$ 111,824.85</t>
   </si>
 </sst>
 </file>
@@ -1906,7 +2083,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="80">
+  <cellXfs count="79">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
@@ -2019,7 +2196,6 @@
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="44" fontId="8" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="167" fontId="2" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="167" fontId="3" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="167" fontId="3" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
@@ -28369,7 +28545,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="TablaDinámica3" cacheId="2" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="6" minRefreshableVersion="3" useAutoFormatting="1" rowGrandTotals="0" colGrandTotals="0" itemPrintTitles="1" createdVersion="6" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="TablaDinámica3" cacheId="15" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="6" minRefreshableVersion="3" useAutoFormatting="1" rowGrandTotals="0" colGrandTotals="0" itemPrintTitles="1" createdVersion="6" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="A3:AP16" firstHeaderRow="1" firstDataRow="3" firstDataCol="1" rowPageCount="1" colPageCount="1"/>
   <pivotFields count="9">
     <pivotField axis="axisRow" showAll="0">
@@ -28654,7 +28830,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="TablaDinámica4" cacheId="4" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="6" minRefreshableVersion="3" useAutoFormatting="1" colGrandTotals="0" itemPrintTitles="1" createdVersion="6" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="TablaDinámica4" cacheId="17" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="6" minRefreshableVersion="3" useAutoFormatting="1" colGrandTotals="0" itemPrintTitles="1" createdVersion="6" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="A22:AZ35" firstHeaderRow="1" firstDataRow="3" firstDataCol="1" rowPageCount="1" colPageCount="1"/>
   <pivotFields count="9">
     <pivotField axis="axisRow" showAll="0">
@@ -29081,7 +29257,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable3.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="TablaDinámica2" cacheId="3" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="6" minRefreshableVersion="3" useAutoFormatting="1" rowGrandTotals="0" colGrandTotals="0" itemPrintTitles="1" createdVersion="6" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="TablaDinámica2" cacheId="16" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="6" minRefreshableVersion="3" useAutoFormatting="1" rowGrandTotals="0" colGrandTotals="0" itemPrintTitles="1" createdVersion="6" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="A4:K16" firstHeaderRow="1" firstDataRow="3" firstDataCol="1" rowPageCount="2" colPageCount="1"/>
   <pivotFields count="9">
     <pivotField axis="axisRow" showAll="0" defaultSubtotal="0">
@@ -29679,7 +29855,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:AQ902"/>
+  <dimension ref="A1:AQ919"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="12.90625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="35.54296875" style="2" customWidth="1"/>
@@ -29744,7 +29920,7 @@
       <c r="E1" s="53" t="s">
         <v>246</v>
       </c>
-      <c r="F1" s="70" t="s">
+      <c r="F1" s="53" t="s">
         <v>2</v>
       </c>
       <c r="G1" s="1" t="s">
@@ -29834,7 +30010,7 @@
       <c r="E3" s="4">
         <v>45845</v>
       </c>
-      <c r="F3" s="71">
+      <c r="F3" s="70">
         <v>55000</v>
       </c>
       <c r="G3" s="2">
@@ -29875,7 +30051,7 @@
       <c r="E4" s="4">
         <v>45845</v>
       </c>
-      <c r="F4" s="71">
+      <c r="F4" s="70">
         <v>40000</v>
       </c>
       <c r="G4" s="2">
@@ -30285,7 +30461,7 @@
       <c r="E14" s="4">
         <v>45845</v>
       </c>
-      <c r="F14" s="71">
+      <c r="F14" s="70">
         <v>55000</v>
       </c>
       <c r="G14" s="2">
@@ -30314,7 +30490,7 @@
       <c r="E15" s="4">
         <v>45845</v>
       </c>
-      <c r="F15" s="71">
+      <c r="F15" s="70">
         <v>40000</v>
       </c>
       <c r="G15" s="2">
@@ -30496,7 +30672,7 @@
       <c r="E22" s="4">
         <v>45845</v>
       </c>
-      <c r="F22" s="71">
+      <c r="F22" s="70">
         <v>40000</v>
       </c>
       <c r="G22" s="2">
@@ -30686,7 +30862,7 @@
       <c r="E27" s="4">
         <v>45845</v>
       </c>
-      <c r="F27" s="71">
+      <c r="F27" s="70">
         <v>40000</v>
       </c>
       <c r="G27" s="2">
@@ -30724,7 +30900,7 @@
       <c r="E28" s="4">
         <v>45845</v>
       </c>
-      <c r="F28" s="71">
+      <c r="F28" s="70">
         <v>55000</v>
       </c>
       <c r="G28" s="2">
@@ -30972,7 +31148,7 @@
       <c r="E34" s="4">
         <v>45845</v>
       </c>
-      <c r="F34" s="71">
+      <c r="F34" s="70">
         <v>55000</v>
       </c>
       <c r="G34" s="2">
@@ -30998,7 +31174,7 @@
       <c r="E35" s="4">
         <v>45845</v>
       </c>
-      <c r="F35" s="71">
+      <c r="F35" s="70">
         <v>40000</v>
       </c>
       <c r="G35" s="2">
@@ -31226,7 +31402,7 @@
       <c r="E44" s="4">
         <v>45845</v>
       </c>
-      <c r="F44" s="72">
+      <c r="F44" s="71">
         <v>40000</v>
       </c>
       <c r="G44" s="2">
@@ -32526,7 +32702,7 @@
         <v>86</v>
       </c>
       <c r="E95" s="23"/>
-      <c r="F95" s="73"/>
+      <c r="F95" s="72"/>
       <c r="G95" s="19">
         <v>5</v>
       </c>
@@ -32694,7 +32870,7 @@
         <v>92</v>
       </c>
       <c r="E102" s="23"/>
-      <c r="F102" s="74">
+      <c r="F102" s="73">
         <v>361000</v>
       </c>
       <c r="G102" s="19">
@@ -33040,7 +33216,7 @@
         <v>101</v>
       </c>
       <c r="E116" s="23"/>
-      <c r="F116" s="74">
+      <c r="F116" s="73">
         <v>143450</v>
       </c>
       <c r="G116" s="19">
@@ -36811,7 +36987,7 @@
       <c r="E263" s="31">
         <v>45931</v>
       </c>
-      <c r="F263" s="75">
+      <c r="F263" s="74">
         <v>20000</v>
       </c>
       <c r="G263" s="19">
@@ -37062,7 +37238,7 @@
       <c r="E273" s="31">
         <v>45931</v>
       </c>
-      <c r="F273" s="75">
+      <c r="F273" s="74">
         <v>40000</v>
       </c>
       <c r="G273" s="19">
@@ -37368,7 +37544,7 @@
       <c r="E285" s="31">
         <v>45931</v>
       </c>
-      <c r="F285" s="75">
+      <c r="F285" s="74">
         <v>40000</v>
       </c>
       <c r="G285" s="19">
@@ -37514,7 +37690,7 @@
       <c r="E291" s="31">
         <v>45931</v>
       </c>
-      <c r="F291" s="75">
+      <c r="F291" s="74">
         <v>40000</v>
       </c>
       <c r="G291" s="19">
@@ -37568,7 +37744,7 @@
       <c r="E293" s="31">
         <v>45931</v>
       </c>
-      <c r="F293" s="75">
+      <c r="F293" s="74">
         <v>40000</v>
       </c>
       <c r="G293" s="19">
@@ -37761,7 +37937,7 @@
       <c r="E301" s="31">
         <v>45931</v>
       </c>
-      <c r="F301" s="75">
+      <c r="F301" s="74">
         <v>40000</v>
       </c>
       <c r="G301" s="19">
@@ -37940,7 +38116,7 @@
       <c r="E308" s="31">
         <v>45931</v>
       </c>
-      <c r="F308" s="75">
+      <c r="F308" s="74">
         <v>20000</v>
       </c>
       <c r="G308" s="19">
@@ -38841,7 +39017,7 @@
       <c r="E342" s="45">
         <v>45988</v>
       </c>
-      <c r="F342" s="76">
+      <c r="F342" s="75">
         <v>20000</v>
       </c>
       <c r="G342" s="19">
@@ -38907,7 +39083,7 @@
       <c r="E344" s="45">
         <v>45988</v>
       </c>
-      <c r="F344" s="76">
+      <c r="F344" s="75">
         <v>40000</v>
       </c>
       <c r="G344" s="19">
@@ -39105,7 +39281,7 @@
       <c r="E350" s="45">
         <v>45988</v>
       </c>
-      <c r="F350" s="76">
+      <c r="F350" s="75">
         <v>40000</v>
       </c>
       <c r="G350" s="19">
@@ -39138,7 +39314,7 @@
       <c r="E351" s="45">
         <v>45988</v>
       </c>
-      <c r="F351" s="76">
+      <c r="F351" s="75">
         <v>40000</v>
       </c>
       <c r="G351" s="19">
@@ -39331,7 +39507,7 @@
       <c r="E357" s="45">
         <v>45988</v>
       </c>
-      <c r="F357" s="76">
+      <c r="F357" s="75">
         <v>40000</v>
       </c>
       <c r="G357" s="19">
@@ -39490,7 +39666,7 @@
       <c r="E362" s="45">
         <v>45988</v>
       </c>
-      <c r="F362" s="76">
+      <c r="F362" s="75">
         <v>40000</v>
       </c>
       <c r="G362" s="19">
@@ -39853,7 +40029,7 @@
       <c r="E373" s="45">
         <v>45988</v>
       </c>
-      <c r="F373" s="76">
+      <c r="F373" s="75">
         <v>40000</v>
       </c>
       <c r="G373" s="19">
@@ -40080,7 +40256,7 @@
       <c r="E380" s="45">
         <v>45988</v>
       </c>
-      <c r="F380" s="76">
+      <c r="F380" s="75">
         <v>40000</v>
       </c>
       <c r="G380" s="19">
@@ -40337,7 +40513,7 @@
       <c r="E388" s="45">
         <v>45988</v>
       </c>
-      <c r="F388" s="76">
+      <c r="F388" s="75">
         <v>40000</v>
       </c>
       <c r="G388" s="19">
@@ -40528,7 +40704,7 @@
       <c r="E394" s="45">
         <v>45988</v>
       </c>
-      <c r="F394" s="76">
+      <c r="F394" s="75">
         <v>40000</v>
       </c>
       <c r="G394" s="19">
@@ -40561,7 +40737,7 @@
       <c r="E395" s="45">
         <v>45988</v>
       </c>
-      <c r="F395" s="76">
+      <c r="F395" s="75">
         <v>20000</v>
       </c>
       <c r="G395" s="19">
@@ -41013,7 +41189,7 @@
       <c r="E409" s="51">
         <v>46045</v>
       </c>
-      <c r="F409" s="77">
+      <c r="F409" s="76">
         <v>40000</v>
       </c>
       <c r="G409" s="19">
@@ -41306,7 +41482,7 @@
       <c r="E418" s="45">
         <v>46045</v>
       </c>
-      <c r="F418" s="76">
+      <c r="F418" s="75">
         <v>40000</v>
       </c>
       <c r="G418" s="19">
@@ -41405,7 +41581,7 @@
       <c r="E421" s="45">
         <v>46045</v>
       </c>
-      <c r="F421" s="76">
+      <c r="F421" s="75">
         <v>20000</v>
       </c>
       <c r="G421" s="19">
@@ -41570,7 +41746,7 @@
       <c r="E426" s="45">
         <v>46045</v>
       </c>
-      <c r="F426" s="76">
+      <c r="F426" s="75">
         <v>40000</v>
       </c>
       <c r="G426" s="19">
@@ -42156,7 +42332,7 @@
       <c r="E444" s="45">
         <v>46045</v>
       </c>
-      <c r="F444" s="76">
+      <c r="F444" s="75">
         <v>40000</v>
       </c>
       <c r="G444" s="19">
@@ -42639,7 +42815,7 @@
       <c r="E459" s="45">
         <v>46045</v>
       </c>
-      <c r="F459" s="76">
+      <c r="F459" s="75">
         <v>40000</v>
       </c>
       <c r="G459" s="19">
@@ -42833,7 +43009,7 @@
       <c r="E465" s="51">
         <v>46045</v>
       </c>
-      <c r="F465" s="77">
+      <c r="F465" s="76">
         <v>20000</v>
       </c>
       <c r="G465" s="19">
@@ -51117,7 +51293,7 @@
       <c r="C768" s="59" t="s">
         <v>8</v>
       </c>
-      <c r="D768" s="78" t="str">
+      <c r="D768" s="77" t="str">
         <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE""")," FC 00001-00000147")</f>
         <v xml:space="preserve"> FC 00001-00000147</v>
       </c>
@@ -51217,11 +51393,11 @@
       <c r="C771" s="59" t="s">
         <v>8</v>
       </c>
-      <c r="D771" s="78" t="str">
+      <c r="D771" s="77" t="str">
         <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE""")," FC 00001-00000147")</f>
         <v xml:space="preserve"> FC 00001-00000147</v>
       </c>
-      <c r="E771" s="79">
+      <c r="E771" s="78">
         <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),46141)</f>
         <v>46141</v>
       </c>
@@ -54738,34 +54914,800 @@
       <c r="M892" s="31"/>
     </row>
     <row r="893" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="M893" s="31"/>
+      <c r="A893" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="B893" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C893" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="D893" s="2" t="s">
+        <v>562</v>
+      </c>
+      <c r="E893" s="31">
+        <v>46181</v>
+      </c>
+      <c r="F893" s="55" t="s">
+        <v>563</v>
+      </c>
+      <c r="G893" s="2" t="s">
+        <v>564</v>
+      </c>
+      <c r="I893" s="2" t="s">
+        <v>565</v>
+      </c>
+      <c r="K893" s="2" t="s">
+        <v>566</v>
+      </c>
+      <c r="L893" s="31">
+        <v>46196</v>
+      </c>
+      <c r="M893" s="31">
+        <v>46196</v>
+      </c>
     </row>
     <row r="894" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="M894" s="31"/>
+      <c r="A894" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="B894" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C894" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="D894" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="F894" s="2" t="s">
+        <v>567</v>
+      </c>
+      <c r="I894" s="2" t="s">
+        <v>567</v>
+      </c>
+      <c r="J894" s="2" t="s">
+        <v>568</v>
+      </c>
+      <c r="K894" s="2" t="s">
+        <v>566</v>
+      </c>
+      <c r="L894" s="31">
+        <v>46180</v>
+      </c>
+      <c r="M894" s="31">
+        <v>46183</v>
+      </c>
     </row>
     <row r="895" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A895" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="B895" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="C895" s="2" t="s">
+        <v>26</v>
+      </c>
       <c r="M895" s="31"/>
     </row>
     <row r="896" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="M896" s="31"/>
-    </row>
-    <row r="897" spans="13:13" x14ac:dyDescent="0.35">
-      <c r="M897" s="31"/>
-    </row>
-    <row r="898" spans="13:13" x14ac:dyDescent="0.35">
-      <c r="M898" s="31"/>
-    </row>
-    <row r="899" spans="13:13" x14ac:dyDescent="0.35">
-      <c r="M899" s="31"/>
-    </row>
-    <row r="900" spans="13:13" x14ac:dyDescent="0.35">
-      <c r="M900" s="31"/>
-    </row>
-    <row r="901" spans="13:13" x14ac:dyDescent="0.35">
-      <c r="M901" s="31"/>
-    </row>
-    <row r="902" spans="13:13" x14ac:dyDescent="0.35">
-      <c r="M902" s="31"/>
+      <c r="A896" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="B896" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C896" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="D896" s="2" t="s">
+        <v>569</v>
+      </c>
+      <c r="E896" s="31">
+        <v>46189</v>
+      </c>
+      <c r="F896" s="2" t="s">
+        <v>570</v>
+      </c>
+      <c r="H896" s="2" t="s">
+        <v>570</v>
+      </c>
+      <c r="I896" s="2" t="s">
+        <v>570</v>
+      </c>
+      <c r="J896" s="2" t="s">
+        <v>571</v>
+      </c>
+      <c r="K896" s="2" t="s">
+        <v>566</v>
+      </c>
+      <c r="L896" s="31">
+        <v>46192</v>
+      </c>
+      <c r="M896" s="31">
+        <v>46192</v>
+      </c>
+    </row>
+    <row r="897" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A897" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="B897" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C897" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="D897" s="2" t="s">
+        <v>572</v>
+      </c>
+      <c r="E897" s="31">
+        <v>46183</v>
+      </c>
+      <c r="F897" s="55" t="s">
+        <v>573</v>
+      </c>
+      <c r="G897" s="2" t="s">
+        <v>574</v>
+      </c>
+      <c r="I897" s="2" t="s">
+        <v>575</v>
+      </c>
+      <c r="J897" s="2" t="s">
+        <v>576</v>
+      </c>
+      <c r="K897" s="2" t="s">
+        <v>566</v>
+      </c>
+      <c r="L897" s="31">
+        <v>46185</v>
+      </c>
+      <c r="M897" s="31">
+        <v>46185</v>
+      </c>
+    </row>
+    <row r="898" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A898" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="B898" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C898" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="D898" s="2" t="s">
+        <v>569</v>
+      </c>
+      <c r="E898" s="31">
+        <v>46189</v>
+      </c>
+      <c r="F898" s="55" t="s">
+        <v>577</v>
+      </c>
+      <c r="G898" s="2" t="s">
+        <v>578</v>
+      </c>
+      <c r="H898" s="2" t="s">
+        <v>579</v>
+      </c>
+      <c r="I898" s="2" t="s">
+        <v>580</v>
+      </c>
+      <c r="K898" s="2" t="s">
+        <v>566</v>
+      </c>
+      <c r="L898" s="31">
+        <v>46192</v>
+      </c>
+      <c r="M898" s="31">
+        <v>46192</v>
+      </c>
+    </row>
+    <row r="899" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A899" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="B899" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C899" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="D899" s="2" t="s">
+        <v>569</v>
+      </c>
+      <c r="E899" s="31">
+        <v>46189</v>
+      </c>
+      <c r="F899" s="2" t="s">
+        <v>581</v>
+      </c>
+      <c r="H899" s="2" t="s">
+        <v>581</v>
+      </c>
+      <c r="I899" s="2" t="s">
+        <v>581</v>
+      </c>
+      <c r="K899" s="2" t="s">
+        <v>566</v>
+      </c>
+      <c r="L899" s="31">
+        <v>46192</v>
+      </c>
+      <c r="M899" s="31">
+        <v>46192</v>
+      </c>
+    </row>
+    <row r="900" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A900" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="B900" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C900" s="2" t="s">
+        <v>321</v>
+      </c>
+      <c r="K900" s="2" t="s">
+        <v>566</v>
+      </c>
+      <c r="L900" s="31">
+        <v>46184</v>
+      </c>
+      <c r="M900" s="31">
+        <v>46184</v>
+      </c>
+    </row>
+    <row r="901" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A901" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="B901" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C901" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="D901" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="F901" s="2" t="s">
+        <v>583</v>
+      </c>
+      <c r="I901" s="2" t="s">
+        <v>583</v>
+      </c>
+      <c r="J901" s="2" t="s">
+        <v>568</v>
+      </c>
+      <c r="K901" s="2" t="s">
+        <v>584</v>
+      </c>
+      <c r="L901" s="31">
+        <v>46183</v>
+      </c>
+      <c r="M901" s="31">
+        <v>46183</v>
+      </c>
+    </row>
+    <row r="902" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A902" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="B902" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C902" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="D902" s="2" t="s">
+        <v>585</v>
+      </c>
+      <c r="E902" s="31">
+        <v>46189</v>
+      </c>
+      <c r="F902" s="55" t="s">
+        <v>586</v>
+      </c>
+      <c r="G902" s="2" t="s">
+        <v>587</v>
+      </c>
+      <c r="I902" s="2" t="s">
+        <v>588</v>
+      </c>
+      <c r="J902" s="2" t="s">
+        <v>589</v>
+      </c>
+      <c r="K902" s="2" t="s">
+        <v>566</v>
+      </c>
+      <c r="L902" s="31">
+        <v>46192</v>
+      </c>
+      <c r="M902" s="31">
+        <v>46192</v>
+      </c>
+    </row>
+    <row r="903" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A903" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="B903" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C903" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="K903" s="2" t="s">
+        <v>566</v>
+      </c>
+      <c r="L903" s="31">
+        <v>46183</v>
+      </c>
+      <c r="M903" s="31">
+        <v>46183</v>
+      </c>
+    </row>
+    <row r="904" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A904" s="2" t="s">
+        <v>590</v>
+      </c>
+      <c r="B904" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C904" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="D904" s="2" t="s">
+        <v>591</v>
+      </c>
+      <c r="E904" s="31">
+        <v>46189</v>
+      </c>
+      <c r="F904" s="55" t="s">
+        <v>592</v>
+      </c>
+      <c r="G904" s="2" t="s">
+        <v>593</v>
+      </c>
+      <c r="I904" s="2" t="s">
+        <v>594</v>
+      </c>
+      <c r="J904" s="2" t="s">
+        <v>595</v>
+      </c>
+      <c r="K904" s="2" t="s">
+        <v>566</v>
+      </c>
+      <c r="L904" s="31">
+        <v>46192</v>
+      </c>
+      <c r="M904" s="31">
+        <v>46192</v>
+      </c>
+    </row>
+    <row r="905" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A905" s="2" t="s">
+        <v>590</v>
+      </c>
+      <c r="B905" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C905" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="D905" s="2" t="s">
+        <v>596</v>
+      </c>
+      <c r="E905" s="31">
+        <v>46175</v>
+      </c>
+      <c r="F905" s="55" t="s">
+        <v>597</v>
+      </c>
+      <c r="G905" s="2" t="s">
+        <v>598</v>
+      </c>
+      <c r="I905" s="2" t="s">
+        <v>599</v>
+      </c>
+      <c r="J905" s="2" t="s">
+        <v>600</v>
+      </c>
+      <c r="K905" s="2" t="s">
+        <v>566</v>
+      </c>
+      <c r="L905" s="31">
+        <v>46192</v>
+      </c>
+      <c r="M905" s="31">
+        <v>46192</v>
+      </c>
+    </row>
+    <row r="906" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A906" s="2" t="s">
+        <v>590</v>
+      </c>
+      <c r="B906" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C906" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="G906" s="2" t="s">
+        <v>582</v>
+      </c>
+      <c r="K906" s="2" t="s">
+        <v>566</v>
+      </c>
+      <c r="L906" s="31">
+        <v>46183</v>
+      </c>
+      <c r="M906" s="31">
+        <v>46183</v>
+      </c>
+    </row>
+    <row r="907" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A907" s="2" t="s">
+        <v>590</v>
+      </c>
+      <c r="B907" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C907" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="K907" s="2" t="s">
+        <v>566</v>
+      </c>
+      <c r="L907" s="31">
+        <v>46183</v>
+      </c>
+      <c r="M907" s="31">
+        <v>46183</v>
+      </c>
+    </row>
+    <row r="908" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A908" s="2" t="s">
+        <v>292</v>
+      </c>
+      <c r="B908" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="C908" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="G908" s="2" t="s">
+        <v>582</v>
+      </c>
+      <c r="K908" s="2" t="s">
+        <v>601</v>
+      </c>
+      <c r="L908" s="31">
+        <v>46178</v>
+      </c>
+      <c r="M908" s="31">
+        <v>46178</v>
+      </c>
+    </row>
+    <row r="909" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A909" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B909" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C909" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="D909" s="2" t="s">
+        <v>602</v>
+      </c>
+      <c r="G909" s="2" t="s">
+        <v>582</v>
+      </c>
+      <c r="I909" s="2" t="s">
+        <v>603</v>
+      </c>
+      <c r="J909" s="2" t="s">
+        <v>604</v>
+      </c>
+      <c r="K909" s="2" t="s">
+        <v>566</v>
+      </c>
+      <c r="L909" s="31">
+        <v>46183</v>
+      </c>
+      <c r="M909" s="31">
+        <v>46183</v>
+      </c>
+    </row>
+    <row r="910" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A910" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B910" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C910" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="D910" s="2" t="s">
+        <v>605</v>
+      </c>
+      <c r="I910" s="2" t="s">
+        <v>606</v>
+      </c>
+      <c r="J910" s="2" t="s">
+        <v>606</v>
+      </c>
+      <c r="K910" s="2" t="s">
+        <v>566</v>
+      </c>
+      <c r="L910" s="31">
+        <v>46183</v>
+      </c>
+      <c r="M910" s="31">
+        <v>46183</v>
+      </c>
+    </row>
+    <row r="911" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A911" s="2" t="s">
+        <v>238</v>
+      </c>
+      <c r="B911" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C911" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="G911" s="2" t="s">
+        <v>582</v>
+      </c>
+      <c r="K911" s="2" t="s">
+        <v>607</v>
+      </c>
+      <c r="L911" s="31">
+        <v>46183</v>
+      </c>
+      <c r="M911" s="31">
+        <v>46183</v>
+      </c>
+    </row>
+    <row r="912" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A912" s="2" t="s">
+        <v>238</v>
+      </c>
+      <c r="B912" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C912" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="G912" s="2" t="s">
+        <v>582</v>
+      </c>
+      <c r="K912" s="2" t="s">
+        <v>566</v>
+      </c>
+      <c r="L912" s="31">
+        <v>46222</v>
+      </c>
+    </row>
+    <row r="913" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A913" s="2" t="s">
+        <v>238</v>
+      </c>
+      <c r="B913" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C913" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="G913" s="2" t="s">
+        <v>582</v>
+      </c>
+      <c r="K913" s="2" t="s">
+        <v>566</v>
+      </c>
+      <c r="L913" s="31">
+        <v>46183</v>
+      </c>
+      <c r="M913" s="31">
+        <v>46183</v>
+      </c>
+    </row>
+    <row r="914" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A914" s="2" t="s">
+        <v>238</v>
+      </c>
+      <c r="B914" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="C914" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="D914" s="2" t="s">
+        <v>608</v>
+      </c>
+      <c r="I914" s="2" t="s">
+        <v>609</v>
+      </c>
+      <c r="J914" s="2" t="s">
+        <v>609</v>
+      </c>
+      <c r="K914" s="2" t="s">
+        <v>566</v>
+      </c>
+      <c r="L914" s="31">
+        <v>46183</v>
+      </c>
+      <c r="M914" s="31">
+        <v>46183</v>
+      </c>
+    </row>
+    <row r="915" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A915" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="B915" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C915" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="D915" s="2" t="s">
+        <v>610</v>
+      </c>
+      <c r="E915" s="31">
+        <v>46181</v>
+      </c>
+      <c r="F915" s="55" t="s">
+        <v>611</v>
+      </c>
+      <c r="G915" s="2" t="s">
+        <v>612</v>
+      </c>
+      <c r="I915" s="2" t="s">
+        <v>613</v>
+      </c>
+      <c r="K915" s="2" t="s">
+        <v>566</v>
+      </c>
+      <c r="L915" s="31">
+        <v>46196</v>
+      </c>
+      <c r="M915" s="31">
+        <v>46196</v>
+      </c>
+    </row>
+    <row r="916" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A916" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="B916" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C916" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="D916" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="I916" s="2" t="s">
+        <v>614</v>
+      </c>
+      <c r="J916" s="2" t="s">
+        <v>568</v>
+      </c>
+      <c r="K916" s="2" t="s">
+        <v>566</v>
+      </c>
+      <c r="L916" s="31">
+        <v>46180</v>
+      </c>
+      <c r="M916" s="31">
+        <v>46183</v>
+      </c>
+    </row>
+    <row r="917" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A917" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="B917" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C917" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="D917" s="2" t="s">
+        <v>615</v>
+      </c>
+      <c r="E917" s="31">
+        <v>46181</v>
+      </c>
+      <c r="F917" s="55" t="s">
+        <v>616</v>
+      </c>
+      <c r="G917" s="2" t="s">
+        <v>617</v>
+      </c>
+      <c r="I917" s="2" t="s">
+        <v>618</v>
+      </c>
+      <c r="J917" s="2" t="s">
+        <v>619</v>
+      </c>
+      <c r="K917" s="2" t="s">
+        <v>566</v>
+      </c>
+      <c r="L917" s="31">
+        <v>46196</v>
+      </c>
+      <c r="M917" s="31">
+        <v>46196</v>
+      </c>
+    </row>
+    <row r="918" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A918" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="B918" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C918" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="D918" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="I918" s="2" t="s">
+        <v>620</v>
+      </c>
+      <c r="J918" s="2" t="s">
+        <v>568</v>
+      </c>
+      <c r="K918" s="2" t="s">
+        <v>566</v>
+      </c>
+      <c r="L918" s="31">
+        <v>46191</v>
+      </c>
+      <c r="M918" s="31">
+        <v>46191</v>
+      </c>
+    </row>
+    <row r="919" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A919" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="B919" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C919" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="D919" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="I919" s="2" t="s">
+        <v>614</v>
+      </c>
+      <c r="J919" s="2" t="s">
+        <v>568</v>
+      </c>
+      <c r="K919" s="2" t="s">
+        <v>566</v>
+      </c>
+      <c r="L919" s="31">
+        <v>46180</v>
+      </c>
+      <c r="M919" s="31">
+        <v>46183</v>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:I890"/>

--- a/Reporte_gastos/gastos desde 2025-05.xlsx
+++ b/Reporte_gastos/gastos desde 2025-05.xlsx
@@ -5,11 +5,11 @@
   <workbookPr hidePivotFieldList="1" defaultThemeVersion="164011"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\PC\Documents\Valeria\Reportes\Reporte_gastos\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\maval\Documents\Vale laburo\Castelli\Reportes\Reporte_gastos\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="7060"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="7056"/>
   </bookViews>
   <sheets>
     <sheet name="tabla" sheetId="1" r:id="rId1"/>
@@ -21,8 +21,8 @@
   </definedNames>
   <calcPr calcId="162913"/>
   <pivotCaches>
-    <pivotCache cacheId="1" r:id="rId4"/>
-    <pivotCache cacheId="20" r:id="rId5"/>
+    <pivotCache cacheId="0" r:id="rId4"/>
+    <pivotCache cacheId="1" r:id="rId5"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -1948,7 +1948,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="58">
+  <cellXfs count="57">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -2074,86 +2074,12 @@
     <xf numFmtId="14" fontId="2" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="169" fontId="2" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Moneda" xfId="1" builtinId="4"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="35">
-    <dxf>
-      <numFmt numFmtId="34" formatCode="_-&quot;$&quot;\ * #,##0.00_-;\-&quot;$&quot;\ * #,##0.00_-;_-&quot;$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="169" formatCode="_-&quot;$&quot;\ * #,##0.0_-;\-&quot;$&quot;\ * #,##0.0_-;_-&quot;$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="_-&quot;$&quot;\ * #,##0_-;\-&quot;$&quot;\ * #,##0_-;_-&quot;$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="none">
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="none">
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFF0000"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="23">
     <dxf>
       <fill>
         <patternFill patternType="solid">
@@ -22013,7 +21939,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="TablaDinámica4" cacheId="20" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="6" minRefreshableVersion="3" useAutoFormatting="1" colGrandTotals="0" itemPrintTitles="1" createdVersion="6" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="TablaDinámica4" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="6" minRefreshableVersion="3" useAutoFormatting="1" colGrandTotals="0" itemPrintTitles="1" createdVersion="6" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="A22:BG35" firstHeaderRow="1" firstDataRow="3" firstDataCol="1" rowPageCount="1" colPageCount="1"/>
   <pivotFields count="9">
     <pivotField axis="axisRow" showAll="0">
@@ -22343,16 +22269,16 @@
     <dataField name="Suma de IMPORTE" fld="5" baseField="0" baseItem="0" numFmtId="164"/>
   </dataFields>
   <formats count="11">
-    <format dxfId="34">
+    <format dxfId="22">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
-    <format dxfId="33">
+    <format dxfId="21">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
-    <format dxfId="32">
+    <format dxfId="20">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
-    <format dxfId="31">
+    <format dxfId="19">
       <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
         <references count="3">
           <reference field="0" count="9">
@@ -22375,7 +22301,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="30">
+    <format dxfId="18">
       <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
         <references count="3">
           <reference field="0" count="1">
@@ -22390,7 +22316,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="29">
+    <format dxfId="17">
       <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
         <references count="3">
           <reference field="0" count="1">
@@ -22405,7 +22331,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="28">
+    <format dxfId="16">
       <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
         <references count="3">
           <reference field="0" count="1">
@@ -22420,7 +22346,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="27">
+    <format dxfId="15">
       <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
         <references count="3">
           <reference field="0" count="1">
@@ -22435,7 +22361,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="26">
+    <format dxfId="14">
       <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
         <references count="3">
           <reference field="0" count="1">
@@ -22450,7 +22376,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="25">
+    <format dxfId="13">
       <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
         <references count="3">
           <reference field="0" count="1">
@@ -22465,7 +22391,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="24">
+    <format dxfId="12">
       <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
         <references count="3">
           <reference field="0" count="9">
@@ -22500,7 +22426,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="TablaDinámica3" cacheId="20" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="6" minRefreshableVersion="3" useAutoFormatting="1" rowGrandTotals="0" colGrandTotals="0" itemPrintTitles="1" createdVersion="6" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="TablaDinámica3" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="6" minRefreshableVersion="3" useAutoFormatting="1" rowGrandTotals="0" colGrandTotals="0" itemPrintTitles="1" createdVersion="6" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="A3:BG16" firstHeaderRow="1" firstDataRow="3" firstDataCol="1" rowPageCount="1" colPageCount="1"/>
   <pivotFields count="9">
     <pivotField axis="axisRow" showAll="0">
@@ -22839,7 +22765,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable3.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="TablaDinámica2" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="6" minRefreshableVersion="3" useAutoFormatting="1" rowGrandTotals="0" colGrandTotals="0" itemPrintTitles="1" createdVersion="6" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="TablaDinámica2" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="6" minRefreshableVersion="3" useAutoFormatting="1" rowGrandTotals="0" colGrandTotals="0" itemPrintTitles="1" createdVersion="6" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="A4:M16" firstHeaderRow="1" firstDataRow="3" firstDataCol="1" rowPageCount="2" colPageCount="1"/>
   <pivotFields count="9">
     <pivotField axis="axisRow" showAll="0" defaultSubtotal="0">
@@ -23016,16 +22942,16 @@
     <dataField name="Suma de IMPORTE" fld="5" baseField="0" baseItem="0" numFmtId="164"/>
   </dataFields>
   <formats count="12">
-    <format dxfId="23">
+    <format dxfId="11">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
-    <format dxfId="22">
+    <format dxfId="10">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
-    <format dxfId="21">
+    <format dxfId="9">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
-    <format dxfId="20">
+    <format dxfId="8">
       <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
         <references count="3">
           <reference field="0" count="1">
@@ -23040,7 +22966,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="19">
+    <format dxfId="7">
       <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
         <references count="3">
           <reference field="0" count="1">
@@ -23055,7 +22981,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="18">
+    <format dxfId="6">
       <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
         <references count="3">
           <reference field="0" count="1">
@@ -23070,7 +22996,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="17">
+    <format dxfId="5">
       <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
         <references count="3">
           <reference field="0" count="1">
@@ -23087,7 +23013,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="16">
+    <format dxfId="4">
       <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
         <references count="3">
           <reference field="0" count="1">
@@ -23102,7 +23028,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="15">
+    <format dxfId="3">
       <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
         <references count="3">
           <reference field="0" count="1">
@@ -23121,7 +23047,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="14">
+    <format dxfId="2">
       <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
         <references count="3">
           <reference field="0" count="4">
@@ -23139,7 +23065,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="13">
+    <format dxfId="1">
       <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
         <references count="3">
           <reference field="0" count="1">
@@ -23154,7 +23080,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="12">
+    <format dxfId="0">
       <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
         <references count="3">
           <reference field="0" count="1">
@@ -23443,55 +23369,55 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:AQ973"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="12.90625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="12.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="35.54296875" style="29" customWidth="1"/>
-    <col min="2" max="2" width="17.6328125" style="29" customWidth="1"/>
+    <col min="1" max="1" width="35.5546875" style="29" customWidth="1"/>
+    <col min="2" max="2" width="17.6640625" style="29" customWidth="1"/>
     <col min="3" max="3" width="21" style="29" customWidth="1"/>
-    <col min="4" max="4" width="22.54296875" style="29" customWidth="1"/>
+    <col min="4" max="4" width="22.5546875" style="29" customWidth="1"/>
     <col min="5" max="5" width="16" style="38" customWidth="1"/>
-    <col min="6" max="6" width="14.54296875" style="43" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.5546875" style="43" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="13" style="36" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="13.6328125" style="36" customWidth="1"/>
-    <col min="9" max="9" width="15.08984375" style="26" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="13.90625" style="1" customWidth="1"/>
+    <col min="8" max="8" width="13.6640625" style="36" customWidth="1"/>
+    <col min="9" max="9" width="15.109375" style="26" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="13.88671875" style="1" customWidth="1"/>
     <col min="11" max="11" width="11" style="1" customWidth="1"/>
-    <col min="12" max="12" width="14.08984375" style="7" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="9.6328125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="5.453125" style="1" customWidth="1"/>
-    <col min="15" max="15" width="10.36328125" style="7" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="12.36328125" style="1" customWidth="1"/>
-    <col min="17" max="17" width="9.36328125" style="1" customWidth="1"/>
-    <col min="18" max="18" width="16.36328125" style="1" customWidth="1"/>
-    <col min="19" max="19" width="12.08984375" style="1" customWidth="1"/>
-    <col min="20" max="20" width="9.90625" style="1" customWidth="1"/>
-    <col min="21" max="21" width="11.90625" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="5.1796875" style="1" customWidth="1"/>
-    <col min="23" max="23" width="9.36328125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="5.453125" style="1" customWidth="1"/>
-    <col min="25" max="25" width="10.36328125" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="12.36328125" style="1" customWidth="1"/>
-    <col min="27" max="27" width="9.36328125" style="1" customWidth="1"/>
-    <col min="28" max="28" width="16.36328125" style="1" customWidth="1"/>
-    <col min="29" max="29" width="12.08984375" style="1" customWidth="1"/>
-    <col min="30" max="30" width="9.90625" style="1" customWidth="1"/>
-    <col min="31" max="31" width="11.90625" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="5.1796875" style="1" customWidth="1"/>
-    <col min="33" max="33" width="8.453125" style="1" customWidth="1"/>
-    <col min="34" max="34" width="9.36328125" style="1" customWidth="1"/>
-    <col min="35" max="35" width="5.453125" style="1" customWidth="1"/>
-    <col min="36" max="36" width="7.6328125" style="1" customWidth="1"/>
-    <col min="37" max="37" width="9.81640625" style="1" customWidth="1"/>
-    <col min="38" max="38" width="12.36328125" style="1" customWidth="1"/>
-    <col min="39" max="39" width="9.36328125" style="1" customWidth="1"/>
-    <col min="40" max="40" width="16.36328125" style="1" customWidth="1"/>
-    <col min="41" max="41" width="12.08984375" style="1" customWidth="1"/>
-    <col min="42" max="42" width="9.90625" style="1" customWidth="1"/>
-    <col min="43" max="43" width="7.6328125" style="1" customWidth="1"/>
-    <col min="44" max="16384" width="12.90625" style="1"/>
+    <col min="12" max="12" width="14.109375" style="7" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="9.6640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="5.44140625" style="1" customWidth="1"/>
+    <col min="15" max="15" width="10.33203125" style="7" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="12.33203125" style="1" customWidth="1"/>
+    <col min="17" max="17" width="9.33203125" style="1" customWidth="1"/>
+    <col min="18" max="18" width="16.33203125" style="1" customWidth="1"/>
+    <col min="19" max="19" width="12.109375" style="1" customWidth="1"/>
+    <col min="20" max="20" width="9.88671875" style="1" customWidth="1"/>
+    <col min="21" max="21" width="11.88671875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="5.21875" style="1" customWidth="1"/>
+    <col min="23" max="23" width="9.33203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="5.44140625" style="1" customWidth="1"/>
+    <col min="25" max="25" width="10.33203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="12.33203125" style="1" customWidth="1"/>
+    <col min="27" max="27" width="9.33203125" style="1" customWidth="1"/>
+    <col min="28" max="28" width="16.33203125" style="1" customWidth="1"/>
+    <col min="29" max="29" width="12.109375" style="1" customWidth="1"/>
+    <col min="30" max="30" width="9.88671875" style="1" customWidth="1"/>
+    <col min="31" max="31" width="11.88671875" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="5.21875" style="1" customWidth="1"/>
+    <col min="33" max="33" width="8.44140625" style="1" customWidth="1"/>
+    <col min="34" max="34" width="9.33203125" style="1" customWidth="1"/>
+    <col min="35" max="35" width="5.44140625" style="1" customWidth="1"/>
+    <col min="36" max="36" width="7.6640625" style="1" customWidth="1"/>
+    <col min="37" max="37" width="9.77734375" style="1" customWidth="1"/>
+    <col min="38" max="38" width="12.33203125" style="1" customWidth="1"/>
+    <col min="39" max="39" width="9.33203125" style="1" customWidth="1"/>
+    <col min="40" max="40" width="16.33203125" style="1" customWidth="1"/>
+    <col min="41" max="41" width="12.109375" style="1" customWidth="1"/>
+    <col min="42" max="42" width="9.88671875" style="1" customWidth="1"/>
+    <col min="43" max="43" width="7.6640625" style="1" customWidth="1"/>
+    <col min="44" max="16384" width="12.88671875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:43" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:43" x14ac:dyDescent="0.3">
       <c r="A1" s="55" t="s">
         <v>244</v>
       </c>
@@ -23507,7 +23433,7 @@
       <c r="E1" s="56" t="s">
         <v>246</v>
       </c>
-      <c r="F1" s="57" t="s">
+      <c r="F1" s="56" t="s">
         <v>2</v>
       </c>
       <c r="G1" s="35" t="s">
@@ -23520,7 +23446,7 @@
         <v>470</v>
       </c>
     </row>
-    <row r="2" spans="1:43" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:43" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="29" t="s">
         <v>60</v>
       </c>
@@ -23580,7 +23506,7 @@
       <c r="AP2"/>
       <c r="AQ2"/>
     </row>
-    <row r="3" spans="1:43" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:43" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="29" t="s">
         <v>60</v>
       </c>
@@ -23620,7 +23546,7 @@
       <c r="AP3"/>
       <c r="AQ3"/>
     </row>
-    <row r="4" spans="1:43" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:43" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="29" t="s">
         <v>60</v>
       </c>
@@ -23660,7 +23586,7 @@
       <c r="AP4"/>
       <c r="AQ4"/>
     </row>
-    <row r="5" spans="1:43" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:43" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="29" t="s">
         <v>60</v>
       </c>
@@ -23700,7 +23626,7 @@
       <c r="AP5"/>
       <c r="AQ5"/>
     </row>
-    <row r="6" spans="1:43" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:43" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="29" t="s">
         <v>60</v>
       </c>
@@ -23740,7 +23666,7 @@
       <c r="AP6"/>
       <c r="AQ6"/>
     </row>
-    <row r="7" spans="1:43" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:43" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="29" t="s">
         <v>60</v>
       </c>
@@ -23780,7 +23706,7 @@
       <c r="AP7"/>
       <c r="AQ7"/>
     </row>
-    <row r="8" spans="1:43" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:43" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="29" t="s">
         <v>60</v>
       </c>
@@ -23820,7 +23746,7 @@
       <c r="AP8"/>
       <c r="AQ8"/>
     </row>
-    <row r="9" spans="1:43" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:43" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="29" t="s">
         <v>60</v>
       </c>
@@ -23860,7 +23786,7 @@
       <c r="AP9"/>
       <c r="AQ9"/>
     </row>
-    <row r="10" spans="1:43" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:43" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="29" t="s">
         <v>60</v>
       </c>
@@ -23900,7 +23826,7 @@
       <c r="AP10"/>
       <c r="AQ10"/>
     </row>
-    <row r="11" spans="1:43" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:43" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="29" t="s">
         <v>60</v>
       </c>
@@ -23940,7 +23866,7 @@
       <c r="AP11"/>
       <c r="AQ11"/>
     </row>
-    <row r="12" spans="1:43" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:43" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="29" t="s">
         <v>60</v>
       </c>
@@ -23980,7 +23906,7 @@
       <c r="AP12"/>
       <c r="AQ12"/>
     </row>
-    <row r="13" spans="1:43" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:43" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="29" t="s">
         <v>60</v>
       </c>
@@ -24020,7 +23946,7 @@
       <c r="AP13"/>
       <c r="AQ13"/>
     </row>
-    <row r="14" spans="1:43" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:43" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="29" t="s">
         <v>15</v>
       </c>
@@ -24048,7 +23974,7 @@
       <c r="J14"/>
       <c r="K14"/>
     </row>
-    <row r="15" spans="1:43" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:43" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="29" t="s">
         <v>15</v>
       </c>
@@ -24074,7 +24000,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="16" spans="1:43" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:43" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="29" t="s">
         <v>15</v>
       </c>
@@ -24100,7 +24026,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="17" spans="1:43" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:43" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="29" t="s">
         <v>15</v>
       </c>
@@ -24126,7 +24052,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="18" spans="1:43" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:43" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="29" t="s">
         <v>15</v>
       </c>
@@ -24152,7 +24078,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="19" spans="1:43" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:43" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="29" t="s">
         <v>15</v>
       </c>
@@ -24178,7 +24104,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="20" spans="1:43" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:43" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="29" t="s">
         <v>15</v>
       </c>
@@ -24204,7 +24130,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="21" spans="1:43" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:43" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="29" t="s">
         <v>15</v>
       </c>
@@ -24230,7 +24156,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="22" spans="1:43" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:43" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="29" t="s">
         <v>67</v>
       </c>
@@ -24268,7 +24194,7 @@
       <c r="AP22"/>
       <c r="AQ22"/>
     </row>
-    <row r="23" spans="1:43" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:43" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="29" t="s">
         <v>67</v>
       </c>
@@ -24306,7 +24232,7 @@
       <c r="AP23"/>
       <c r="AQ23"/>
     </row>
-    <row r="24" spans="1:43" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:43" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="29" t="s">
         <v>67</v>
       </c>
@@ -24344,7 +24270,7 @@
       <c r="AP24"/>
       <c r="AQ24"/>
     </row>
-    <row r="25" spans="1:43" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:43" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="29" t="s">
         <v>67</v>
       </c>
@@ -24382,7 +24308,7 @@
       <c r="AP25"/>
       <c r="AQ25"/>
     </row>
-    <row r="26" spans="1:43" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:43" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="29" t="s">
         <v>67</v>
       </c>
@@ -24420,7 +24346,7 @@
       <c r="AP26"/>
       <c r="AQ26"/>
     </row>
-    <row r="27" spans="1:43" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:43" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="29" t="s">
         <v>24</v>
       </c>
@@ -24458,7 +24384,7 @@
       <c r="AP27"/>
       <c r="AQ27"/>
     </row>
-    <row r="28" spans="1:43" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:43" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="29" t="s">
         <v>24</v>
       </c>
@@ -24496,7 +24422,7 @@
       <c r="AP28"/>
       <c r="AQ28"/>
     </row>
-    <row r="29" spans="1:43" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:43" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="29" t="s">
         <v>24</v>
       </c>
@@ -24534,7 +24460,7 @@
       <c r="AP29"/>
       <c r="AQ29"/>
     </row>
-    <row r="30" spans="1:43" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:43" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="29" t="s">
         <v>24</v>
       </c>
@@ -24572,7 +24498,7 @@
       <c r="AP30"/>
       <c r="AQ30"/>
     </row>
-    <row r="31" spans="1:43" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:43" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="29" t="s">
         <v>24</v>
       </c>
@@ -24610,7 +24536,7 @@
       <c r="AP31"/>
       <c r="AQ31"/>
     </row>
-    <row r="32" spans="1:43" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:43" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="29" t="s">
         <v>24</v>
       </c>
@@ -24648,7 +24574,7 @@
       <c r="AP32"/>
       <c r="AQ32"/>
     </row>
-    <row r="33" spans="1:43" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:43" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A33" s="29" t="s">
         <v>24</v>
       </c>
@@ -24706,7 +24632,7 @@
       <c r="AP33"/>
       <c r="AQ33"/>
     </row>
-    <row r="34" spans="1:43" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:43" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A34" s="29" t="s">
         <v>28</v>
       </c>
@@ -24732,7 +24658,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="35" spans="1:43" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:43" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A35" s="29" t="s">
         <v>28</v>
       </c>
@@ -24758,7 +24684,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="36" spans="1:43" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:43" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A36" s="29" t="s">
         <v>28</v>
       </c>
@@ -24784,7 +24710,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="37" spans="1:43" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:43" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A37" s="29" t="s">
         <v>28</v>
       </c>
@@ -24810,7 +24736,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="38" spans="1:43" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:43" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A38" s="29" t="s">
         <v>28</v>
       </c>
@@ -24834,7 +24760,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="39" spans="1:43" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:43" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A39" s="29" t="s">
         <v>28</v>
       </c>
@@ -24860,7 +24786,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="40" spans="1:43" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:43" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A40" s="29" t="s">
         <v>32</v>
       </c>
@@ -24886,7 +24812,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="41" spans="1:43" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:43" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A41" s="29" t="s">
         <v>32</v>
       </c>
@@ -24910,7 +24836,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="42" spans="1:43" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:43" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A42" s="29" t="s">
         <v>32</v>
       </c>
@@ -24934,7 +24860,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="43" spans="1:43" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:43" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A43" s="29" t="s">
         <v>32</v>
       </c>
@@ -24960,7 +24886,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="44" spans="1:43" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:43" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A44" s="29" t="s">
         <v>52</v>
       </c>
@@ -24986,7 +24912,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="45" spans="1:43" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:43" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A45" s="29" t="s">
         <v>52</v>
       </c>
@@ -25012,7 +24938,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="46" spans="1:43" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:43" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A46" s="29" t="s">
         <v>52</v>
       </c>
@@ -25038,7 +24964,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="47" spans="1:43" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:43" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A47" s="29" t="s">
         <v>52</v>
       </c>
@@ -25061,7 +24987,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="48" spans="1:43" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:43" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A48" s="29" t="s">
         <v>52</v>
       </c>
@@ -25087,7 +25013,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="49" spans="1:8" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:8" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A49" s="29" t="s">
         <v>52</v>
       </c>
@@ -25113,7 +25039,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="50" spans="1:8" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:8" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A50" s="29" t="s">
         <v>52</v>
       </c>
@@ -25139,7 +25065,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="51" spans="1:8" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:8" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A51" s="29" t="s">
         <v>52</v>
       </c>
@@ -25165,7 +25091,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="52" spans="1:8" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:8" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A52" s="29" t="s">
         <v>52</v>
       </c>
@@ -25191,7 +25117,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="53" spans="1:8" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:8" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A53" s="29" t="s">
         <v>52</v>
       </c>
@@ -25215,7 +25141,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="54" spans="1:8" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:8" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A54" s="29" t="s">
         <v>52</v>
       </c>
@@ -25241,7 +25167,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="55" spans="1:8" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:8" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A55" s="29" t="s">
         <v>52</v>
       </c>
@@ -25267,7 +25193,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="56" spans="1:8" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:8" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A56" s="29" t="s">
         <v>60</v>
       </c>
@@ -25293,7 +25219,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="57" spans="1:8" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:8" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A57" s="29" t="s">
         <v>60</v>
       </c>
@@ -25316,7 +25242,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="58" spans="1:8" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:8" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A58" s="29" t="s">
         <v>60</v>
       </c>
@@ -25342,7 +25268,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="59" spans="1:8" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:8" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A59" s="29" t="s">
         <v>60</v>
       </c>
@@ -25368,7 +25294,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="60" spans="1:8" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:8" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A60" s="29" t="s">
         <v>60</v>
       </c>
@@ -25394,7 +25320,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="61" spans="1:8" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:8" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A61" s="29" t="s">
         <v>60</v>
       </c>
@@ -25420,7 +25346,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="62" spans="1:8" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:8" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A62" s="29" t="s">
         <v>60</v>
       </c>
@@ -25446,7 +25372,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="63" spans="1:8" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:8" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A63" s="29" t="s">
         <v>60</v>
       </c>
@@ -25472,7 +25398,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="64" spans="1:8" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:8" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A64" s="29" t="s">
         <v>60</v>
       </c>
@@ -25498,7 +25424,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="65" spans="1:8" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:8" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A65" s="29" t="s">
         <v>67</v>
       </c>
@@ -25522,7 +25448,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="66" spans="1:8" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:8" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A66" s="29" t="s">
         <v>67</v>
       </c>
@@ -25548,7 +25474,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="67" spans="1:8" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:8" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A67" s="29" t="s">
         <v>67</v>
       </c>
@@ -25572,7 +25498,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="68" spans="1:8" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:8" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A68" s="29" t="s">
         <v>67</v>
       </c>
@@ -25598,7 +25524,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="69" spans="1:8" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:8" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A69" s="29" t="s">
         <v>67</v>
       </c>
@@ -25624,7 +25550,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="70" spans="1:8" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:8" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A70" s="29" t="s">
         <v>67</v>
       </c>
@@ -25650,7 +25576,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="71" spans="1:8" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:8" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A71" s="29" t="s">
         <v>67</v>
       </c>
@@ -25676,7 +25602,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="72" spans="1:8" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:8" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A72" s="29" t="s">
         <v>24</v>
       </c>
@@ -25699,7 +25625,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="73" spans="1:8" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:8" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A73" s="29" t="s">
         <v>24</v>
       </c>
@@ -25725,7 +25651,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="74" spans="1:8" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:8" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A74" s="29" t="s">
         <v>24</v>
       </c>
@@ -25751,7 +25677,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="75" spans="1:8" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="75" spans="1:8" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A75" s="29" t="s">
         <v>24</v>
       </c>
@@ -25777,7 +25703,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="76" spans="1:8" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="76" spans="1:8" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A76" s="29" t="s">
         <v>24</v>
       </c>
@@ -25803,7 +25729,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="77" spans="1:8" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="77" spans="1:8" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A77" s="29" t="s">
         <v>24</v>
       </c>
@@ -25829,7 +25755,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="78" spans="1:8" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="78" spans="1:8" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A78" s="29" t="s">
         <v>28</v>
       </c>
@@ -25855,7 +25781,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="79" spans="1:8" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="79" spans="1:8" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A79" s="29" t="s">
         <v>28</v>
       </c>
@@ -25879,7 +25805,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="80" spans="1:8" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="80" spans="1:8" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A80" s="29" t="s">
         <v>32</v>
       </c>
@@ -25905,7 +25831,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="81" spans="1:8" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="81" spans="1:8" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A81" s="29" t="s">
         <v>32</v>
       </c>
@@ -25929,7 +25855,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="82" spans="1:8" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="82" spans="1:8" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A82" s="29" t="s">
         <v>15</v>
       </c>
@@ -25952,7 +25878,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="83" spans="1:8" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="83" spans="1:8" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A83" s="29" t="s">
         <v>15</v>
       </c>
@@ -25978,7 +25904,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="84" spans="1:8" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="84" spans="1:8" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A84" s="29" t="s">
         <v>15</v>
       </c>
@@ -26004,7 +25930,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="85" spans="1:8" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="85" spans="1:8" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A85" s="29" t="s">
         <v>15</v>
       </c>
@@ -26030,7 +25956,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="86" spans="1:8" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="86" spans="1:8" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A86" s="29" t="s">
         <v>15</v>
       </c>
@@ -26054,7 +25980,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="87" spans="1:8" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="87" spans="1:8" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A87" s="29" t="s">
         <v>15</v>
       </c>
@@ -26080,7 +26006,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="88" spans="1:8" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="88" spans="1:8" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A88" s="29" t="s">
         <v>15</v>
       </c>
@@ -26106,7 +26032,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="89" spans="1:8" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="89" spans="1:8" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A89" s="29" t="s">
         <v>28</v>
       </c>
@@ -26132,7 +26058,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="90" spans="1:8" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="90" spans="1:8" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A90" s="29" t="s">
         <v>28</v>
       </c>
@@ -26158,7 +26084,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="91" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="91" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A91" s="29" t="s">
         <v>28</v>
       </c>
@@ -26181,7 +26107,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="92" spans="1:8" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="92" spans="1:8" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A92" s="29" t="s">
         <v>32</v>
       </c>
@@ -26207,7 +26133,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="93" spans="1:8" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="93" spans="1:8" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A93" s="29" t="s">
         <v>32</v>
       </c>
@@ -26233,7 +26159,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="94" spans="1:8" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="94" spans="1:8" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A94" s="29" t="s">
         <v>32</v>
       </c>
@@ -26257,7 +26183,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="95" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="95" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A95" s="51" t="s">
         <v>52</v>
       </c>
@@ -26279,7 +26205,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="96" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="96" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A96" s="51" t="s">
         <v>52</v>
       </c>
@@ -26303,7 +26229,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="97" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="97" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A97" s="51" t="s">
         <v>52</v>
       </c>
@@ -26329,7 +26255,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="98" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="98" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A98" s="51" t="s">
         <v>52</v>
       </c>
@@ -26353,7 +26279,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="99" spans="1:8" ht="29.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="99" spans="1:8" ht="29.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A99" s="51" t="s">
         <v>52</v>
       </c>
@@ -26377,7 +26303,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="100" spans="1:8" ht="44" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="100" spans="1:8" ht="43.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A100" s="51" t="s">
         <v>52</v>
       </c>
@@ -26401,7 +26327,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="101" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="101" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A101" s="51" t="s">
         <v>60</v>
       </c>
@@ -26425,7 +26351,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="102" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="102" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A102" s="51" t="s">
         <v>60</v>
       </c>
@@ -26449,7 +26375,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="103" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="103" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A103" s="51" t="s">
         <v>60</v>
       </c>
@@ -26473,7 +26399,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="104" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="104" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A104" s="51" t="s">
         <v>60</v>
       </c>
@@ -26497,7 +26423,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="105" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="105" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A105" s="51" t="s">
         <v>60</v>
       </c>
@@ -26523,7 +26449,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="106" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="106" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A106" s="51" t="s">
         <v>60</v>
       </c>
@@ -26549,7 +26475,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="107" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="107" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A107" s="51" t="s">
         <v>60</v>
       </c>
@@ -26575,7 +26501,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="108" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="108" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A108" s="51" t="s">
         <v>60</v>
       </c>
@@ -26599,7 +26525,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="109" spans="1:8" ht="29.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="109" spans="1:8" ht="29.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A109" s="51" t="s">
         <v>60</v>
       </c>
@@ -26623,7 +26549,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="110" spans="1:8" ht="29.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="110" spans="1:8" ht="29.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A110" s="51" t="s">
         <v>60</v>
       </c>
@@ -26649,7 +26575,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="111" spans="1:8" ht="29.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="111" spans="1:8" ht="29.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A111" s="51" t="s">
         <v>60</v>
       </c>
@@ -26673,7 +26599,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="112" spans="1:8" ht="29.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="112" spans="1:8" ht="29.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A112" s="51" t="s">
         <v>67</v>
       </c>
@@ -26697,7 +26623,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="113" spans="1:8" ht="29.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="113" spans="1:8" ht="29.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A113" s="51" t="s">
         <v>67</v>
       </c>
@@ -26721,7 +26647,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="114" spans="1:8" ht="29.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="114" spans="1:8" ht="29.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A114" s="51" t="s">
         <v>67</v>
       </c>
@@ -26745,7 +26671,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="115" spans="1:8" ht="29.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="115" spans="1:8" ht="29.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A115" s="51" t="s">
         <v>67</v>
       </c>
@@ -26771,7 +26697,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="116" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="116" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A116" s="51" t="s">
         <v>24</v>
       </c>
@@ -26795,7 +26721,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="117" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="117" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A117" s="51" t="s">
         <v>24</v>
       </c>
@@ -26819,7 +26745,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="118" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="118" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A118" s="51" t="s">
         <v>24</v>
       </c>
@@ -26845,7 +26771,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="119" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="119" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A119" s="51" t="s">
         <v>24</v>
       </c>
@@ -26869,7 +26795,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="120" spans="1:8" ht="29.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="120" spans="1:8" ht="29.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A120" s="51" t="s">
         <v>24</v>
       </c>
@@ -26893,7 +26819,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="121" spans="1:8" ht="29.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="121" spans="1:8" ht="29.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A121" s="51" t="s">
         <v>24</v>
       </c>
@@ -26919,7 +26845,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="122" spans="1:8" ht="29.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="122" spans="1:8" ht="29.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A122" s="51" t="s">
         <v>24</v>
       </c>
@@ -26943,7 +26869,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="123" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="123" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A123" s="51" t="s">
         <v>28</v>
       </c>
@@ -26967,7 +26893,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="124" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="124" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A124" s="51" t="s">
         <v>28</v>
       </c>
@@ -26993,7 +26919,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="125" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="125" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A125" s="51" t="s">
         <v>28</v>
       </c>
@@ -27017,7 +26943,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="126" spans="1:8" ht="29.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="126" spans="1:8" ht="29.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A126" s="51" t="s">
         <v>28</v>
       </c>
@@ -27041,7 +26967,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="127" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="127" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A127" s="51" t="s">
         <v>32</v>
       </c>
@@ -27065,7 +26991,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="128" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="128" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A128" s="51" t="s">
         <v>32</v>
       </c>
@@ -27089,7 +27015,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="129" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="129" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A129" s="51" t="s">
         <v>32</v>
       </c>
@@ -27113,7 +27039,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="130" spans="1:9" ht="29.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="130" spans="1:9" ht="29.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A130" s="51" t="s">
         <v>32</v>
       </c>
@@ -27137,7 +27063,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="131" spans="1:9" ht="29.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="131" spans="1:9" ht="29.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A131" s="51" t="s">
         <v>32</v>
       </c>
@@ -27161,7 +27087,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="132" spans="1:9" ht="29.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="132" spans="1:9" ht="29.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A132" s="51" t="s">
         <v>15</v>
       </c>
@@ -27185,7 +27111,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="133" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="133" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A133" s="51" t="s">
         <v>15</v>
       </c>
@@ -27211,7 +27137,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="134" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="134" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A134" s="51" t="s">
         <v>15</v>
       </c>
@@ -27237,7 +27163,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="135" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="135" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A135" s="51" t="s">
         <v>15</v>
       </c>
@@ -27261,7 +27187,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="136" spans="1:9" ht="29.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="136" spans="1:9" ht="29.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A136" s="51" t="s">
         <v>15</v>
       </c>
@@ -27285,7 +27211,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="137" spans="1:9" ht="29.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="137" spans="1:9" ht="29.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A137" s="51" t="s">
         <v>15</v>
       </c>
@@ -27311,7 +27237,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="138" spans="1:9" ht="29.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="138" spans="1:9" ht="29.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A138" s="51" t="s">
         <v>15</v>
       </c>
@@ -27335,7 +27261,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="139" spans="1:9" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="139" spans="1:9" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A139" s="29" t="s">
         <v>52</v>
       </c>
@@ -27361,7 +27287,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="140" spans="1:9" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="140" spans="1:9" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A140" s="29" t="s">
         <v>52</v>
       </c>
@@ -27387,7 +27313,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="141" spans="1:9" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="141" spans="1:9" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A141" s="29" t="s">
         <v>52</v>
       </c>
@@ -27411,7 +27337,7 @@
       </c>
       <c r="I141" s="30"/>
     </row>
-    <row r="142" spans="1:9" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="142" spans="1:9" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A142" s="29" t="s">
         <v>52</v>
       </c>
@@ -27437,7 +27363,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="143" spans="1:9" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="143" spans="1:9" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A143" s="29" t="s">
         <v>52</v>
       </c>
@@ -27463,7 +27389,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="144" spans="1:9" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="144" spans="1:9" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A144" s="29" t="s">
         <v>52</v>
       </c>
@@ -27489,7 +27415,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="145" spans="1:8" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="145" spans="1:8" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A145" s="29" t="s">
         <v>52</v>
       </c>
@@ -27515,7 +27441,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="146" spans="1:8" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="146" spans="1:8" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A146" s="29" t="s">
         <v>52</v>
       </c>
@@ -27541,7 +27467,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="147" spans="1:8" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="147" spans="1:8" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A147" s="29" t="s">
         <v>52</v>
       </c>
@@ -27567,7 +27493,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="148" spans="1:8" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="148" spans="1:8" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A148" s="29" t="s">
         <v>52</v>
       </c>
@@ -27593,7 +27519,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="149" spans="1:8" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="149" spans="1:8" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A149" s="29" t="s">
         <v>60</v>
       </c>
@@ -27619,7 +27545,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="150" spans="1:8" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="150" spans="1:8" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A150" s="29" t="s">
         <v>60</v>
       </c>
@@ -27645,7 +27571,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="151" spans="1:8" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="151" spans="1:8" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A151" s="29" t="s">
         <v>60</v>
       </c>
@@ -27671,7 +27597,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="152" spans="1:8" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="152" spans="1:8" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A152" s="29" t="s">
         <v>60</v>
       </c>
@@ -27697,7 +27623,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="153" spans="1:8" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="153" spans="1:8" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A153" s="29" t="s">
         <v>60</v>
       </c>
@@ -27723,7 +27649,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="154" spans="1:8" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="154" spans="1:8" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A154" s="29" t="s">
         <v>60</v>
       </c>
@@ -27749,7 +27675,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="155" spans="1:8" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="155" spans="1:8" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A155" s="29" t="s">
         <v>60</v>
       </c>
@@ -27775,7 +27701,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="156" spans="1:8" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="156" spans="1:8" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A156" s="29" t="s">
         <v>60</v>
       </c>
@@ -27801,7 +27727,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="157" spans="1:8" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="157" spans="1:8" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A157" s="29" t="s">
         <v>60</v>
       </c>
@@ -27827,7 +27753,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="158" spans="1:8" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="158" spans="1:8" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A158" s="29" t="s">
         <v>60</v>
       </c>
@@ -27853,7 +27779,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="159" spans="1:8" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="159" spans="1:8" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A159" s="29" t="s">
         <v>60</v>
       </c>
@@ -27879,7 +27805,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="160" spans="1:8" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="160" spans="1:8" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A160" s="29" t="s">
         <v>15</v>
       </c>
@@ -27905,7 +27831,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="161" spans="1:9" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="161" spans="1:9" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A161" s="29" t="s">
         <v>15</v>
       </c>
@@ -27931,7 +27857,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="162" spans="1:9" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="162" spans="1:9" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A162" s="29" t="s">
         <v>15</v>
       </c>
@@ -27958,7 +27884,7 @@
       </c>
       <c r="I162" s="30"/>
     </row>
-    <row r="163" spans="1:9" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="163" spans="1:9" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A163" s="29" t="s">
         <v>15</v>
       </c>
@@ -27984,7 +27910,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="164" spans="1:9" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="164" spans="1:9" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A164" s="29" t="s">
         <v>15</v>
       </c>
@@ -28010,7 +27936,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="165" spans="1:9" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="165" spans="1:9" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A165" s="29" t="s">
         <v>15</v>
       </c>
@@ -28037,7 +27963,7 @@
       </c>
       <c r="I165" s="30"/>
     </row>
-    <row r="166" spans="1:9" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="166" spans="1:9" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A166" s="29" t="s">
         <v>15</v>
       </c>
@@ -28063,7 +27989,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="167" spans="1:9" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="167" spans="1:9" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A167" s="29" t="s">
         <v>15</v>
       </c>
@@ -28089,7 +28015,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="168" spans="1:9" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="168" spans="1:9" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A168" s="29" t="s">
         <v>15</v>
       </c>
@@ -28115,7 +28041,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="169" spans="1:9" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="169" spans="1:9" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A169" s="29" t="s">
         <v>67</v>
       </c>
@@ -28141,7 +28067,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="170" spans="1:9" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="170" spans="1:9" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A170" s="29" t="s">
         <v>67</v>
       </c>
@@ -28167,7 +28093,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="171" spans="1:9" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="171" spans="1:9" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A171" s="29" t="s">
         <v>67</v>
       </c>
@@ -28193,7 +28119,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="172" spans="1:9" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="172" spans="1:9" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A172" s="29" t="s">
         <v>67</v>
       </c>
@@ -28219,7 +28145,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="173" spans="1:9" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="173" spans="1:9" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A173" s="29" t="s">
         <v>67</v>
       </c>
@@ -28245,7 +28171,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="174" spans="1:9" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="174" spans="1:9" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A174" s="29" t="s">
         <v>67</v>
       </c>
@@ -28271,7 +28197,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="175" spans="1:9" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="175" spans="1:9" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A175" s="29" t="s">
         <v>24</v>
       </c>
@@ -28297,7 +28223,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="176" spans="1:9" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="176" spans="1:9" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A176" s="29" t="s">
         <v>24</v>
       </c>
@@ -28323,7 +28249,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="177" spans="1:8" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="177" spans="1:8" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A177" s="29" t="s">
         <v>24</v>
       </c>
@@ -28349,7 +28275,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="178" spans="1:8" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="178" spans="1:8" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A178" s="29" t="s">
         <v>24</v>
       </c>
@@ -28375,7 +28301,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="179" spans="1:8" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="179" spans="1:8" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A179" s="29" t="s">
         <v>24</v>
       </c>
@@ -28401,7 +28327,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="180" spans="1:8" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="180" spans="1:8" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A180" s="29" t="s">
         <v>24</v>
       </c>
@@ -28427,7 +28353,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="181" spans="1:8" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="181" spans="1:8" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A181" s="29" t="s">
         <v>24</v>
       </c>
@@ -28453,7 +28379,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="182" spans="1:8" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="182" spans="1:8" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A182" s="29" t="s">
         <v>24</v>
       </c>
@@ -28479,7 +28405,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="183" spans="1:8" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="183" spans="1:8" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A183" s="29" t="s">
         <v>24</v>
       </c>
@@ -28505,7 +28431,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="184" spans="1:8" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="184" spans="1:8" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A184" s="29" t="s">
         <v>28</v>
       </c>
@@ -28531,7 +28457,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="185" spans="1:8" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="185" spans="1:8" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A185" s="29" t="s">
         <v>28</v>
       </c>
@@ -28557,7 +28483,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="186" spans="1:8" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="186" spans="1:8" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A186" s="29" t="s">
         <v>28</v>
       </c>
@@ -28583,7 +28509,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="187" spans="1:8" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="187" spans="1:8" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A187" s="29" t="s">
         <v>28</v>
       </c>
@@ -28609,7 +28535,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="188" spans="1:8" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="188" spans="1:8" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A188" s="29" t="s">
         <v>28</v>
       </c>
@@ -28635,7 +28561,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="189" spans="1:8" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="189" spans="1:8" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A189" s="29" t="s">
         <v>28</v>
       </c>
@@ -28661,7 +28587,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="190" spans="1:8" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="190" spans="1:8" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A190" s="29" t="s">
         <v>32</v>
       </c>
@@ -28687,7 +28613,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="191" spans="1:8" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="191" spans="1:8" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A191" s="29" t="s">
         <v>32</v>
       </c>
@@ -28713,7 +28639,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="192" spans="1:8" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="192" spans="1:8" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A192" s="29" t="s">
         <v>32</v>
       </c>
@@ -28739,7 +28665,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="193" spans="1:8" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="193" spans="1:8" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A193" s="29" t="s">
         <v>32</v>
       </c>
@@ -28765,7 +28691,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="194" spans="1:8" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="194" spans="1:8" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A194" s="29" t="s">
         <v>32</v>
       </c>
@@ -28789,7 +28715,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="195" spans="1:8" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="195" spans="1:8" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A195" s="29" t="s">
         <v>52</v>
       </c>
@@ -28815,7 +28741,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="196" spans="1:8" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="196" spans="1:8" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A196" s="29" t="s">
         <v>52</v>
       </c>
@@ -28841,7 +28767,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="197" spans="1:8" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="197" spans="1:8" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A197" s="29" t="s">
         <v>15</v>
       </c>
@@ -28867,7 +28793,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="198" spans="1:8" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="198" spans="1:8" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A198" s="29" t="s">
         <v>15</v>
       </c>
@@ -28893,7 +28819,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="199" spans="1:8" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="199" spans="1:8" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A199" s="29" t="s">
         <v>60</v>
       </c>
@@ -28919,7 +28845,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="200" spans="1:8" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="200" spans="1:8" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A200" s="29" t="s">
         <v>60</v>
       </c>
@@ -28945,7 +28871,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="201" spans="1:8" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="201" spans="1:8" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A201" s="29" t="s">
         <v>60</v>
       </c>
@@ -28971,7 +28897,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="202" spans="1:8" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="202" spans="1:8" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A202" s="29" t="s">
         <v>60</v>
       </c>
@@ -28997,7 +28923,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="203" spans="1:8" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="203" spans="1:8" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A203" s="29" t="s">
         <v>15</v>
       </c>
@@ -29023,7 +28949,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="204" spans="1:8" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="204" spans="1:8" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A204" s="29" t="s">
         <v>15</v>
       </c>
@@ -29049,7 +28975,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="205" spans="1:8" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="205" spans="1:8" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A205" s="29" t="s">
         <v>15</v>
       </c>
@@ -29075,7 +29001,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="206" spans="1:8" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="206" spans="1:8" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A206" s="29" t="s">
         <v>67</v>
       </c>
@@ -29101,7 +29027,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="207" spans="1:8" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="207" spans="1:8" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A207" s="29" t="s">
         <v>24</v>
       </c>
@@ -29127,7 +29053,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="208" spans="1:8" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="208" spans="1:8" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A208" s="29" t="s">
         <v>24</v>
       </c>
@@ -29153,7 +29079,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="209" spans="1:8" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="209" spans="1:8" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A209" s="29" t="s">
         <v>28</v>
       </c>
@@ -29179,7 +29105,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="210" spans="1:8" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="210" spans="1:8" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A210" s="29" t="s">
         <v>52</v>
       </c>
@@ -29205,7 +29131,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="211" spans="1:8" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="211" spans="1:8" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A211" s="29" t="s">
         <v>52</v>
       </c>
@@ -29231,7 +29157,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="212" spans="1:8" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="212" spans="1:8" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A212" s="29" t="s">
         <v>52</v>
       </c>
@@ -29251,7 +29177,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="213" spans="1:8" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="213" spans="1:8" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A213" s="29" t="s">
         <v>52</v>
       </c>
@@ -29277,7 +29203,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="214" spans="1:8" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="214" spans="1:8" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A214" s="29" t="s">
         <v>52</v>
       </c>
@@ -29303,7 +29229,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="215" spans="1:8" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="215" spans="1:8" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A215" s="29" t="s">
         <v>52</v>
       </c>
@@ -29329,7 +29255,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="216" spans="1:8" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="216" spans="1:8" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A216" s="29" t="s">
         <v>60</v>
       </c>
@@ -29355,7 +29281,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="217" spans="1:8" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="217" spans="1:8" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A217" s="29" t="s">
         <v>60</v>
       </c>
@@ -29381,7 +29307,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="218" spans="1:8" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="218" spans="1:8" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A218" s="29" t="s">
         <v>60</v>
       </c>
@@ -29407,7 +29333,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="219" spans="1:8" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="219" spans="1:8" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A219" s="29" t="s">
         <v>60</v>
       </c>
@@ -29433,7 +29359,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="220" spans="1:8" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="220" spans="1:8" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A220" s="29" t="s">
         <v>60</v>
       </c>
@@ -29459,7 +29385,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="221" spans="1:8" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="221" spans="1:8" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A221" s="29" t="s">
         <v>60</v>
       </c>
@@ -29485,7 +29411,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="222" spans="1:8" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="222" spans="1:8" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A222" s="29" t="s">
         <v>15</v>
       </c>
@@ -29511,7 +29437,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="223" spans="1:8" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="223" spans="1:8" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A223" s="29" t="s">
         <v>15</v>
       </c>
@@ -29534,7 +29460,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="224" spans="1:8" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="224" spans="1:8" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A224" s="29" t="s">
         <v>15</v>
       </c>
@@ -29557,7 +29483,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="225" spans="1:8" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="225" spans="1:8" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A225" s="29" t="s">
         <v>67</v>
       </c>
@@ -29583,7 +29509,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="226" spans="1:8" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="226" spans="1:8" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A226" s="29" t="s">
         <v>67</v>
       </c>
@@ -29609,7 +29535,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="227" spans="1:8" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="227" spans="1:8" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A227" s="29" t="s">
         <v>67</v>
       </c>
@@ -29635,7 +29561,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="228" spans="1:8" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="228" spans="1:8" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A228" s="29" t="s">
         <v>67</v>
       </c>
@@ -29661,7 +29587,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="229" spans="1:8" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="229" spans="1:8" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A229" s="29" t="s">
         <v>67</v>
       </c>
@@ -29687,7 +29613,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="230" spans="1:8" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="230" spans="1:8" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A230" s="29" t="s">
         <v>24</v>
       </c>
@@ -29713,7 +29639,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="231" spans="1:8" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="231" spans="1:8" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A231" s="29" t="s">
         <v>24</v>
       </c>
@@ -29739,7 +29665,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="232" spans="1:8" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="232" spans="1:8" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A232" s="29" t="s">
         <v>24</v>
       </c>
@@ -29765,7 +29691,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="233" spans="1:8" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="233" spans="1:8" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A233" s="29" t="s">
         <v>24</v>
       </c>
@@ -29791,7 +29717,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="234" spans="1:8" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="234" spans="1:8" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A234" s="29" t="s">
         <v>28</v>
       </c>
@@ -29817,7 +29743,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="235" spans="1:8" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="235" spans="1:8" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A235" s="29" t="s">
         <v>28</v>
       </c>
@@ -29843,7 +29769,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="236" spans="1:8" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="236" spans="1:8" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A236" s="29" t="s">
         <v>28</v>
       </c>
@@ -29863,7 +29789,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="237" spans="1:8" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="237" spans="1:8" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A237" s="29" t="s">
         <v>28</v>
       </c>
@@ -29889,7 +29815,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="238" spans="1:8" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="238" spans="1:8" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A238" s="29" t="s">
         <v>28</v>
       </c>
@@ -29915,7 +29841,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="239" spans="1:8" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="239" spans="1:8" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A239" s="29" t="s">
         <v>32</v>
       </c>
@@ -29941,7 +29867,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="240" spans="1:8" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="240" spans="1:8" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A240" s="29" t="s">
         <v>32</v>
       </c>
@@ -29967,7 +29893,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="241" spans="1:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="241" spans="1:11" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A241" s="29" t="s">
         <v>32</v>
       </c>
@@ -29993,7 +29919,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="242" spans="1:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="242" spans="1:11" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A242" s="29" t="s">
         <v>32</v>
       </c>
@@ -30013,7 +29939,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="243" spans="1:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="243" spans="1:11" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A243" s="29" t="s">
         <v>32</v>
       </c>
@@ -30039,7 +29965,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="244" spans="1:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="244" spans="1:11" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A244" s="29" t="s">
         <v>52</v>
       </c>
@@ -30065,7 +29991,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="245" spans="1:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="245" spans="1:11" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A245" s="29" t="s">
         <v>32</v>
       </c>
@@ -30088,7 +30014,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="246" spans="1:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="246" spans="1:11" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A246" s="29" t="s">
         <v>52</v>
       </c>
@@ -30115,7 +30041,7 @@
       </c>
       <c r="K246" s="7"/>
     </row>
-    <row r="247" spans="1:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="247" spans="1:11" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A247" s="29" t="s">
         <v>52</v>
       </c>
@@ -30137,7 +30063,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="248" spans="1:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="248" spans="1:11" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A248" s="29" t="s">
         <v>60</v>
       </c>
@@ -30164,7 +30090,7 @@
       </c>
       <c r="K248" s="7"/>
     </row>
-    <row r="249" spans="1:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="249" spans="1:11" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A249" s="29" t="s">
         <v>60</v>
       </c>
@@ -30191,7 +30117,7 @@
       </c>
       <c r="K249" s="7"/>
     </row>
-    <row r="250" spans="1:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="250" spans="1:11" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A250" s="29" t="s">
         <v>60</v>
       </c>
@@ -30218,7 +30144,7 @@
       </c>
       <c r="K250" s="7"/>
     </row>
-    <row r="251" spans="1:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="251" spans="1:11" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A251" s="29" t="s">
         <v>60</v>
       </c>
@@ -30245,7 +30171,7 @@
       </c>
       <c r="K251" s="7"/>
     </row>
-    <row r="252" spans="1:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="252" spans="1:11" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A252" s="29" t="s">
         <v>15</v>
       </c>
@@ -30272,7 +30198,7 @@
       </c>
       <c r="K252" s="7"/>
     </row>
-    <row r="253" spans="1:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="253" spans="1:11" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A253" s="29" t="s">
         <v>15</v>
       </c>
@@ -30299,7 +30225,7 @@
       </c>
       <c r="K253" s="7"/>
     </row>
-    <row r="254" spans="1:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="254" spans="1:11" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A254" s="29" t="s">
         <v>15</v>
       </c>
@@ -30326,7 +30252,7 @@
       </c>
       <c r="K254" s="7"/>
     </row>
-    <row r="255" spans="1:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="255" spans="1:11" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A255" s="29" t="s">
         <v>67</v>
       </c>
@@ -30353,7 +30279,7 @@
       </c>
       <c r="K255" s="7"/>
     </row>
-    <row r="256" spans="1:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="256" spans="1:11" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A256" s="29" t="s">
         <v>24</v>
       </c>
@@ -30380,7 +30306,7 @@
       </c>
       <c r="K256" s="7"/>
     </row>
-    <row r="257" spans="1:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="257" spans="1:11" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A257" s="29" t="s">
         <v>24</v>
       </c>
@@ -30407,7 +30333,7 @@
       </c>
       <c r="K257" s="7"/>
     </row>
-    <row r="258" spans="1:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="258" spans="1:11" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A258" s="29" t="s">
         <v>24</v>
       </c>
@@ -30434,7 +30360,7 @@
       </c>
       <c r="K258" s="7"/>
     </row>
-    <row r="259" spans="1:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="259" spans="1:11" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A259" s="29" t="s">
         <v>28</v>
       </c>
@@ -30461,7 +30387,7 @@
       </c>
       <c r="K259" s="7"/>
     </row>
-    <row r="260" spans="1:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="260" spans="1:11" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A260" s="29" t="s">
         <v>32</v>
       </c>
@@ -30486,7 +30412,7 @@
       </c>
       <c r="K260" s="7"/>
     </row>
-    <row r="261" spans="1:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="261" spans="1:11" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A261" s="29" t="s">
         <v>52</v>
       </c>
@@ -30513,7 +30439,7 @@
       </c>
       <c r="K261" s="7"/>
     </row>
-    <row r="262" spans="1:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="262" spans="1:11" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A262" s="29" t="s">
         <v>52</v>
       </c>
@@ -30540,7 +30466,7 @@
       </c>
       <c r="K262" s="7"/>
     </row>
-    <row r="263" spans="1:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="263" spans="1:11" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A263" s="29" t="s">
         <v>52</v>
       </c>
@@ -30567,7 +30493,7 @@
       </c>
       <c r="K263" s="7"/>
     </row>
-    <row r="264" spans="1:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="264" spans="1:11" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A264" s="29" t="s">
         <v>52</v>
       </c>
@@ -30594,7 +30520,7 @@
       </c>
       <c r="K264" s="7"/>
     </row>
-    <row r="265" spans="1:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="265" spans="1:11" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A265" s="29" t="s">
         <v>52</v>
       </c>
@@ -30616,7 +30542,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="266" spans="1:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="266" spans="1:11" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A266" s="29" t="s">
         <v>52</v>
       </c>
@@ -30643,7 +30569,7 @@
       </c>
       <c r="K266" s="7"/>
     </row>
-    <row r="267" spans="1:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="267" spans="1:11" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A267" s="29" t="s">
         <v>52</v>
       </c>
@@ -30670,7 +30596,7 @@
       </c>
       <c r="K267" s="7"/>
     </row>
-    <row r="268" spans="1:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="268" spans="1:11" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A268" s="29" t="s">
         <v>52</v>
       </c>
@@ -30696,7 +30622,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="269" spans="1:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="269" spans="1:11" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A269" s="29" t="s">
         <v>52</v>
       </c>
@@ -30723,7 +30649,7 @@
       </c>
       <c r="K269" s="7"/>
     </row>
-    <row r="270" spans="1:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="270" spans="1:11" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A270" s="29" t="s">
         <v>52</v>
       </c>
@@ -30742,7 +30668,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="271" spans="1:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="271" spans="1:11" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A271" s="29" t="s">
         <v>52</v>
       </c>
@@ -30764,7 +30690,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="272" spans="1:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="272" spans="1:11" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A272" s="29" t="s">
         <v>60</v>
       </c>
@@ -30791,7 +30717,7 @@
       </c>
       <c r="K272" s="7"/>
     </row>
-    <row r="273" spans="1:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="273" spans="1:11" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A273" s="29" t="s">
         <v>60</v>
       </c>
@@ -30818,7 +30744,7 @@
       </c>
       <c r="K273" s="7"/>
     </row>
-    <row r="274" spans="1:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="274" spans="1:11" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A274" s="29" t="s">
         <v>60</v>
       </c>
@@ -30845,7 +30771,7 @@
       </c>
       <c r="K274" s="7"/>
     </row>
-    <row r="275" spans="1:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="275" spans="1:11" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A275" s="29" t="s">
         <v>60</v>
       </c>
@@ -30872,7 +30798,7 @@
       </c>
       <c r="K275" s="7"/>
     </row>
-    <row r="276" spans="1:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="276" spans="1:11" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A276" s="29" t="s">
         <v>60</v>
       </c>
@@ -30899,7 +30825,7 @@
       </c>
       <c r="K276" s="7"/>
     </row>
-    <row r="277" spans="1:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="277" spans="1:11" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A277" s="29" t="s">
         <v>60</v>
       </c>
@@ -30926,7 +30852,7 @@
       </c>
       <c r="K277" s="7"/>
     </row>
-    <row r="278" spans="1:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="278" spans="1:11" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A278" s="29" t="s">
         <v>60</v>
       </c>
@@ -30953,7 +30879,7 @@
       </c>
       <c r="K278" s="7"/>
     </row>
-    <row r="279" spans="1:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="279" spans="1:11" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A279" s="29" t="s">
         <v>15</v>
       </c>
@@ -30972,7 +30898,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="280" spans="1:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="280" spans="1:11" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A280" s="29" t="s">
         <v>15</v>
       </c>
@@ -30999,7 +30925,7 @@
       </c>
       <c r="K280" s="7"/>
     </row>
-    <row r="281" spans="1:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="281" spans="1:11" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A281" s="29" t="s">
         <v>15</v>
       </c>
@@ -31021,7 +30947,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="282" spans="1:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="282" spans="1:11" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A282" s="29" t="s">
         <v>15</v>
       </c>
@@ -31048,7 +30974,7 @@
       </c>
       <c r="K282" s="7"/>
     </row>
-    <row r="283" spans="1:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="283" spans="1:11" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A283" s="29" t="s">
         <v>15</v>
       </c>
@@ -31075,7 +31001,7 @@
       </c>
       <c r="K283" s="7"/>
     </row>
-    <row r="284" spans="1:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="284" spans="1:11" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A284" s="29" t="s">
         <v>15</v>
       </c>
@@ -31097,7 +31023,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="285" spans="1:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="285" spans="1:11" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A285" s="29" t="s">
         <v>15</v>
       </c>
@@ -31124,7 +31050,7 @@
       </c>
       <c r="K285" s="7"/>
     </row>
-    <row r="286" spans="1:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="286" spans="1:11" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A286" s="29" t="s">
         <v>67</v>
       </c>
@@ -31151,7 +31077,7 @@
       </c>
       <c r="K286" s="7"/>
     </row>
-    <row r="287" spans="1:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="287" spans="1:11" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A287" s="29" t="s">
         <v>67</v>
       </c>
@@ -31178,7 +31104,7 @@
       </c>
       <c r="K287" s="7"/>
     </row>
-    <row r="288" spans="1:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="288" spans="1:11" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A288" s="29" t="s">
         <v>67</v>
       </c>
@@ -31205,7 +31131,7 @@
       </c>
       <c r="K288" s="7"/>
     </row>
-    <row r="289" spans="1:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="289" spans="1:11" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A289" s="29" t="s">
         <v>67</v>
       </c>
@@ -31224,7 +31150,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="290" spans="1:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="290" spans="1:11" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A290" s="29" t="s">
         <v>67</v>
       </c>
@@ -31243,7 +31169,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="291" spans="1:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="291" spans="1:11" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A291" s="29" t="s">
         <v>67</v>
       </c>
@@ -31270,7 +31196,7 @@
       </c>
       <c r="K291" s="7"/>
     </row>
-    <row r="292" spans="1:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="292" spans="1:11" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A292" s="29" t="s">
         <v>67</v>
       </c>
@@ -31297,7 +31223,7 @@
       </c>
       <c r="K292" s="7"/>
     </row>
-    <row r="293" spans="1:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="293" spans="1:11" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A293" s="29" t="s">
         <v>24</v>
       </c>
@@ -31324,7 +31250,7 @@
       </c>
       <c r="K293" s="7"/>
     </row>
-    <row r="294" spans="1:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="294" spans="1:11" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A294" s="29" t="s">
         <v>24</v>
       </c>
@@ -31351,7 +31277,7 @@
       </c>
       <c r="K294" s="7"/>
     </row>
-    <row r="295" spans="1:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="295" spans="1:11" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A295" s="29" t="s">
         <v>24</v>
       </c>
@@ -31373,7 +31299,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="296" spans="1:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="296" spans="1:11" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A296" s="29" t="s">
         <v>24</v>
       </c>
@@ -31400,7 +31326,7 @@
       </c>
       <c r="K296" s="7"/>
     </row>
-    <row r="297" spans="1:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="297" spans="1:11" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A297" s="29" t="s">
         <v>24</v>
       </c>
@@ -31427,7 +31353,7 @@
       </c>
       <c r="K297" s="7"/>
     </row>
-    <row r="298" spans="1:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="298" spans="1:11" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A298" s="29" t="s">
         <v>24</v>
       </c>
@@ -31449,7 +31375,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="299" spans="1:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="299" spans="1:11" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A299" s="29" t="s">
         <v>24</v>
       </c>
@@ -31468,7 +31394,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="300" spans="1:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="300" spans="1:11" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A300" s="29" t="s">
         <v>24</v>
       </c>
@@ -31490,7 +31416,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="301" spans="1:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="301" spans="1:11" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A301" s="29" t="s">
         <v>28</v>
       </c>
@@ -31517,7 +31443,7 @@
       </c>
       <c r="K301" s="7"/>
     </row>
-    <row r="302" spans="1:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="302" spans="1:11" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A302" s="29" t="s">
         <v>28</v>
       </c>
@@ -31544,7 +31470,7 @@
       </c>
       <c r="K302" s="7"/>
     </row>
-    <row r="303" spans="1:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="303" spans="1:11" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A303" s="29" t="s">
         <v>28</v>
       </c>
@@ -31566,7 +31492,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="304" spans="1:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="304" spans="1:11" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A304" s="29" t="s">
         <v>28</v>
       </c>
@@ -31593,7 +31519,7 @@
       </c>
       <c r="K304" s="7"/>
     </row>
-    <row r="305" spans="1:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="305" spans="1:11" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A305" s="29" t="s">
         <v>28</v>
       </c>
@@ -31620,7 +31546,7 @@
       </c>
       <c r="K305" s="7"/>
     </row>
-    <row r="306" spans="1:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="306" spans="1:11" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A306" s="29" t="s">
         <v>32</v>
       </c>
@@ -31647,7 +31573,7 @@
       </c>
       <c r="K306" s="7"/>
     </row>
-    <row r="307" spans="1:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="307" spans="1:11" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A307" s="29" t="s">
         <v>28</v>
       </c>
@@ -31669,7 +31595,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="308" spans="1:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="308" spans="1:11" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A308" s="29" t="s">
         <v>32</v>
       </c>
@@ -31696,7 +31622,7 @@
       </c>
       <c r="K308" s="7"/>
     </row>
-    <row r="309" spans="1:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="309" spans="1:11" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A309" s="29" t="s">
         <v>32</v>
       </c>
@@ -31723,7 +31649,7 @@
       </c>
       <c r="K309" s="7"/>
     </row>
-    <row r="310" spans="1:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="310" spans="1:11" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A310" s="29" t="s">
         <v>32</v>
       </c>
@@ -31742,7 +31668,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="311" spans="1:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="311" spans="1:11" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A311" s="29" t="s">
         <v>32</v>
       </c>
@@ -31769,7 +31695,7 @@
       </c>
       <c r="K311" s="7"/>
     </row>
-    <row r="312" spans="1:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="312" spans="1:11" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A312" s="29" t="s">
         <v>32</v>
       </c>
@@ -31796,7 +31722,7 @@
       </c>
       <c r="K312" s="7"/>
     </row>
-    <row r="313" spans="1:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="313" spans="1:11" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A313" s="29" t="s">
         <v>32</v>
       </c>
@@ -31818,7 +31744,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="314" spans="1:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="314" spans="1:11" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A314" s="29" t="s">
         <v>238</v>
       </c>
@@ -31845,7 +31771,7 @@
       </c>
       <c r="K314" s="7"/>
     </row>
-    <row r="315" spans="1:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="315" spans="1:11" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A315" s="29" t="s">
         <v>238</v>
       </c>
@@ -31870,7 +31796,7 @@
       </c>
       <c r="K315" s="7"/>
     </row>
-    <row r="316" spans="1:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="316" spans="1:11" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A316" s="29" t="s">
         <v>238</v>
       </c>
@@ -31889,7 +31815,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="317" spans="1:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="317" spans="1:11" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A317" s="29" t="s">
         <v>238</v>
       </c>
@@ -31908,7 +31834,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="318" spans="1:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="318" spans="1:11" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A318" s="29" t="s">
         <v>28</v>
       </c>
@@ -31935,7 +31861,7 @@
       </c>
       <c r="K318" s="7"/>
     </row>
-    <row r="319" spans="1:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="319" spans="1:11" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A319" s="29" t="s">
         <v>15</v>
       </c>
@@ -31962,7 +31888,7 @@
       </c>
       <c r="K319" s="7"/>
     </row>
-    <row r="320" spans="1:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="320" spans="1:11" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A320" s="29" t="s">
         <v>60</v>
       </c>
@@ -31989,7 +31915,7 @@
       </c>
       <c r="K320" s="7"/>
     </row>
-    <row r="321" spans="1:15" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="321" spans="1:15" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A321" s="29" t="s">
         <v>67</v>
       </c>
@@ -32016,7 +31942,7 @@
       </c>
       <c r="K321" s="7"/>
     </row>
-    <row r="322" spans="1:15" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="322" spans="1:15" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A322" s="29" t="s">
         <v>24</v>
       </c>
@@ -32043,7 +31969,7 @@
       </c>
       <c r="K322" s="7"/>
     </row>
-    <row r="323" spans="1:15" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="323" spans="1:15" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A323" s="29" t="s">
         <v>52</v>
       </c>
@@ -32069,7 +31995,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="324" spans="1:15" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="324" spans="1:15" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A324" s="29" t="s">
         <v>52</v>
       </c>
@@ -32095,7 +32021,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="325" spans="1:15" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="325" spans="1:15" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A325" s="29" t="s">
         <v>60</v>
       </c>
@@ -32121,7 +32047,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="326" spans="1:15" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="326" spans="1:15" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A326" s="29" t="s">
         <v>60</v>
       </c>
@@ -32147,7 +32073,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="327" spans="1:15" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="327" spans="1:15" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A327" s="29" t="s">
         <v>60</v>
       </c>
@@ -32173,7 +32099,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="328" spans="1:15" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="328" spans="1:15" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A328" s="29" t="s">
         <v>60</v>
       </c>
@@ -32199,7 +32125,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="329" spans="1:15" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="329" spans="1:15" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A329" s="29" t="s">
         <v>15</v>
       </c>
@@ -32226,7 +32152,7 @@
       </c>
       <c r="I329" s="24"/>
     </row>
-    <row r="330" spans="1:15" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="330" spans="1:15" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A330" s="29" t="s">
         <v>15</v>
       </c>
@@ -32253,7 +32179,7 @@
       </c>
       <c r="I330" s="24"/>
     </row>
-    <row r="331" spans="1:15" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="331" spans="1:15" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A331" s="29" t="s">
         <v>15</v>
       </c>
@@ -32280,7 +32206,7 @@
       </c>
       <c r="I331" s="24"/>
     </row>
-    <row r="332" spans="1:15" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="332" spans="1:15" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A332" s="29" t="s">
         <v>67</v>
       </c>
@@ -32307,7 +32233,7 @@
       </c>
       <c r="I332" s="24"/>
     </row>
-    <row r="333" spans="1:15" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="333" spans="1:15" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A333" s="29" t="s">
         <v>259</v>
       </c>
@@ -32327,7 +32253,7 @@
       </c>
       <c r="I333" s="24"/>
     </row>
-    <row r="334" spans="1:15" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="334" spans="1:15" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A334" s="29" t="s">
         <v>24</v>
       </c>
@@ -32354,7 +32280,7 @@
       </c>
       <c r="I334" s="24"/>
     </row>
-    <row r="335" spans="1:15" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="335" spans="1:15" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A335" s="29" t="s">
         <v>24</v>
       </c>
@@ -32381,7 +32307,7 @@
       </c>
       <c r="I335" s="24"/>
     </row>
-    <row r="336" spans="1:15" s="13" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="336" spans="1:15" s="13" customFormat="1" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A336" s="29" t="s">
         <v>28</v>
       </c>
@@ -32414,7 +32340,7 @@
       <c r="N336" s="9"/>
       <c r="O336" s="12"/>
     </row>
-    <row r="337" spans="1:15" s="13" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="337" spans="1:15" s="13" customFormat="1" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A337" s="29" t="s">
         <v>32</v>
       </c>
@@ -32445,7 +32371,7 @@
       <c r="N337" s="9"/>
       <c r="O337" s="12"/>
     </row>
-    <row r="338" spans="1:15" s="13" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="338" spans="1:15" s="13" customFormat="1" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A338" s="29" t="s">
         <v>52</v>
       </c>
@@ -32478,7 +32404,7 @@
       <c r="N338" s="9"/>
       <c r="O338" s="12"/>
     </row>
-    <row r="339" spans="1:15" s="13" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="339" spans="1:15" s="13" customFormat="1" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A339" s="29" t="s">
         <v>52</v>
       </c>
@@ -32511,7 +32437,7 @@
       <c r="N339" s="9"/>
       <c r="O339" s="12"/>
     </row>
-    <row r="340" spans="1:15" s="13" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="340" spans="1:15" s="13" customFormat="1" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A340" s="29" t="s">
         <v>52</v>
       </c>
@@ -32544,7 +32470,7 @@
       <c r="N340" s="9"/>
       <c r="O340" s="12"/>
     </row>
-    <row r="341" spans="1:15" s="13" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="341" spans="1:15" s="13" customFormat="1" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A341" s="29" t="s">
         <v>52</v>
       </c>
@@ -32571,7 +32497,7 @@
       <c r="N341" s="9"/>
       <c r="O341" s="12"/>
     </row>
-    <row r="342" spans="1:15" s="13" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="342" spans="1:15" s="13" customFormat="1" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A342" s="29" t="s">
         <v>52</v>
       </c>
@@ -32604,7 +32530,7 @@
       <c r="N342" s="9"/>
       <c r="O342" s="12"/>
     </row>
-    <row r="343" spans="1:15" s="13" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="343" spans="1:15" s="13" customFormat="1" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A343" s="29" t="s">
         <v>60</v>
       </c>
@@ -32637,7 +32563,7 @@
       <c r="N343" s="9"/>
       <c r="O343" s="12"/>
     </row>
-    <row r="344" spans="1:15" s="13" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="344" spans="1:15" s="13" customFormat="1" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A344" s="29" t="s">
         <v>60</v>
       </c>
@@ -32670,7 +32596,7 @@
       <c r="N344" s="9"/>
       <c r="O344" s="12"/>
     </row>
-    <row r="345" spans="1:15" s="13" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="345" spans="1:15" s="13" customFormat="1" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A345" s="29" t="s">
         <v>60</v>
       </c>
@@ -32703,7 +32629,7 @@
       <c r="N345" s="9"/>
       <c r="O345" s="12"/>
     </row>
-    <row r="346" spans="1:15" s="13" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="346" spans="1:15" s="13" customFormat="1" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A346" s="29" t="s">
         <v>60</v>
       </c>
@@ -32736,7 +32662,7 @@
       <c r="N346" s="9"/>
       <c r="O346" s="12"/>
     </row>
-    <row r="347" spans="1:15" s="13" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="347" spans="1:15" s="13" customFormat="1" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A347" s="29" t="s">
         <v>60</v>
       </c>
@@ -32769,7 +32695,7 @@
       <c r="N347" s="9"/>
       <c r="O347" s="12"/>
     </row>
-    <row r="348" spans="1:15" s="13" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="348" spans="1:15" s="13" customFormat="1" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A348" s="29" t="s">
         <v>60</v>
       </c>
@@ -32802,7 +32728,7 @@
       <c r="N348" s="9"/>
       <c r="O348" s="12"/>
     </row>
-    <row r="349" spans="1:15" s="13" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="349" spans="1:15" s="13" customFormat="1" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A349" s="29" t="s">
         <v>60</v>
       </c>
@@ -32835,7 +32761,7 @@
       <c r="N349" s="9"/>
       <c r="O349" s="12"/>
     </row>
-    <row r="350" spans="1:15" s="13" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="350" spans="1:15" s="13" customFormat="1" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A350" s="29" t="s">
         <v>60</v>
       </c>
@@ -32868,7 +32794,7 @@
       <c r="N350" s="9"/>
       <c r="O350" s="12"/>
     </row>
-    <row r="351" spans="1:15" s="13" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="351" spans="1:15" s="13" customFormat="1" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A351" s="29" t="s">
         <v>15</v>
       </c>
@@ -32901,7 +32827,7 @@
       <c r="N351" s="9"/>
       <c r="O351" s="12"/>
     </row>
-    <row r="352" spans="1:15" s="13" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="352" spans="1:15" s="13" customFormat="1" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A352" s="29" t="s">
         <v>15</v>
       </c>
@@ -32932,7 +32858,7 @@
       <c r="N352" s="9"/>
       <c r="O352" s="12"/>
     </row>
-    <row r="353" spans="1:15" s="13" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="353" spans="1:15" s="13" customFormat="1" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A353" s="29" t="s">
         <v>15</v>
       </c>
@@ -32963,7 +32889,7 @@
       <c r="N353" s="9"/>
       <c r="O353" s="12"/>
     </row>
-    <row r="354" spans="1:15" s="13" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="354" spans="1:15" s="13" customFormat="1" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A354" s="29" t="s">
         <v>15</v>
       </c>
@@ -32996,7 +32922,7 @@
       <c r="N354" s="9"/>
       <c r="O354" s="12"/>
     </row>
-    <row r="355" spans="1:15" s="13" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="355" spans="1:15" s="13" customFormat="1" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A355" s="29" t="s">
         <v>15</v>
       </c>
@@ -33029,7 +32955,7 @@
       <c r="N355" s="9"/>
       <c r="O355" s="12"/>
     </row>
-    <row r="356" spans="1:15" s="13" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="356" spans="1:15" s="13" customFormat="1" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A356" s="29" t="s">
         <v>15</v>
       </c>
@@ -33062,7 +32988,7 @@
       <c r="N356" s="9"/>
       <c r="O356" s="12"/>
     </row>
-    <row r="357" spans="1:15" s="13" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="357" spans="1:15" s="13" customFormat="1" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A357" s="29" t="s">
         <v>67</v>
       </c>
@@ -33095,7 +33021,7 @@
       <c r="N357" s="9"/>
       <c r="O357" s="12"/>
     </row>
-    <row r="358" spans="1:15" s="13" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="358" spans="1:15" s="13" customFormat="1" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A358" s="29" t="s">
         <v>67</v>
       </c>
@@ -33128,7 +33054,7 @@
       <c r="N358" s="9"/>
       <c r="O358" s="12"/>
     </row>
-    <row r="359" spans="1:15" s="13" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="359" spans="1:15" s="13" customFormat="1" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A359" s="29" t="s">
         <v>67</v>
       </c>
@@ -33161,7 +33087,7 @@
       <c r="N359" s="9"/>
       <c r="O359" s="12"/>
     </row>
-    <row r="360" spans="1:15" s="13" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="360" spans="1:15" s="13" customFormat="1" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A360" s="29" t="s">
         <v>67</v>
       </c>
@@ -33194,7 +33120,7 @@
       <c r="N360" s="9"/>
       <c r="O360" s="12"/>
     </row>
-    <row r="361" spans="1:15" s="13" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="361" spans="1:15" s="13" customFormat="1" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A361" s="29" t="s">
         <v>67</v>
       </c>
@@ -33221,7 +33147,7 @@
       <c r="N361" s="9"/>
       <c r="O361" s="12"/>
     </row>
-    <row r="362" spans="1:15" s="13" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="362" spans="1:15" s="13" customFormat="1" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A362" s="29" t="s">
         <v>67</v>
       </c>
@@ -33254,7 +33180,7 @@
       <c r="N362" s="9"/>
       <c r="O362" s="12"/>
     </row>
-    <row r="363" spans="1:15" s="13" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="363" spans="1:15" s="13" customFormat="1" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A363" s="29" t="s">
         <v>259</v>
       </c>
@@ -33287,7 +33213,7 @@
       <c r="N363" s="9"/>
       <c r="O363" s="12"/>
     </row>
-    <row r="364" spans="1:15" s="13" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="364" spans="1:15" s="13" customFormat="1" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A364" s="29" t="s">
         <v>259</v>
       </c>
@@ -33320,7 +33246,7 @@
       <c r="N364" s="9"/>
       <c r="O364" s="12"/>
     </row>
-    <row r="365" spans="1:15" s="13" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="365" spans="1:15" s="13" customFormat="1" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A365" s="29" t="s">
         <v>259</v>
       </c>
@@ -33353,7 +33279,7 @@
       <c r="N365" s="9"/>
       <c r="O365" s="12"/>
     </row>
-    <row r="366" spans="1:15" s="13" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="366" spans="1:15" s="13" customFormat="1" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A366" s="29" t="s">
         <v>259</v>
       </c>
@@ -33386,7 +33312,7 @@
       <c r="N366" s="9"/>
       <c r="O366" s="12"/>
     </row>
-    <row r="367" spans="1:15" s="13" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="367" spans="1:15" s="13" customFormat="1" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A367" s="29" t="s">
         <v>290</v>
       </c>
@@ -33419,7 +33345,7 @@
       <c r="N367" s="9"/>
       <c r="O367" s="12"/>
     </row>
-    <row r="368" spans="1:15" s="13" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="368" spans="1:15" s="13" customFormat="1" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A368" s="29" t="s">
         <v>290</v>
       </c>
@@ -33452,7 +33378,7 @@
       <c r="N368" s="9"/>
       <c r="O368" s="12"/>
     </row>
-    <row r="369" spans="1:15" s="13" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="369" spans="1:15" s="13" customFormat="1" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A369" s="29" t="s">
         <v>290</v>
       </c>
@@ -33485,7 +33411,7 @@
       <c r="N369" s="9"/>
       <c r="O369" s="12"/>
     </row>
-    <row r="370" spans="1:15" s="13" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="370" spans="1:15" s="13" customFormat="1" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A370" s="29" t="s">
         <v>292</v>
       </c>
@@ -33518,7 +33444,7 @@
       <c r="N370" s="9"/>
       <c r="O370" s="12"/>
     </row>
-    <row r="371" spans="1:15" s="13" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="371" spans="1:15" s="13" customFormat="1" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A371" s="29" t="s">
         <v>292</v>
       </c>
@@ -33551,7 +33477,7 @@
       <c r="N371" s="9"/>
       <c r="O371" s="12"/>
     </row>
-    <row r="372" spans="1:15" s="13" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="372" spans="1:15" s="13" customFormat="1" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A372" s="29" t="s">
         <v>292</v>
       </c>
@@ -33584,7 +33510,7 @@
       <c r="N372" s="9"/>
       <c r="O372" s="12"/>
     </row>
-    <row r="373" spans="1:15" s="13" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="373" spans="1:15" s="13" customFormat="1" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A373" s="29" t="s">
         <v>24</v>
       </c>
@@ -33617,7 +33543,7 @@
       <c r="N373" s="9"/>
       <c r="O373" s="12"/>
     </row>
-    <row r="374" spans="1:15" s="13" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="374" spans="1:15" s="13" customFormat="1" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A374" s="29" t="s">
         <v>24</v>
       </c>
@@ -33650,7 +33576,7 @@
       <c r="N374" s="9"/>
       <c r="O374" s="12"/>
     </row>
-    <row r="375" spans="1:15" s="13" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="375" spans="1:15" s="13" customFormat="1" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A375" s="29" t="s">
         <v>24</v>
       </c>
@@ -33683,7 +33609,7 @@
       <c r="N375" s="9"/>
       <c r="O375" s="12"/>
     </row>
-    <row r="376" spans="1:15" s="13" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="376" spans="1:15" s="13" customFormat="1" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A376" s="29" t="s">
         <v>24</v>
       </c>
@@ -33716,7 +33642,7 @@
       <c r="N376" s="9"/>
       <c r="O376" s="12"/>
     </row>
-    <row r="377" spans="1:15" s="13" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="377" spans="1:15" s="13" customFormat="1" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A377" s="29" t="s">
         <v>24</v>
       </c>
@@ -33749,7 +33675,7 @@
       <c r="N377" s="9"/>
       <c r="O377" s="12"/>
     </row>
-    <row r="378" spans="1:15" s="13" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="378" spans="1:15" s="13" customFormat="1" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A378" s="29" t="s">
         <v>24</v>
       </c>
@@ -33782,7 +33708,7 @@
       <c r="N378" s="9"/>
       <c r="O378" s="12"/>
     </row>
-    <row r="379" spans="1:15" s="13" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="379" spans="1:15" s="13" customFormat="1" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A379" s="29" t="s">
         <v>24</v>
       </c>
@@ -33811,7 +33737,7 @@
       <c r="N379" s="9"/>
       <c r="O379" s="12"/>
     </row>
-    <row r="380" spans="1:15" s="13" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="380" spans="1:15" s="13" customFormat="1" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A380" s="29" t="s">
         <v>24</v>
       </c>
@@ -33844,7 +33770,7 @@
       <c r="N380" s="9"/>
       <c r="O380" s="12"/>
     </row>
-    <row r="381" spans="1:15" s="13" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="381" spans="1:15" s="13" customFormat="1" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A381" s="29" t="s">
         <v>300</v>
       </c>
@@ -33877,7 +33803,7 @@
       <c r="N381" s="9"/>
       <c r="O381" s="12"/>
     </row>
-    <row r="382" spans="1:15" s="13" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="382" spans="1:15" s="13" customFormat="1" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A382" s="29" t="s">
         <v>238</v>
       </c>
@@ -33910,7 +33836,7 @@
       <c r="N382" s="9"/>
       <c r="O382" s="12"/>
     </row>
-    <row r="383" spans="1:15" s="13" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="383" spans="1:15" s="13" customFormat="1" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A383" s="29" t="s">
         <v>238</v>
       </c>
@@ -33943,7 +33869,7 @@
       <c r="N383" s="9"/>
       <c r="O383" s="12"/>
     </row>
-    <row r="384" spans="1:15" s="13" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="384" spans="1:15" s="13" customFormat="1" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A384" s="29" t="s">
         <v>238</v>
       </c>
@@ -33976,7 +33902,7 @@
       <c r="N384" s="9"/>
       <c r="O384" s="12"/>
     </row>
-    <row r="385" spans="1:15" s="13" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="385" spans="1:15" s="13" customFormat="1" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A385" s="29" t="s">
         <v>238</v>
       </c>
@@ -34009,7 +33935,7 @@
       <c r="N385" s="9"/>
       <c r="O385" s="12"/>
     </row>
-    <row r="386" spans="1:15" s="13" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="386" spans="1:15" s="13" customFormat="1" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A386" s="29" t="s">
         <v>238</v>
       </c>
@@ -34036,7 +33962,7 @@
       <c r="N386" s="9"/>
       <c r="O386" s="12"/>
     </row>
-    <row r="387" spans="1:15" s="13" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="387" spans="1:15" s="13" customFormat="1" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A387" s="29" t="s">
         <v>238</v>
       </c>
@@ -34069,7 +33995,7 @@
       <c r="N387" s="9"/>
       <c r="O387" s="12"/>
     </row>
-    <row r="388" spans="1:15" s="13" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="388" spans="1:15" s="13" customFormat="1" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A388" s="29" t="s">
         <v>28</v>
       </c>
@@ -34102,7 +34028,7 @@
       <c r="N388" s="9"/>
       <c r="O388" s="12"/>
     </row>
-    <row r="389" spans="1:15" s="13" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="389" spans="1:15" s="13" customFormat="1" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A389" s="29" t="s">
         <v>28</v>
       </c>
@@ -34135,7 +34061,7 @@
       <c r="N389" s="9"/>
       <c r="O389" s="12"/>
     </row>
-    <row r="390" spans="1:15" s="13" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="390" spans="1:15" s="13" customFormat="1" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A390" s="29" t="s">
         <v>28</v>
       </c>
@@ -34168,7 +34094,7 @@
       <c r="N390" s="9"/>
       <c r="O390" s="12"/>
     </row>
-    <row r="391" spans="1:15" s="13" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="391" spans="1:15" s="13" customFormat="1" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A391" s="29" t="s">
         <v>28</v>
       </c>
@@ -34201,7 +34127,7 @@
       <c r="N391" s="9"/>
       <c r="O391" s="12"/>
     </row>
-    <row r="392" spans="1:15" s="13" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="392" spans="1:15" s="13" customFormat="1" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A392" s="29" t="s">
         <v>28</v>
       </c>
@@ -34228,7 +34154,7 @@
       <c r="N392" s="9"/>
       <c r="O392" s="12"/>
     </row>
-    <row r="393" spans="1:15" s="13" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="393" spans="1:15" s="13" customFormat="1" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A393" s="29" t="s">
         <v>28</v>
       </c>
@@ -34261,7 +34187,7 @@
       <c r="N393" s="9"/>
       <c r="O393" s="12"/>
     </row>
-    <row r="394" spans="1:15" s="13" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="394" spans="1:15" s="13" customFormat="1" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A394" s="29" t="s">
         <v>28</v>
       </c>
@@ -34294,7 +34220,7 @@
       <c r="N394" s="9"/>
       <c r="O394" s="12"/>
     </row>
-    <row r="395" spans="1:15" s="13" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="395" spans="1:15" s="13" customFormat="1" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A395" s="29" t="s">
         <v>32</v>
       </c>
@@ -34327,7 +34253,7 @@
       <c r="N395" s="9"/>
       <c r="O395" s="12"/>
     </row>
-    <row r="396" spans="1:15" s="13" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="396" spans="1:15" s="13" customFormat="1" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A396" s="29" t="s">
         <v>32</v>
       </c>
@@ -34360,7 +34286,7 @@
       <c r="N396" s="9"/>
       <c r="O396" s="12"/>
     </row>
-    <row r="397" spans="1:15" s="13" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="397" spans="1:15" s="13" customFormat="1" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A397" s="29" t="s">
         <v>32</v>
       </c>
@@ -34393,7 +34319,7 @@
       <c r="N397" s="9"/>
       <c r="O397" s="12"/>
     </row>
-    <row r="398" spans="1:15" s="13" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="398" spans="1:15" s="13" customFormat="1" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A398" s="29" t="s">
         <v>32</v>
       </c>
@@ -34422,7 +34348,7 @@
       <c r="N398" s="9"/>
       <c r="O398" s="12"/>
     </row>
-    <row r="399" spans="1:15" s="13" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="399" spans="1:15" s="13" customFormat="1" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A399" s="29" t="s">
         <v>32</v>
       </c>
@@ -34455,7 +34381,7 @@
       <c r="N399" s="9"/>
       <c r="O399" s="12"/>
     </row>
-    <row r="400" spans="1:15" s="13" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="400" spans="1:15" s="13" customFormat="1" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A400" s="29" t="s">
         <v>32</v>
       </c>
@@ -34488,7 +34414,7 @@
       <c r="N400" s="9"/>
       <c r="O400" s="12"/>
     </row>
-    <row r="401" spans="1:15" s="13" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="401" spans="1:15" s="13" customFormat="1" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A401" s="29" t="s">
         <v>313</v>
       </c>
@@ -34521,7 +34447,7 @@
       <c r="N401" s="9"/>
       <c r="O401" s="12"/>
     </row>
-    <row r="402" spans="1:15" s="13" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="402" spans="1:15" s="13" customFormat="1" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A402" s="29" t="s">
         <v>52</v>
       </c>
@@ -34554,7 +34480,7 @@
       <c r="N402" s="9"/>
       <c r="O402" s="12"/>
     </row>
-    <row r="403" spans="1:15" s="13" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="403" spans="1:15" s="13" customFormat="1" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A403" s="29" t="s">
         <v>52</v>
       </c>
@@ -34587,7 +34513,7 @@
       <c r="N403" s="9"/>
       <c r="O403" s="12"/>
     </row>
-    <row r="404" spans="1:15" s="13" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="404" spans="1:15" s="13" customFormat="1" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A404" s="29" t="s">
         <v>52</v>
       </c>
@@ -34620,7 +34546,7 @@
       <c r="N404" s="9"/>
       <c r="O404" s="12"/>
     </row>
-    <row r="405" spans="1:15" s="13" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="405" spans="1:15" s="13" customFormat="1" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A405" s="29" t="s">
         <v>52</v>
       </c>
@@ -34653,7 +34579,7 @@
       <c r="N405" s="9"/>
       <c r="O405" s="12"/>
     </row>
-    <row r="406" spans="1:15" s="13" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="406" spans="1:15" s="13" customFormat="1" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A406" s="29" t="s">
         <v>60</v>
       </c>
@@ -34686,7 +34612,7 @@
       <c r="N406" s="9"/>
       <c r="O406" s="12"/>
     </row>
-    <row r="407" spans="1:15" s="13" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="407" spans="1:15" s="13" customFormat="1" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A407" s="29" t="s">
         <v>60</v>
       </c>
@@ -34719,7 +34645,7 @@
       <c r="N407" s="9"/>
       <c r="O407" s="12"/>
     </row>
-    <row r="408" spans="1:15" s="13" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="408" spans="1:15" s="13" customFormat="1" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A408" s="29" t="s">
         <v>60</v>
       </c>
@@ -34748,7 +34674,7 @@
       <c r="N408" s="9"/>
       <c r="O408" s="12"/>
     </row>
-    <row r="409" spans="1:15" s="13" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="409" spans="1:15" s="13" customFormat="1" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A409" s="29" t="s">
         <v>60</v>
       </c>
@@ -34781,7 +34707,7 @@
       <c r="N409" s="9"/>
       <c r="O409" s="12"/>
     </row>
-    <row r="410" spans="1:15" s="13" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="410" spans="1:15" s="13" customFormat="1" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A410" s="29" t="s">
         <v>60</v>
       </c>
@@ -34814,7 +34740,7 @@
       <c r="N410" s="9"/>
       <c r="O410" s="12"/>
     </row>
-    <row r="411" spans="1:15" s="13" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="411" spans="1:15" s="13" customFormat="1" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A411" s="29" t="s">
         <v>60</v>
       </c>
@@ -34847,7 +34773,7 @@
       <c r="N411" s="9"/>
       <c r="O411" s="12"/>
     </row>
-    <row r="412" spans="1:15" s="13" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="412" spans="1:15" s="13" customFormat="1" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A412" s="29" t="s">
         <v>60</v>
       </c>
@@ -34880,7 +34806,7 @@
       <c r="N412" s="9"/>
       <c r="O412" s="12"/>
     </row>
-    <row r="413" spans="1:15" s="13" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="413" spans="1:15" s="13" customFormat="1" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A413" s="29" t="s">
         <v>52</v>
       </c>
@@ -34913,7 +34839,7 @@
       <c r="N413" s="9"/>
       <c r="O413" s="12"/>
     </row>
-    <row r="414" spans="1:15" s="13" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="414" spans="1:15" s="13" customFormat="1" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A414" s="29" t="s">
         <v>60</v>
       </c>
@@ -34946,7 +34872,7 @@
       <c r="N414" s="9"/>
       <c r="O414" s="12"/>
     </row>
-    <row r="415" spans="1:15" s="13" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="415" spans="1:15" s="13" customFormat="1" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A415" s="29" t="s">
         <v>15</v>
       </c>
@@ -34977,7 +34903,7 @@
       <c r="N415" s="9"/>
       <c r="O415" s="12"/>
     </row>
-    <row r="416" spans="1:15" s="13" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="416" spans="1:15" s="13" customFormat="1" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A416" s="29" t="s">
         <v>15</v>
       </c>
@@ -35008,7 +34934,7 @@
       <c r="N416" s="9"/>
       <c r="O416" s="12"/>
     </row>
-    <row r="417" spans="1:15" s="13" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="417" spans="1:15" s="13" customFormat="1" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A417" s="29" t="s">
         <v>15</v>
       </c>
@@ -35041,7 +34967,7 @@
       <c r="N417" s="9"/>
       <c r="O417" s="12"/>
     </row>
-    <row r="418" spans="1:15" s="13" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="418" spans="1:15" s="13" customFormat="1" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A418" s="29" t="s">
         <v>15</v>
       </c>
@@ -35074,7 +35000,7 @@
       <c r="N418" s="9"/>
       <c r="O418" s="12"/>
     </row>
-    <row r="419" spans="1:15" s="13" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="419" spans="1:15" s="13" customFormat="1" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A419" s="29" t="s">
         <v>15</v>
       </c>
@@ -35107,7 +35033,7 @@
       <c r="N419" s="9"/>
       <c r="O419" s="12"/>
     </row>
-    <row r="420" spans="1:15" s="13" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="420" spans="1:15" s="13" customFormat="1" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A420" s="29" t="s">
         <v>67</v>
       </c>
@@ -35140,7 +35066,7 @@
       <c r="N420" s="9"/>
       <c r="O420" s="12"/>
     </row>
-    <row r="421" spans="1:15" s="13" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="421" spans="1:15" s="13" customFormat="1" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A421" s="29" t="s">
         <v>52</v>
       </c>
@@ -35173,7 +35099,7 @@
       <c r="N421" s="9"/>
       <c r="O421" s="12"/>
     </row>
-    <row r="422" spans="1:15" s="13" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="422" spans="1:15" s="13" customFormat="1" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A422" s="29" t="s">
         <v>15</v>
       </c>
@@ -35206,7 +35132,7 @@
       <c r="N422" s="9"/>
       <c r="O422" s="12"/>
     </row>
-    <row r="423" spans="1:15" s="13" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="423" spans="1:15" s="13" customFormat="1" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A423" s="29" t="s">
         <v>15</v>
       </c>
@@ -35239,7 +35165,7 @@
       <c r="N423" s="9"/>
       <c r="O423" s="12"/>
     </row>
-    <row r="424" spans="1:15" s="13" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="424" spans="1:15" s="13" customFormat="1" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A424" s="29" t="s">
         <v>67</v>
       </c>
@@ -35272,7 +35198,7 @@
       <c r="N424" s="9"/>
       <c r="O424" s="12"/>
     </row>
-    <row r="425" spans="1:15" s="13" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="425" spans="1:15" s="13" customFormat="1" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A425" s="29" t="s">
         <v>67</v>
       </c>
@@ -35305,7 +35231,7 @@
       <c r="N425" s="9"/>
       <c r="O425" s="12"/>
     </row>
-    <row r="426" spans="1:15" s="13" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="426" spans="1:15" s="13" customFormat="1" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A426" s="29" t="s">
         <v>67</v>
       </c>
@@ -35338,7 +35264,7 @@
       <c r="N426" s="9"/>
       <c r="O426" s="12"/>
     </row>
-    <row r="427" spans="1:15" s="13" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="427" spans="1:15" s="13" customFormat="1" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A427" s="29" t="s">
         <v>67</v>
       </c>
@@ -35371,7 +35297,7 @@
       <c r="N427" s="9"/>
       <c r="O427" s="12"/>
     </row>
-    <row r="428" spans="1:15" s="13" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="428" spans="1:15" s="13" customFormat="1" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A428" s="29" t="s">
         <v>67</v>
       </c>
@@ -35404,7 +35330,7 @@
       <c r="N428" s="9"/>
       <c r="O428" s="12"/>
     </row>
-    <row r="429" spans="1:15" s="13" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="429" spans="1:15" s="13" customFormat="1" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A429" s="29" t="s">
         <v>290</v>
       </c>
@@ -35437,7 +35363,7 @@
       <c r="N429" s="9"/>
       <c r="O429" s="12"/>
     </row>
-    <row r="430" spans="1:15" s="13" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="430" spans="1:15" s="13" customFormat="1" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A430" s="29" t="s">
         <v>259</v>
       </c>
@@ -35470,7 +35396,7 @@
       <c r="N430" s="9"/>
       <c r="O430" s="12"/>
     </row>
-    <row r="431" spans="1:15" s="13" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="431" spans="1:15" s="13" customFormat="1" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A431" s="29" t="s">
         <v>259</v>
       </c>
@@ -35503,7 +35429,7 @@
       <c r="N431" s="9"/>
       <c r="O431" s="12"/>
     </row>
-    <row r="432" spans="1:15" s="13" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="432" spans="1:15" s="13" customFormat="1" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A432" s="29" t="s">
         <v>259</v>
       </c>
@@ -35532,7 +35458,7 @@
       <c r="N432" s="9"/>
       <c r="O432" s="12"/>
     </row>
-    <row r="433" spans="1:15" s="13" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="433" spans="1:15" s="13" customFormat="1" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A433" s="29" t="s">
         <v>259</v>
       </c>
@@ -35561,7 +35487,7 @@
       <c r="N433" s="9"/>
       <c r="O433" s="12"/>
     </row>
-    <row r="434" spans="1:15" s="13" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="434" spans="1:15" s="13" customFormat="1" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A434" s="29" t="s">
         <v>290</v>
       </c>
@@ -35594,7 +35520,7 @@
       <c r="N434" s="9"/>
       <c r="O434" s="12"/>
     </row>
-    <row r="435" spans="1:15" s="13" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="435" spans="1:15" s="13" customFormat="1" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A435" s="29" t="s">
         <v>290</v>
       </c>
@@ -35627,7 +35553,7 @@
       <c r="N435" s="9"/>
       <c r="O435" s="12"/>
     </row>
-    <row r="436" spans="1:15" s="13" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="436" spans="1:15" s="13" customFormat="1" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A436" s="29" t="s">
         <v>290</v>
       </c>
@@ -35660,7 +35586,7 @@
       <c r="N436" s="9"/>
       <c r="O436" s="12"/>
     </row>
-    <row r="437" spans="1:15" s="13" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="437" spans="1:15" s="13" customFormat="1" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A437" s="29" t="s">
         <v>290</v>
       </c>
@@ -35693,7 +35619,7 @@
       <c r="N437" s="9"/>
       <c r="O437" s="12"/>
     </row>
-    <row r="438" spans="1:15" s="13" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="438" spans="1:15" s="13" customFormat="1" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A438" s="29" t="s">
         <v>292</v>
       </c>
@@ -35726,7 +35652,7 @@
       <c r="N438" s="9"/>
       <c r="O438" s="12"/>
     </row>
-    <row r="439" spans="1:15" s="13" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="439" spans="1:15" s="13" customFormat="1" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A439" s="29" t="s">
         <v>292</v>
       </c>
@@ -35759,7 +35685,7 @@
       <c r="N439" s="9"/>
       <c r="O439" s="12"/>
     </row>
-    <row r="440" spans="1:15" s="13" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="440" spans="1:15" s="13" customFormat="1" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A440" s="29" t="s">
         <v>292</v>
       </c>
@@ -35792,7 +35718,7 @@
       <c r="N440" s="9"/>
       <c r="O440" s="12"/>
     </row>
-    <row r="441" spans="1:15" s="13" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="441" spans="1:15" s="13" customFormat="1" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A441" s="29" t="s">
         <v>292</v>
       </c>
@@ -35825,7 +35751,7 @@
       <c r="N441" s="9"/>
       <c r="O441" s="12"/>
     </row>
-    <row r="442" spans="1:15" s="13" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="442" spans="1:15" s="13" customFormat="1" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A442" s="29" t="s">
         <v>24</v>
       </c>
@@ -35858,7 +35784,7 @@
       <c r="N442" s="9"/>
       <c r="O442" s="12"/>
     </row>
-    <row r="443" spans="1:15" s="13" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="443" spans="1:15" s="13" customFormat="1" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A443" s="29" t="s">
         <v>24</v>
       </c>
@@ -35891,7 +35817,7 @@
       <c r="N443" s="9"/>
       <c r="O443" s="12"/>
     </row>
-    <row r="444" spans="1:15" s="13" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="444" spans="1:15" s="13" customFormat="1" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A444" s="29" t="s">
         <v>24</v>
       </c>
@@ -35924,7 +35850,7 @@
       <c r="N444" s="9"/>
       <c r="O444" s="12"/>
     </row>
-    <row r="445" spans="1:15" s="13" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="445" spans="1:15" s="13" customFormat="1" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A445" s="29" t="s">
         <v>24</v>
       </c>
@@ -35957,7 +35883,7 @@
       <c r="N445" s="9"/>
       <c r="O445" s="12"/>
     </row>
-    <row r="446" spans="1:15" s="13" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="446" spans="1:15" s="13" customFormat="1" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A446" s="29" t="s">
         <v>24</v>
       </c>
@@ -35990,7 +35916,7 @@
       <c r="N446" s="9"/>
       <c r="O446" s="12"/>
     </row>
-    <row r="447" spans="1:15" s="13" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="447" spans="1:15" s="13" customFormat="1" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A447" s="29" t="s">
         <v>67</v>
       </c>
@@ -36023,7 +35949,7 @@
       <c r="N447" s="9"/>
       <c r="O447" s="12"/>
     </row>
-    <row r="448" spans="1:15" s="13" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="448" spans="1:15" s="13" customFormat="1" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A448" s="29" t="s">
         <v>24</v>
       </c>
@@ -36052,7 +35978,7 @@
       <c r="N448" s="9"/>
       <c r="O448" s="12"/>
     </row>
-    <row r="449" spans="1:15" s="13" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="449" spans="1:15" s="13" customFormat="1" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A449" s="29" t="s">
         <v>24</v>
       </c>
@@ -36085,7 +36011,7 @@
       <c r="N449" s="9"/>
       <c r="O449" s="12"/>
     </row>
-    <row r="450" spans="1:15" s="13" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="450" spans="1:15" s="13" customFormat="1" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A450" s="29" t="s">
         <v>238</v>
       </c>
@@ -36118,7 +36044,7 @@
       <c r="N450" s="9"/>
       <c r="O450" s="12"/>
     </row>
-    <row r="451" spans="1:15" s="13" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="451" spans="1:15" s="13" customFormat="1" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A451" s="29" t="s">
         <v>238</v>
       </c>
@@ -36151,7 +36077,7 @@
       <c r="N451" s="9"/>
       <c r="O451" s="12"/>
     </row>
-    <row r="452" spans="1:15" s="13" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="452" spans="1:15" s="13" customFormat="1" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A452" s="29" t="s">
         <v>238</v>
       </c>
@@ -36184,7 +36110,7 @@
       <c r="N452" s="9"/>
       <c r="O452" s="12"/>
     </row>
-    <row r="453" spans="1:15" s="13" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="453" spans="1:15" s="13" customFormat="1" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A453" s="29" t="s">
         <v>238</v>
       </c>
@@ -36217,7 +36143,7 @@
       <c r="N453" s="9"/>
       <c r="O453" s="12"/>
     </row>
-    <row r="454" spans="1:15" s="13" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="454" spans="1:15" s="13" customFormat="1" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A454" s="29" t="s">
         <v>238</v>
       </c>
@@ -36246,7 +36172,7 @@
       <c r="N454" s="9"/>
       <c r="O454" s="12"/>
     </row>
-    <row r="455" spans="1:15" s="13" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="455" spans="1:15" s="13" customFormat="1" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A455" s="29" t="s">
         <v>238</v>
       </c>
@@ -36275,7 +36201,7 @@
       <c r="N455" s="9"/>
       <c r="O455" s="12"/>
     </row>
-    <row r="456" spans="1:15" s="13" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="456" spans="1:15" s="13" customFormat="1" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A456" s="29" t="s">
         <v>32</v>
       </c>
@@ -36308,7 +36234,7 @@
       <c r="N456" s="9"/>
       <c r="O456" s="12"/>
     </row>
-    <row r="457" spans="1:15" s="13" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="457" spans="1:15" s="13" customFormat="1" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A457" s="29" t="s">
         <v>28</v>
       </c>
@@ -36341,7 +36267,7 @@
       <c r="N457" s="9"/>
       <c r="O457" s="12"/>
     </row>
-    <row r="458" spans="1:15" s="13" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="458" spans="1:15" s="13" customFormat="1" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A458" s="29" t="s">
         <v>28</v>
       </c>
@@ -36374,7 +36300,7 @@
       <c r="N458" s="9"/>
       <c r="O458" s="12"/>
     </row>
-    <row r="459" spans="1:15" s="13" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="459" spans="1:15" s="13" customFormat="1" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A459" s="29" t="s">
         <v>28</v>
       </c>
@@ -36407,7 +36333,7 @@
       <c r="N459" s="9"/>
       <c r="O459" s="12"/>
     </row>
-    <row r="460" spans="1:15" s="13" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="460" spans="1:15" s="13" customFormat="1" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A460" s="29" t="s">
         <v>28</v>
       </c>
@@ -36440,7 +36366,7 @@
       <c r="N460" s="9"/>
       <c r="O460" s="12"/>
     </row>
-    <row r="461" spans="1:15" s="13" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="461" spans="1:15" s="13" customFormat="1" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A461" s="29" t="s">
         <v>28</v>
       </c>
@@ -36473,7 +36399,7 @@
       <c r="N461" s="9"/>
       <c r="O461" s="12"/>
     </row>
-    <row r="462" spans="1:15" s="13" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="462" spans="1:15" s="13" customFormat="1" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A462" s="29" t="s">
         <v>28</v>
       </c>
@@ -36502,7 +36428,7 @@
       <c r="N462" s="9"/>
       <c r="O462" s="12"/>
     </row>
-    <row r="463" spans="1:15" s="13" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="463" spans="1:15" s="13" customFormat="1" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A463" s="29" t="s">
         <v>32</v>
       </c>
@@ -36535,7 +36461,7 @@
       <c r="N463" s="9"/>
       <c r="O463" s="12"/>
     </row>
-    <row r="464" spans="1:15" s="13" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="464" spans="1:15" s="13" customFormat="1" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A464" s="29" t="s">
         <v>32</v>
       </c>
@@ -36568,7 +36494,7 @@
       <c r="N464" s="9"/>
       <c r="O464" s="12"/>
     </row>
-    <row r="465" spans="1:15" s="13" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="465" spans="1:15" s="13" customFormat="1" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A465" s="29" t="s">
         <v>32</v>
       </c>
@@ -36601,7 +36527,7 @@
       <c r="N465" s="9"/>
       <c r="O465" s="12"/>
     </row>
-    <row r="466" spans="1:15" s="13" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="466" spans="1:15" s="13" customFormat="1" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A466" s="29" t="s">
         <v>32</v>
       </c>
@@ -36634,7 +36560,7 @@
       <c r="N466" s="9"/>
       <c r="O466" s="12"/>
     </row>
-    <row r="467" spans="1:15" s="13" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="467" spans="1:15" s="13" customFormat="1" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A467" s="29" t="s">
         <v>32</v>
       </c>
@@ -36667,7 +36593,7 @@
       <c r="N467" s="9"/>
       <c r="O467" s="12"/>
     </row>
-    <row r="468" spans="1:15" s="13" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="468" spans="1:15" s="13" customFormat="1" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A468" s="29" t="s">
         <v>32</v>
       </c>
@@ -36700,7 +36626,7 @@
       <c r="N468" s="9"/>
       <c r="O468" s="12"/>
     </row>
-    <row r="469" spans="1:15" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="469" spans="1:15" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A469" s="29" t="s">
         <v>32</v>
       </c>
@@ -36728,7 +36654,7 @@
       <c r="J469" s="9"/>
       <c r="K469" s="7"/>
     </row>
-    <row r="470" spans="1:15" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="470" spans="1:15" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A470" s="29" t="s">
         <v>32</v>
       </c>
@@ -36756,7 +36682,7 @@
       <c r="J470" s="9"/>
       <c r="K470" s="7"/>
     </row>
-    <row r="471" spans="1:15" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="471" spans="1:15" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A471" s="29" t="s">
         <v>28</v>
       </c>
@@ -36784,7 +36710,7 @@
       <c r="J471" s="9"/>
       <c r="K471" s="7"/>
     </row>
-    <row r="472" spans="1:15" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="472" spans="1:15" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A472" s="29" t="s">
         <v>313</v>
       </c>
@@ -36812,7 +36738,7 @@
       <c r="J472" s="9"/>
       <c r="K472" s="7"/>
     </row>
-    <row r="473" spans="1:15" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="473" spans="1:15" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A473" s="29" t="s">
         <v>52</v>
       </c>
@@ -36840,7 +36766,7 @@
       <c r="J473" s="9"/>
       <c r="K473" s="7"/>
     </row>
-    <row r="474" spans="1:15" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="474" spans="1:15" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A474" s="29" t="s">
         <v>52</v>
       </c>
@@ -36868,7 +36794,7 @@
       <c r="J474" s="9"/>
       <c r="K474" s="7"/>
     </row>
-    <row r="475" spans="1:15" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="475" spans="1:15" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A475" s="29" t="s">
         <v>52</v>
       </c>
@@ -36896,7 +36822,7 @@
       <c r="J475" s="9"/>
       <c r="K475" s="7"/>
     </row>
-    <row r="476" spans="1:15" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="476" spans="1:15" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A476" s="29" t="s">
         <v>52</v>
       </c>
@@ -36924,7 +36850,7 @@
       <c r="J476" s="9"/>
       <c r="K476" s="7"/>
     </row>
-    <row r="477" spans="1:15" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="477" spans="1:15" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A477" s="29" t="s">
         <v>15</v>
       </c>
@@ -36952,7 +36878,7 @@
       <c r="J477" s="9"/>
       <c r="K477" s="7"/>
     </row>
-    <row r="478" spans="1:15" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="478" spans="1:15" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A478" s="29" t="s">
         <v>60</v>
       </c>
@@ -36980,7 +36906,7 @@
       <c r="J478" s="9"/>
       <c r="K478" s="7"/>
     </row>
-    <row r="479" spans="1:15" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="479" spans="1:15" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A479" s="29" t="s">
         <v>60</v>
       </c>
@@ -37008,7 +36934,7 @@
       <c r="J479" s="9"/>
       <c r="K479" s="7"/>
     </row>
-    <row r="480" spans="1:15" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="480" spans="1:15" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A480" s="29" t="s">
         <v>60</v>
       </c>
@@ -37036,7 +36962,7 @@
       <c r="J480" s="9"/>
       <c r="K480" s="7"/>
     </row>
-    <row r="481" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="481" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A481" s="29" t="s">
         <v>60</v>
       </c>
@@ -37064,7 +36990,7 @@
       <c r="J481" s="9"/>
       <c r="K481" s="7"/>
     </row>
-    <row r="482" spans="1:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="482" spans="1:11" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A482" s="29" t="s">
         <v>60</v>
       </c>
@@ -37092,7 +37018,7 @@
       <c r="J482" s="9"/>
       <c r="K482" s="7"/>
     </row>
-    <row r="483" spans="1:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="483" spans="1:11" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A483" s="29" t="s">
         <v>60</v>
       </c>
@@ -37120,7 +37046,7 @@
       <c r="J483" s="9"/>
       <c r="K483" s="7"/>
     </row>
-    <row r="484" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="484" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A484" s="29" t="s">
         <v>52</v>
       </c>
@@ -37148,7 +37074,7 @@
       <c r="J484" s="9"/>
       <c r="K484" s="7"/>
     </row>
-    <row r="485" spans="1:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="485" spans="1:11" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A485" s="29" t="s">
         <v>60</v>
       </c>
@@ -37176,7 +37102,7 @@
       <c r="J485" s="9"/>
       <c r="K485" s="7"/>
     </row>
-    <row r="486" spans="1:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="486" spans="1:11" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A486" s="29" t="s">
         <v>28</v>
       </c>
@@ -37207,7 +37133,7 @@
       <c r="J486" s="9"/>
       <c r="K486" s="7"/>
     </row>
-    <row r="487" spans="1:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="487" spans="1:11" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A487" s="29" t="s">
         <v>15</v>
       </c>
@@ -37223,7 +37149,7 @@
       </c>
       <c r="J487" s="9"/>
     </row>
-    <row r="488" spans="1:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="488" spans="1:11" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A488" s="29" t="s">
         <v>15</v>
       </c>
@@ -37249,7 +37175,7 @@
       <c r="J488" s="9"/>
       <c r="K488" s="7"/>
     </row>
-    <row r="489" spans="1:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="489" spans="1:11" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A489" s="29" t="s">
         <v>15</v>
       </c>
@@ -37277,7 +37203,7 @@
       <c r="J489" s="9"/>
       <c r="K489" s="7"/>
     </row>
-    <row r="490" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="490" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A490" s="29" t="s">
         <v>15</v>
       </c>
@@ -37305,7 +37231,7 @@
       <c r="J490" s="9"/>
       <c r="K490" s="7"/>
     </row>
-    <row r="491" spans="1:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="491" spans="1:11" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A491" s="29" t="s">
         <v>15</v>
       </c>
@@ -37333,7 +37259,7 @@
       <c r="J491" s="9"/>
       <c r="K491" s="7"/>
     </row>
-    <row r="492" spans="1:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="492" spans="1:11" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A492" s="29" t="s">
         <v>15</v>
       </c>
@@ -37355,7 +37281,7 @@
       </c>
       <c r="J492" s="9"/>
     </row>
-    <row r="493" spans="1:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="493" spans="1:11" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A493" s="29" t="s">
         <v>15</v>
       </c>
@@ -37383,7 +37309,7 @@
       <c r="J493" s="9"/>
       <c r="K493" s="7"/>
     </row>
-    <row r="494" spans="1:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="494" spans="1:11" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A494" s="29" t="s">
         <v>15</v>
       </c>
@@ -37405,7 +37331,7 @@
       </c>
       <c r="J494" s="9"/>
     </row>
-    <row r="495" spans="1:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="495" spans="1:11" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A495" s="29" t="s">
         <v>67</v>
       </c>
@@ -37421,7 +37347,7 @@
       </c>
       <c r="J495" s="9"/>
     </row>
-    <row r="496" spans="1:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="496" spans="1:11" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A496" s="29" t="s">
         <v>67</v>
       </c>
@@ -37449,7 +37375,7 @@
       <c r="J496" s="9"/>
       <c r="K496" s="7"/>
     </row>
-    <row r="497" spans="1:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="497" spans="1:11" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A497" s="29" t="s">
         <v>67</v>
       </c>
@@ -37477,7 +37403,7 @@
       <c r="J497" s="9"/>
       <c r="K497" s="7"/>
     </row>
-    <row r="498" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="498" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A498" s="29" t="s">
         <v>67</v>
       </c>
@@ -37505,7 +37431,7 @@
       <c r="J498" s="9"/>
       <c r="K498" s="7"/>
     </row>
-    <row r="499" spans="1:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="499" spans="1:11" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A499" s="29" t="s">
         <v>67</v>
       </c>
@@ -37533,7 +37459,7 @@
       <c r="J499" s="9"/>
       <c r="K499" s="7"/>
     </row>
-    <row r="500" spans="1:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="500" spans="1:11" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A500" s="29" t="s">
         <v>67</v>
       </c>
@@ -37561,7 +37487,7 @@
       <c r="J500" s="9"/>
       <c r="K500" s="7"/>
     </row>
-    <row r="501" spans="1:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="501" spans="1:11" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A501" s="29" t="s">
         <v>67</v>
       </c>
@@ -37577,7 +37503,7 @@
       </c>
       <c r="J501" s="9"/>
     </row>
-    <row r="502" spans="1:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="502" spans="1:11" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A502" s="29" t="s">
         <v>292</v>
       </c>
@@ -37605,7 +37531,7 @@
       <c r="J502" s="9"/>
       <c r="K502" s="7"/>
     </row>
-    <row r="503" spans="1:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="503" spans="1:11" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A503" s="29" t="s">
         <v>259</v>
       </c>
@@ -37633,7 +37559,7 @@
       <c r="J503" s="9"/>
       <c r="K503" s="7"/>
     </row>
-    <row r="504" spans="1:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="504" spans="1:11" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A504" s="29" t="s">
         <v>259</v>
       </c>
@@ -37661,7 +37587,7 @@
       <c r="J504" s="9"/>
       <c r="K504" s="7"/>
     </row>
-    <row r="505" spans="1:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="505" spans="1:11" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A505" s="29" t="s">
         <v>259</v>
       </c>
@@ -37683,7 +37609,7 @@
       </c>
       <c r="J505" s="9"/>
     </row>
-    <row r="506" spans="1:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="506" spans="1:11" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A506" s="29" t="s">
         <v>259</v>
       </c>
@@ -37705,7 +37631,7 @@
       </c>
       <c r="J506" s="9"/>
     </row>
-    <row r="507" spans="1:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="507" spans="1:11" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A507" s="29" t="s">
         <v>290</v>
       </c>
@@ -37733,7 +37659,7 @@
       <c r="J507" s="9"/>
       <c r="K507" s="7"/>
     </row>
-    <row r="508" spans="1:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="508" spans="1:11" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A508" s="29" t="s">
         <v>290</v>
       </c>
@@ -37761,7 +37687,7 @@
       <c r="J508" s="9"/>
       <c r="K508" s="7"/>
     </row>
-    <row r="509" spans="1:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="509" spans="1:11" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A509" s="29" t="s">
         <v>290</v>
       </c>
@@ -37789,7 +37715,7 @@
       <c r="J509" s="9"/>
       <c r="K509" s="7"/>
     </row>
-    <row r="510" spans="1:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="510" spans="1:11" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A510" s="29" t="s">
         <v>290</v>
       </c>
@@ -37811,7 +37737,7 @@
       </c>
       <c r="J510" s="9"/>
     </row>
-    <row r="511" spans="1:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="511" spans="1:11" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A511" s="29" t="s">
         <v>292</v>
       </c>
@@ -37839,7 +37765,7 @@
       <c r="J511" s="9"/>
       <c r="K511" s="7"/>
     </row>
-    <row r="512" spans="1:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="512" spans="1:11" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A512" s="29" t="s">
         <v>292</v>
       </c>
@@ -37867,7 +37793,7 @@
       <c r="J512" s="9"/>
       <c r="K512" s="7"/>
     </row>
-    <row r="513" spans="1:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="513" spans="1:11" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A513" s="29" t="s">
         <v>292</v>
       </c>
@@ -37895,7 +37821,7 @@
       <c r="J513" s="9"/>
       <c r="K513" s="7"/>
     </row>
-    <row r="514" spans="1:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="514" spans="1:11" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A514" s="29" t="s">
         <v>290</v>
       </c>
@@ -37923,7 +37849,7 @@
       <c r="J514" s="9"/>
       <c r="K514" s="7"/>
     </row>
-    <row r="515" spans="1:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="515" spans="1:11" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A515" s="29" t="s">
         <v>24</v>
       </c>
@@ -37951,7 +37877,7 @@
       <c r="J515" s="9"/>
       <c r="K515" s="7"/>
     </row>
-    <row r="516" spans="1:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="516" spans="1:11" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A516" s="29" t="s">
         <v>24</v>
       </c>
@@ -37979,7 +37905,7 @@
       <c r="J516" s="9"/>
       <c r="K516" s="7"/>
     </row>
-    <row r="517" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="517" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A517" s="29" t="s">
         <v>24</v>
       </c>
@@ -38007,7 +37933,7 @@
       <c r="J517" s="9"/>
       <c r="K517" s="7"/>
     </row>
-    <row r="518" spans="1:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="518" spans="1:11" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A518" s="29" t="s">
         <v>24</v>
       </c>
@@ -38035,7 +37961,7 @@
       <c r="J518" s="9"/>
       <c r="K518" s="7"/>
     </row>
-    <row r="519" spans="1:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="519" spans="1:11" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A519" s="29" t="s">
         <v>24</v>
       </c>
@@ -38063,7 +37989,7 @@
       <c r="J519" s="9"/>
       <c r="K519" s="7"/>
     </row>
-    <row r="520" spans="1:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="520" spans="1:11" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A520" s="29" t="s">
         <v>24</v>
       </c>
@@ -38085,7 +38011,7 @@
       </c>
       <c r="J520" s="9"/>
     </row>
-    <row r="521" spans="1:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="521" spans="1:11" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A521" s="29" t="s">
         <v>292</v>
       </c>
@@ -38113,7 +38039,7 @@
       <c r="J521" s="9"/>
       <c r="K521" s="7"/>
     </row>
-    <row r="522" spans="1:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="522" spans="1:11" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A522" s="29" t="s">
         <v>238</v>
       </c>
@@ -38141,7 +38067,7 @@
       <c r="J522" s="9"/>
       <c r="K522" s="7"/>
     </row>
-    <row r="523" spans="1:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="523" spans="1:11" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A523" s="29" t="s">
         <v>238</v>
       </c>
@@ -38169,7 +38095,7 @@
       <c r="J523" s="9"/>
       <c r="K523" s="7"/>
     </row>
-    <row r="524" spans="1:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="524" spans="1:11" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A524" s="29" t="s">
         <v>238</v>
       </c>
@@ -38197,7 +38123,7 @@
       <c r="J524" s="9"/>
       <c r="K524" s="7"/>
     </row>
-    <row r="525" spans="1:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="525" spans="1:11" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A525" s="29" t="s">
         <v>238</v>
       </c>
@@ -38219,7 +38145,7 @@
       </c>
       <c r="J525" s="9"/>
     </row>
-    <row r="526" spans="1:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="526" spans="1:11" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A526" s="29" t="s">
         <v>238</v>
       </c>
@@ -38241,7 +38167,7 @@
       </c>
       <c r="J526" s="9"/>
     </row>
-    <row r="527" spans="1:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="527" spans="1:11" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A527" s="29" t="s">
         <v>28</v>
       </c>
@@ -38269,7 +38195,7 @@
       <c r="J527" s="9"/>
       <c r="K527" s="7"/>
     </row>
-    <row r="528" spans="1:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="528" spans="1:11" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A528" s="29" t="s">
         <v>28</v>
       </c>
@@ -38297,7 +38223,7 @@
       <c r="J528" s="9"/>
       <c r="K528" s="7"/>
     </row>
-    <row r="529" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="529" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A529" s="29" t="s">
         <v>28</v>
       </c>
@@ -38325,7 +38251,7 @@
       <c r="J529" s="9"/>
       <c r="K529" s="7"/>
     </row>
-    <row r="530" spans="1:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="530" spans="1:11" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A530" s="29" t="s">
         <v>28</v>
       </c>
@@ -38353,7 +38279,7 @@
       <c r="J530" s="9"/>
       <c r="K530" s="7"/>
     </row>
-    <row r="531" spans="1:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="531" spans="1:11" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A531" s="29" t="s">
         <v>28</v>
       </c>
@@ -38384,7 +38310,7 @@
       <c r="J531" s="9"/>
       <c r="K531" s="7"/>
     </row>
-    <row r="532" spans="1:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="532" spans="1:11" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A532" s="29" t="s">
         <v>28</v>
       </c>
@@ -38403,7 +38329,7 @@
       </c>
       <c r="J532" s="9"/>
     </row>
-    <row r="533" spans="1:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="533" spans="1:11" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A533" s="29" t="s">
         <v>32</v>
       </c>
@@ -38419,7 +38345,7 @@
       </c>
       <c r="J533" s="9"/>
     </row>
-    <row r="534" spans="1:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="534" spans="1:11" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A534" s="29" t="s">
         <v>32</v>
       </c>
@@ -38447,7 +38373,7 @@
       <c r="J534" s="9"/>
       <c r="K534" s="7"/>
     </row>
-    <row r="535" spans="1:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="535" spans="1:11" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A535" s="29" t="s">
         <v>32</v>
       </c>
@@ -38475,7 +38401,7 @@
       <c r="J535" s="9"/>
       <c r="K535" s="7"/>
     </row>
-    <row r="536" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="536" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A536" s="29" t="s">
         <v>32</v>
       </c>
@@ -38503,7 +38429,7 @@
       <c r="J536" s="9"/>
       <c r="K536" s="7"/>
     </row>
-    <row r="537" spans="1:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="537" spans="1:11" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A537" s="29" t="s">
         <v>32</v>
       </c>
@@ -38531,7 +38457,7 @@
       <c r="J537" s="9"/>
       <c r="K537" s="7"/>
     </row>
-    <row r="538" spans="1:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="538" spans="1:11" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A538" s="29" t="s">
         <v>32</v>
       </c>
@@ -38557,7 +38483,7 @@
       <c r="J538" s="9"/>
       <c r="K538" s="7"/>
     </row>
-    <row r="539" spans="1:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="539" spans="1:11" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A539" s="29" t="s">
         <v>32</v>
       </c>
@@ -38585,7 +38511,7 @@
       <c r="J539" s="9"/>
       <c r="K539" s="7"/>
     </row>
-    <row r="540" spans="1:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="540" spans="1:11" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A540" s="29" t="s">
         <v>32</v>
       </c>
@@ -38604,7 +38530,7 @@
       </c>
       <c r="J540" s="9"/>
     </row>
-    <row r="541" spans="1:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="541" spans="1:11" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A541" s="29" t="s">
         <v>32</v>
       </c>
@@ -38623,7 +38549,7 @@
       </c>
       <c r="J541" s="9"/>
     </row>
-    <row r="542" spans="1:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="542" spans="1:11" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A542" s="29" t="s">
         <v>52</v>
       </c>
@@ -38651,7 +38577,7 @@
       <c r="J542" s="9"/>
       <c r="K542" s="7"/>
     </row>
-    <row r="543" spans="1:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="543" spans="1:11" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A543" s="29" t="s">
         <v>52</v>
       </c>
@@ -38679,7 +38605,7 @@
       <c r="J543" s="9"/>
       <c r="K543" s="7"/>
     </row>
-    <row r="544" spans="1:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="544" spans="1:11" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A544" s="29" t="s">
         <v>52</v>
       </c>
@@ -38707,7 +38633,7 @@
       <c r="J544" s="9"/>
       <c r="K544" s="7"/>
     </row>
-    <row r="545" spans="1:15" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="545" spans="1:15" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A545" s="29" t="s">
         <v>52</v>
       </c>
@@ -38735,7 +38661,7 @@
       <c r="J545" s="9"/>
       <c r="K545" s="7"/>
     </row>
-    <row r="546" spans="1:15" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="546" spans="1:15" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A546" s="29" t="s">
         <v>60</v>
       </c>
@@ -38763,7 +38689,7 @@
       <c r="J546" s="9"/>
       <c r="K546" s="7"/>
     </row>
-    <row r="547" spans="1:15" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="547" spans="1:15" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A547" s="29" t="s">
         <v>60</v>
       </c>
@@ -38791,7 +38717,7 @@
       <c r="J547" s="9"/>
       <c r="K547" s="7"/>
     </row>
-    <row r="548" spans="1:15" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="548" spans="1:15" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A548" s="29" t="s">
         <v>60</v>
       </c>
@@ -38819,7 +38745,7 @@
       <c r="J548" s="9"/>
       <c r="K548" s="7"/>
     </row>
-    <row r="549" spans="1:15" s="3" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="549" spans="1:15" s="3" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A549" s="29" t="s">
         <v>60</v>
       </c>
@@ -38849,7 +38775,7 @@
       <c r="L549" s="17"/>
       <c r="O549" s="17"/>
     </row>
-    <row r="550" spans="1:15" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="550" spans="1:15" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A550" s="29" t="s">
         <v>60</v>
       </c>
@@ -38877,7 +38803,7 @@
       <c r="J550" s="9"/>
       <c r="K550" s="7"/>
     </row>
-    <row r="551" spans="1:15" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="551" spans="1:15" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A551" s="29" t="s">
         <v>60</v>
       </c>
@@ -38905,7 +38831,7 @@
       <c r="J551" s="9"/>
       <c r="K551" s="7"/>
     </row>
-    <row r="552" spans="1:15" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="552" spans="1:15" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A552" s="29" t="s">
         <v>60</v>
       </c>
@@ -38927,7 +38853,7 @@
       </c>
       <c r="J552" s="9"/>
     </row>
-    <row r="553" spans="1:15" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="553" spans="1:15" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A553" s="29" t="s">
         <v>60</v>
       </c>
@@ -38955,7 +38881,7 @@
       <c r="J553" s="9"/>
       <c r="K553" s="7"/>
     </row>
-    <row r="554" spans="1:15" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="554" spans="1:15" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A554" s="29" t="s">
         <v>60</v>
       </c>
@@ -38983,7 +38909,7 @@
       <c r="J554" s="9"/>
       <c r="K554" s="7"/>
     </row>
-    <row r="555" spans="1:15" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="555" spans="1:15" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A555" s="29" t="s">
         <v>15</v>
       </c>
@@ -39011,7 +38937,7 @@
       <c r="J555" s="9"/>
       <c r="K555" s="7"/>
     </row>
-    <row r="556" spans="1:15" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="556" spans="1:15" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A556" s="29" t="s">
         <v>15</v>
       </c>
@@ -39027,7 +38953,7 @@
       </c>
       <c r="J556" s="9"/>
     </row>
-    <row r="557" spans="1:15" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="557" spans="1:15" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A557" s="29" t="s">
         <v>15</v>
       </c>
@@ -39053,7 +38979,7 @@
       <c r="J557" s="9"/>
       <c r="K557" s="7"/>
     </row>
-    <row r="558" spans="1:15" s="3" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="558" spans="1:15" s="3" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A558" s="29" t="s">
         <v>15</v>
       </c>
@@ -39081,7 +39007,7 @@
       <c r="L558" s="17"/>
       <c r="O558" s="17"/>
     </row>
-    <row r="559" spans="1:15" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="559" spans="1:15" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A559" s="29" t="s">
         <v>15</v>
       </c>
@@ -39109,7 +39035,7 @@
       <c r="J559" s="9"/>
       <c r="K559" s="7"/>
     </row>
-    <row r="560" spans="1:15" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="560" spans="1:15" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A560" s="29" t="s">
         <v>15</v>
       </c>
@@ -39137,7 +39063,7 @@
       <c r="J560" s="9"/>
       <c r="K560" s="7"/>
     </row>
-    <row r="561" spans="1:15" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="561" spans="1:15" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A561" s="29" t="s">
         <v>15</v>
       </c>
@@ -39159,7 +39085,7 @@
       </c>
       <c r="J561" s="9"/>
     </row>
-    <row r="562" spans="1:15" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="562" spans="1:15" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A562" s="29" t="s">
         <v>15</v>
       </c>
@@ -39187,7 +39113,7 @@
       <c r="J562" s="9"/>
       <c r="K562" s="7"/>
     </row>
-    <row r="563" spans="1:15" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="563" spans="1:15" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A563" s="29" t="s">
         <v>15</v>
       </c>
@@ -39215,7 +39141,7 @@
       <c r="J563" s="9"/>
       <c r="K563" s="7"/>
     </row>
-    <row r="564" spans="1:15" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="564" spans="1:15" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A564" s="29" t="s">
         <v>67</v>
       </c>
@@ -39243,7 +39169,7 @@
       <c r="J564" s="9"/>
       <c r="K564" s="7"/>
     </row>
-    <row r="565" spans="1:15" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="565" spans="1:15" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A565" s="29" t="s">
         <v>67</v>
       </c>
@@ -39271,7 +39197,7 @@
       <c r="J565" s="9"/>
       <c r="K565" s="7"/>
     </row>
-    <row r="566" spans="1:15" s="3" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="566" spans="1:15" s="3" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A566" s="29" t="s">
         <v>67</v>
       </c>
@@ -39299,7 +39225,7 @@
       <c r="L566" s="17"/>
       <c r="O566" s="17"/>
     </row>
-    <row r="567" spans="1:15" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="567" spans="1:15" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A567" s="29" t="s">
         <v>67</v>
       </c>
@@ -39327,7 +39253,7 @@
       <c r="J567" s="9"/>
       <c r="K567" s="7"/>
     </row>
-    <row r="568" spans="1:15" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="568" spans="1:15" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A568" s="29" t="s">
         <v>67</v>
       </c>
@@ -39355,7 +39281,7 @@
       <c r="J568" s="9"/>
       <c r="K568" s="7"/>
     </row>
-    <row r="569" spans="1:15" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="569" spans="1:15" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A569" s="29" t="s">
         <v>259</v>
       </c>
@@ -39383,7 +39309,7 @@
       <c r="J569" s="9"/>
       <c r="K569" s="7"/>
     </row>
-    <row r="570" spans="1:15" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="570" spans="1:15" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A570" s="29" t="s">
         <v>259</v>
       </c>
@@ -39411,7 +39337,7 @@
       <c r="J570" s="9"/>
       <c r="K570" s="7"/>
     </row>
-    <row r="571" spans="1:15" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="571" spans="1:15" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A571" s="29" t="s">
         <v>259</v>
       </c>
@@ -39439,7 +39365,7 @@
       <c r="J571" s="9"/>
       <c r="K571" s="7"/>
     </row>
-    <row r="572" spans="1:15" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="572" spans="1:15" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A572" s="29" t="s">
         <v>259</v>
       </c>
@@ -39461,7 +39387,7 @@
       </c>
       <c r="J572" s="9"/>
     </row>
-    <row r="573" spans="1:15" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="573" spans="1:15" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A573" s="29" t="s">
         <v>259</v>
       </c>
@@ -39483,7 +39409,7 @@
       </c>
       <c r="J573" s="9"/>
     </row>
-    <row r="574" spans="1:15" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="574" spans="1:15" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A574" s="29" t="s">
         <v>290</v>
       </c>
@@ -39511,7 +39437,7 @@
       <c r="J574" s="9"/>
       <c r="K574" s="7"/>
     </row>
-    <row r="575" spans="1:15" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="575" spans="1:15" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A575" s="29" t="s">
         <v>290</v>
       </c>
@@ -39539,7 +39465,7 @@
       <c r="J575" s="9"/>
       <c r="K575" s="7"/>
     </row>
-    <row r="576" spans="1:15" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="576" spans="1:15" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A576" s="29" t="s">
         <v>290</v>
       </c>
@@ -39567,7 +39493,7 @@
       <c r="J576" s="9"/>
       <c r="K576" s="7"/>
     </row>
-    <row r="577" spans="1:15" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="577" spans="1:15" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A577" s="29" t="s">
         <v>290</v>
       </c>
@@ -39595,7 +39521,7 @@
       <c r="J577" s="9"/>
       <c r="K577" s="7"/>
     </row>
-    <row r="578" spans="1:15" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="578" spans="1:15" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A578" s="29" t="s">
         <v>290</v>
       </c>
@@ -39617,7 +39543,7 @@
       </c>
       <c r="J578" s="9"/>
     </row>
-    <row r="579" spans="1:15" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="579" spans="1:15" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A579" s="29" t="s">
         <v>292</v>
       </c>
@@ -39645,7 +39571,7 @@
       <c r="J579" s="9"/>
       <c r="K579" s="7"/>
     </row>
-    <row r="580" spans="1:15" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="580" spans="1:15" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A580" s="29" t="s">
         <v>292</v>
       </c>
@@ -39673,7 +39599,7 @@
       <c r="J580" s="9"/>
       <c r="K580" s="7"/>
     </row>
-    <row r="581" spans="1:15" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="581" spans="1:15" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A581" s="29" t="s">
         <v>292</v>
       </c>
@@ -39701,7 +39627,7 @@
       <c r="J581" s="9"/>
       <c r="K581" s="7"/>
     </row>
-    <row r="582" spans="1:15" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="582" spans="1:15" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A582" s="29" t="s">
         <v>290</v>
       </c>
@@ -39729,7 +39655,7 @@
       <c r="J582" s="9"/>
       <c r="K582" s="7"/>
     </row>
-    <row r="583" spans="1:15" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="583" spans="1:15" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A583" s="29" t="s">
         <v>24</v>
       </c>
@@ -39757,7 +39683,7 @@
       <c r="J583" s="9"/>
       <c r="K583" s="7"/>
     </row>
-    <row r="584" spans="1:15" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="584" spans="1:15" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A584" s="29" t="s">
         <v>24</v>
       </c>
@@ -39785,7 +39711,7 @@
       <c r="J584" s="9"/>
       <c r="K584" s="7"/>
     </row>
-    <row r="585" spans="1:15" s="3" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="585" spans="1:15" s="3" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A585" s="29" t="s">
         <v>24</v>
       </c>
@@ -39813,7 +39739,7 @@
       <c r="L585" s="17"/>
       <c r="O585" s="17"/>
     </row>
-    <row r="586" spans="1:15" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="586" spans="1:15" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A586" s="29" t="s">
         <v>24</v>
       </c>
@@ -39841,7 +39767,7 @@
       <c r="J586" s="9"/>
       <c r="K586" s="7"/>
     </row>
-    <row r="587" spans="1:15" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="587" spans="1:15" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A587" s="29" t="s">
         <v>24</v>
       </c>
@@ -39869,7 +39795,7 @@
       <c r="J587" s="9"/>
       <c r="K587" s="7"/>
     </row>
-    <row r="588" spans="1:15" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="588" spans="1:15" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A588" s="29" t="s">
         <v>24</v>
       </c>
@@ -39891,7 +39817,7 @@
       </c>
       <c r="J588" s="9"/>
     </row>
-    <row r="589" spans="1:15" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="589" spans="1:15" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A589" s="29" t="s">
         <v>24</v>
       </c>
@@ -39919,7 +39845,7 @@
       <c r="J589" s="9"/>
       <c r="K589" s="7"/>
     </row>
-    <row r="590" spans="1:15" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="590" spans="1:15" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A590" s="29" t="s">
         <v>24</v>
       </c>
@@ -39947,7 +39873,7 @@
       <c r="J590" s="9"/>
       <c r="K590" s="7"/>
     </row>
-    <row r="591" spans="1:15" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="591" spans="1:15" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A591" s="29" t="s">
         <v>238</v>
       </c>
@@ -39975,7 +39901,7 @@
       <c r="J591" s="9"/>
       <c r="K591" s="7"/>
     </row>
-    <row r="592" spans="1:15" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="592" spans="1:15" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A592" s="29" t="s">
         <v>238</v>
       </c>
@@ -40003,7 +39929,7 @@
       <c r="J592" s="9"/>
       <c r="K592" s="7"/>
     </row>
-    <row r="593" spans="1:15" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="593" spans="1:15" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A593" s="29" t="s">
         <v>238</v>
       </c>
@@ -40031,7 +39957,7 @@
       <c r="J593" s="9"/>
       <c r="K593" s="7"/>
     </row>
-    <row r="594" spans="1:15" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="594" spans="1:15" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A594" s="29" t="s">
         <v>238</v>
       </c>
@@ -40053,7 +39979,7 @@
       </c>
       <c r="J594" s="9"/>
     </row>
-    <row r="595" spans="1:15" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="595" spans="1:15" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A595" s="29" t="s">
         <v>238</v>
       </c>
@@ -40075,7 +40001,7 @@
       </c>
       <c r="J595" s="9"/>
     </row>
-    <row r="596" spans="1:15" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="596" spans="1:15" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A596" s="29" t="s">
         <v>28</v>
       </c>
@@ -40103,7 +40029,7 @@
       <c r="J596" s="9"/>
       <c r="K596" s="7"/>
     </row>
-    <row r="597" spans="1:15" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="597" spans="1:15" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A597" s="29" t="s">
         <v>28</v>
       </c>
@@ -40131,7 +40057,7 @@
       <c r="J597" s="9"/>
       <c r="K597" s="7"/>
     </row>
-    <row r="598" spans="1:15" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="598" spans="1:15" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A598" s="29" t="s">
         <v>28</v>
       </c>
@@ -40159,7 +40085,7 @@
       <c r="J598" s="9"/>
       <c r="K598" s="7"/>
     </row>
-    <row r="599" spans="1:15" s="3" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="599" spans="1:15" s="3" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A599" s="29" t="s">
         <v>28</v>
       </c>
@@ -40185,7 +40111,7 @@
       <c r="L599" s="17"/>
       <c r="O599" s="17"/>
     </row>
-    <row r="600" spans="1:15" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="600" spans="1:15" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A600" s="29" t="s">
         <v>28</v>
       </c>
@@ -40213,7 +40139,7 @@
       <c r="J600" s="9"/>
       <c r="K600" s="7"/>
     </row>
-    <row r="601" spans="1:15" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="601" spans="1:15" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A601" s="29" t="s">
         <v>28</v>
       </c>
@@ -40241,7 +40167,7 @@
       <c r="J601" s="9"/>
       <c r="K601" s="7"/>
     </row>
-    <row r="602" spans="1:15" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="602" spans="1:15" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A602" s="29" t="s">
         <v>28</v>
       </c>
@@ -40262,7 +40188,7 @@
       </c>
       <c r="J602" s="9"/>
     </row>
-    <row r="603" spans="1:15" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="603" spans="1:15" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A603" s="29" t="s">
         <v>32</v>
       </c>
@@ -40290,7 +40216,7 @@
       <c r="J603" s="9"/>
       <c r="K603" s="7"/>
     </row>
-    <row r="604" spans="1:15" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="604" spans="1:15" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A604" s="29" t="s">
         <v>32</v>
       </c>
@@ -40318,7 +40244,7 @@
       <c r="J604" s="9"/>
       <c r="K604" s="7"/>
     </row>
-    <row r="605" spans="1:15" s="3" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="605" spans="1:15" s="3" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A605" s="29" t="s">
         <v>32</v>
       </c>
@@ -40346,7 +40272,7 @@
       <c r="L605" s="17"/>
       <c r="O605" s="17"/>
     </row>
-    <row r="606" spans="1:15" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="606" spans="1:15" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A606" s="29" t="s">
         <v>32</v>
       </c>
@@ -40374,7 +40300,7 @@
       <c r="J606" s="9"/>
       <c r="K606" s="7"/>
     </row>
-    <row r="607" spans="1:15" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="607" spans="1:15" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A607" s="29" t="s">
         <v>32</v>
       </c>
@@ -40399,7 +40325,7 @@
       <c r="J607" s="9"/>
       <c r="K607" s="7"/>
     </row>
-    <row r="608" spans="1:15" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="608" spans="1:15" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A608" s="29" t="s">
         <v>32</v>
       </c>
@@ -40427,7 +40353,7 @@
       <c r="J608" s="9"/>
       <c r="K608" s="7"/>
     </row>
-    <row r="609" spans="1:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="609" spans="1:11" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A609" s="29" t="s">
         <v>32</v>
       </c>
@@ -40448,7 +40374,7 @@
       </c>
       <c r="J609" s="9"/>
     </row>
-    <row r="610" spans="1:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="610" spans="1:11" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A610" s="29" t="s">
         <v>32</v>
       </c>
@@ -40469,7 +40395,7 @@
       </c>
       <c r="J610" s="9"/>
     </row>
-    <row r="611" spans="1:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="611" spans="1:11" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A611" s="29" t="s">
         <v>259</v>
       </c>
@@ -40491,7 +40417,7 @@
       </c>
       <c r="J611" s="9"/>
     </row>
-    <row r="612" spans="1:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="612" spans="1:11" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A612" s="29" t="s">
         <v>290</v>
       </c>
@@ -40519,7 +40445,7 @@
       <c r="J612" s="9"/>
       <c r="K612" s="7"/>
     </row>
-    <row r="613" spans="1:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="613" spans="1:11" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A613" s="29" t="s">
         <v>292</v>
       </c>
@@ -40547,7 +40473,7 @@
       <c r="J613" s="9"/>
       <c r="K613" s="7"/>
     </row>
-    <row r="614" spans="1:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="614" spans="1:11" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A614" s="29" t="s">
         <v>67</v>
       </c>
@@ -40575,7 +40501,7 @@
       <c r="J614" s="9"/>
       <c r="K614" s="7"/>
     </row>
-    <row r="615" spans="1:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="615" spans="1:11" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A615" s="29" t="s">
         <v>238</v>
       </c>
@@ -40603,7 +40529,7 @@
       <c r="J615" s="9"/>
       <c r="K615" s="7"/>
     </row>
-    <row r="616" spans="1:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="616" spans="1:11" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A616" s="29" t="s">
         <v>52</v>
       </c>
@@ -40631,7 +40557,7 @@
       <c r="J616" s="9"/>
       <c r="K616" s="7"/>
     </row>
-    <row r="617" spans="1:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="617" spans="1:11" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A617" s="29" t="s">
         <v>52</v>
       </c>
@@ -40659,7 +40585,7 @@
       <c r="J617" s="9"/>
       <c r="K617" s="7"/>
     </row>
-    <row r="618" spans="1:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="618" spans="1:11" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A618" s="29" t="s">
         <v>60</v>
       </c>
@@ -40687,7 +40613,7 @@
       <c r="J618" s="9"/>
       <c r="K618" s="7"/>
     </row>
-    <row r="619" spans="1:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="619" spans="1:11" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A619" s="29" t="s">
         <v>60</v>
       </c>
@@ -40715,7 +40641,7 @@
       <c r="J619" s="9"/>
       <c r="K619" s="7"/>
     </row>
-    <row r="620" spans="1:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="620" spans="1:11" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A620" s="29" t="s">
         <v>60</v>
       </c>
@@ -40743,7 +40669,7 @@
       <c r="J620" s="9"/>
       <c r="K620" s="7"/>
     </row>
-    <row r="621" spans="1:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="621" spans="1:11" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A621" s="29" t="s">
         <v>60</v>
       </c>
@@ -40771,7 +40697,7 @@
       <c r="J621" s="9"/>
       <c r="K621" s="7"/>
     </row>
-    <row r="622" spans="1:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="622" spans="1:11" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A622" s="29" t="s">
         <v>15</v>
       </c>
@@ -40799,7 +40725,7 @@
       <c r="J622" s="9"/>
       <c r="K622" s="7"/>
     </row>
-    <row r="623" spans="1:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="623" spans="1:11" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A623" s="29" t="s">
         <v>15</v>
       </c>
@@ -40827,7 +40753,7 @@
       <c r="J623" s="9"/>
       <c r="K623" s="7"/>
     </row>
-    <row r="624" spans="1:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="624" spans="1:11" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A624" s="29" t="s">
         <v>15</v>
       </c>
@@ -40855,7 +40781,7 @@
       <c r="J624" s="9"/>
       <c r="K624" s="7"/>
     </row>
-    <row r="625" spans="1:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="625" spans="1:11" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A625" s="29" t="s">
         <v>67</v>
       </c>
@@ -40883,7 +40809,7 @@
       <c r="J625" s="9"/>
       <c r="K625" s="7"/>
     </row>
-    <row r="626" spans="1:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="626" spans="1:11" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A626" s="29" t="s">
         <v>24</v>
       </c>
@@ -40911,7 +40837,7 @@
       <c r="J626" s="9"/>
       <c r="K626" s="7"/>
     </row>
-    <row r="627" spans="1:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="627" spans="1:11" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A627" s="29" t="s">
         <v>24</v>
       </c>
@@ -40939,7 +40865,7 @@
       <c r="J627" s="9"/>
       <c r="K627" s="7"/>
     </row>
-    <row r="628" spans="1:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="628" spans="1:11" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A628" s="29" t="s">
         <v>28</v>
       </c>
@@ -40967,7 +40893,7 @@
       <c r="J628" s="9"/>
       <c r="K628" s="7"/>
     </row>
-    <row r="629" spans="1:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="629" spans="1:11" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A629" s="29" t="s">
         <v>32</v>
       </c>
@@ -40995,7 +40921,7 @@
       <c r="J629" s="9"/>
       <c r="K629" s="7"/>
     </row>
-    <row r="630" spans="1:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="630" spans="1:11" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A630" s="29" t="s">
         <v>52</v>
       </c>
@@ -41023,7 +40949,7 @@
       <c r="J630" s="9"/>
       <c r="K630" s="7"/>
     </row>
-    <row r="631" spans="1:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="631" spans="1:11" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A631" s="29" t="s">
         <v>52</v>
       </c>
@@ -41051,7 +40977,7 @@
       <c r="J631" s="9"/>
       <c r="K631" s="7"/>
     </row>
-    <row r="632" spans="1:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="632" spans="1:11" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A632" s="29" t="s">
         <v>60</v>
       </c>
@@ -41079,7 +41005,7 @@
       <c r="J632" s="9"/>
       <c r="K632" s="7"/>
     </row>
-    <row r="633" spans="1:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="633" spans="1:11" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A633" s="29" t="s">
         <v>60</v>
       </c>
@@ -41107,7 +41033,7 @@
       <c r="J633" s="9"/>
       <c r="K633" s="7"/>
     </row>
-    <row r="634" spans="1:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="634" spans="1:11" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A634" s="29" t="s">
         <v>60</v>
       </c>
@@ -41135,7 +41061,7 @@
       <c r="J634" s="9"/>
       <c r="K634" s="7"/>
     </row>
-    <row r="635" spans="1:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="635" spans="1:11" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A635" s="29" t="s">
         <v>60</v>
       </c>
@@ -41163,7 +41089,7 @@
       <c r="J635" s="9"/>
       <c r="K635" s="7"/>
     </row>
-    <row r="636" spans="1:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="636" spans="1:11" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A636" s="29" t="s">
         <v>15</v>
       </c>
@@ -41191,7 +41117,7 @@
       <c r="J636" s="9"/>
       <c r="K636" s="7"/>
     </row>
-    <row r="637" spans="1:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="637" spans="1:11" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A637" s="29" t="s">
         <v>15</v>
       </c>
@@ -41219,7 +41145,7 @@
       <c r="J637" s="9"/>
       <c r="K637" s="7"/>
     </row>
-    <row r="638" spans="1:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="638" spans="1:11" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A638" s="29" t="s">
         <v>15</v>
       </c>
@@ -41247,7 +41173,7 @@
       <c r="J638" s="9"/>
       <c r="K638" s="7"/>
     </row>
-    <row r="639" spans="1:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="639" spans="1:11" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A639" s="29" t="s">
         <v>67</v>
       </c>
@@ -41275,7 +41201,7 @@
       <c r="J639" s="9"/>
       <c r="K639" s="7"/>
     </row>
-    <row r="640" spans="1:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="640" spans="1:11" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A640" s="29" t="s">
         <v>24</v>
       </c>
@@ -41303,7 +41229,7 @@
       <c r="J640" s="9"/>
       <c r="K640" s="7"/>
     </row>
-    <row r="641" spans="1:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="641" spans="1:11" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A641" s="29" t="s">
         <v>24</v>
       </c>
@@ -41331,7 +41257,7 @@
       <c r="J641" s="9"/>
       <c r="K641" s="7"/>
     </row>
-    <row r="642" spans="1:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="642" spans="1:11" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A642" s="29" t="s">
         <v>28</v>
       </c>
@@ -41359,7 +41285,7 @@
       <c r="J642" s="9"/>
       <c r="K642" s="7"/>
     </row>
-    <row r="643" spans="1:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="643" spans="1:11" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A643" s="29" t="s">
         <v>52</v>
       </c>
@@ -41388,7 +41314,7 @@
       <c r="J643" s="9"/>
       <c r="K643" s="7"/>
     </row>
-    <row r="644" spans="1:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="644" spans="1:11" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A644" s="29" t="s">
         <v>52</v>
       </c>
@@ -41417,7 +41343,7 @@
       <c r="J644" s="9"/>
       <c r="K644" s="7"/>
     </row>
-    <row r="645" spans="1:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="645" spans="1:11" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A645" s="29" t="s">
         <v>60</v>
       </c>
@@ -41446,7 +41372,7 @@
       <c r="J645" s="9"/>
       <c r="K645" s="7"/>
     </row>
-    <row r="646" spans="1:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="646" spans="1:11" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A646" s="29" t="s">
         <v>60</v>
       </c>
@@ -41475,7 +41401,7 @@
       <c r="J646" s="9"/>
       <c r="K646" s="7"/>
     </row>
-    <row r="647" spans="1:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="647" spans="1:11" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A647" s="29" t="s">
         <v>60</v>
       </c>
@@ -41504,7 +41430,7 @@
       <c r="J647" s="9"/>
       <c r="K647" s="7"/>
     </row>
-    <row r="648" spans="1:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="648" spans="1:11" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A648" s="29" t="s">
         <v>60</v>
       </c>
@@ -41533,7 +41459,7 @@
       <c r="J648" s="9"/>
       <c r="K648" s="7"/>
     </row>
-    <row r="649" spans="1:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="649" spans="1:11" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A649" s="29" t="s">
         <v>15</v>
       </c>
@@ -41562,7 +41488,7 @@
       <c r="J649" s="9"/>
       <c r="K649" s="7"/>
     </row>
-    <row r="650" spans="1:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="650" spans="1:11" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A650" s="29" t="s">
         <v>15</v>
       </c>
@@ -41591,7 +41517,7 @@
       <c r="J650" s="9"/>
       <c r="K650" s="7"/>
     </row>
-    <row r="651" spans="1:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="651" spans="1:11" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A651" s="29" t="s">
         <v>15</v>
       </c>
@@ -41620,7 +41546,7 @@
       <c r="J651" s="9"/>
       <c r="K651" s="7"/>
     </row>
-    <row r="652" spans="1:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="652" spans="1:11" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A652" s="29" t="s">
         <v>67</v>
       </c>
@@ -41649,7 +41575,7 @@
       <c r="J652" s="9"/>
       <c r="K652" s="7"/>
     </row>
-    <row r="653" spans="1:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="653" spans="1:11" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A653" s="29" t="s">
         <v>24</v>
       </c>
@@ -41678,7 +41604,7 @@
       <c r="J653" s="9"/>
       <c r="K653" s="7"/>
     </row>
-    <row r="654" spans="1:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="654" spans="1:11" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A654" s="29" t="s">
         <v>24</v>
       </c>
@@ -41707,7 +41633,7 @@
       <c r="J654" s="9"/>
       <c r="K654" s="7"/>
     </row>
-    <row r="655" spans="1:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="655" spans="1:11" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A655" s="29" t="s">
         <v>28</v>
       </c>
@@ -41736,7 +41662,7 @@
       <c r="J655" s="9"/>
       <c r="K655" s="7"/>
     </row>
-    <row r="656" spans="1:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="656" spans="1:11" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A656" s="29" t="s">
         <v>52</v>
       </c>
@@ -41762,7 +41688,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="657" spans="1:8" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="657" spans="1:8" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A657" s="29" t="s">
         <v>52</v>
       </c>
@@ -41788,7 +41714,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="658" spans="1:8" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="658" spans="1:8" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A658" s="29" t="s">
         <v>60</v>
       </c>
@@ -41814,7 +41740,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="659" spans="1:8" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="659" spans="1:8" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A659" s="29" t="s">
         <v>60</v>
       </c>
@@ -41840,7 +41766,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="660" spans="1:8" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="660" spans="1:8" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A660" s="29" t="s">
         <v>60</v>
       </c>
@@ -41866,7 +41792,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="661" spans="1:8" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="661" spans="1:8" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A661" s="29" t="s">
         <v>60</v>
       </c>
@@ -41892,7 +41818,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="662" spans="1:8" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="662" spans="1:8" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A662" s="29" t="s">
         <v>15</v>
       </c>
@@ -41918,7 +41844,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="663" spans="1:8" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="663" spans="1:8" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A663" s="29" t="s">
         <v>15</v>
       </c>
@@ -41944,7 +41870,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="664" spans="1:8" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="664" spans="1:8" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A664" s="29" t="s">
         <v>15</v>
       </c>
@@ -41970,7 +41896,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="665" spans="1:8" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="665" spans="1:8" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A665" s="29" t="s">
         <v>67</v>
       </c>
@@ -41996,7 +41922,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="666" spans="1:8" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="666" spans="1:8" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A666" s="29" t="s">
         <v>24</v>
       </c>
@@ -42022,7 +41948,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="667" spans="1:8" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="667" spans="1:8" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A667" s="29" t="s">
         <v>24</v>
       </c>
@@ -42048,7 +41974,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="668" spans="1:8" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="668" spans="1:8" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A668" s="29" t="s">
         <v>28</v>
       </c>
@@ -42074,7 +42000,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="669" spans="1:8" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="669" spans="1:8" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A669" s="29" t="s">
         <v>52</v>
       </c>
@@ -42100,7 +42026,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="670" spans="1:8" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="670" spans="1:8" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A670" s="29" t="s">
         <v>52</v>
       </c>
@@ -42123,7 +42049,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="671" spans="1:8" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="671" spans="1:8" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A671" s="29" t="s">
         <v>52</v>
       </c>
@@ -42149,7 +42075,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="672" spans="1:8" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="672" spans="1:8" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A672" s="29" t="s">
         <v>52</v>
       </c>
@@ -42175,7 +42101,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="673" spans="1:15" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="673" spans="1:15" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A673" s="29" t="s">
         <v>60</v>
       </c>
@@ -42201,7 +42127,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="674" spans="1:15" s="3" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="674" spans="1:15" s="3" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A674" s="29" t="s">
         <v>60</v>
       </c>
@@ -42230,7 +42156,7 @@
       <c r="L674" s="17"/>
       <c r="O674" s="17"/>
     </row>
-    <row r="675" spans="1:15" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="675" spans="1:15" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A675" s="29" t="s">
         <v>60</v>
       </c>
@@ -42256,7 +42182,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="676" spans="1:15" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="676" spans="1:15" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A676" s="29" t="s">
         <v>60</v>
       </c>
@@ -42282,7 +42208,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="677" spans="1:15" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="677" spans="1:15" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A677" s="29" t="s">
         <v>60</v>
       </c>
@@ -42308,7 +42234,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="678" spans="1:15" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="678" spans="1:15" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A678" s="29" t="s">
         <v>60</v>
       </c>
@@ -42334,7 +42260,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="679" spans="1:15" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="679" spans="1:15" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A679" s="29" t="s">
         <v>60</v>
       </c>
@@ -42360,7 +42286,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="680" spans="1:15" s="3" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="680" spans="1:15" s="3" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A680" s="29" t="s">
         <v>15</v>
       </c>
@@ -42387,7 +42313,7 @@
       <c r="L680" s="17"/>
       <c r="O680" s="17"/>
     </row>
-    <row r="681" spans="1:15" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="681" spans="1:15" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A681" s="29" t="s">
         <v>15</v>
       </c>
@@ -42410,7 +42336,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="682" spans="1:15" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="682" spans="1:15" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A682" s="29" t="s">
         <v>15</v>
       </c>
@@ -42433,7 +42359,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="683" spans="1:15" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="683" spans="1:15" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A683" s="29" t="s">
         <v>15</v>
       </c>
@@ -42459,7 +42385,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="684" spans="1:15" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="684" spans="1:15" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A684" s="29" t="s">
         <v>15</v>
       </c>
@@ -42485,7 +42411,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="685" spans="1:15" s="3" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="685" spans="1:15" s="3" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A685" s="29" t="s">
         <v>67</v>
       </c>
@@ -42512,7 +42438,7 @@
       <c r="L685" s="17"/>
       <c r="O685" s="17"/>
     </row>
-    <row r="686" spans="1:15" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="686" spans="1:15" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A686" s="29" t="s">
         <v>67</v>
       </c>
@@ -42538,7 +42464,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="687" spans="1:15" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="687" spans="1:15" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A687" s="29" t="s">
         <v>67</v>
       </c>
@@ -42564,7 +42490,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="688" spans="1:15" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="688" spans="1:15" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A688" s="29" t="s">
         <v>67</v>
       </c>
@@ -42590,7 +42516,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="689" spans="1:15" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="689" spans="1:15" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A689" s="29" t="s">
         <v>67</v>
       </c>
@@ -42616,7 +42542,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="690" spans="1:15" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="690" spans="1:15" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A690" s="29" t="s">
         <v>259</v>
       </c>
@@ -42642,7 +42568,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="691" spans="1:15" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="691" spans="1:15" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A691" s="29" t="s">
         <v>259</v>
       </c>
@@ -42668,7 +42594,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="692" spans="1:15" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="692" spans="1:15" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A692" s="29" t="s">
         <v>259</v>
       </c>
@@ -42694,7 +42620,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="693" spans="1:15" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="693" spans="1:15" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A693" s="29" t="s">
         <v>67</v>
       </c>
@@ -42720,7 +42646,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="694" spans="1:15" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="694" spans="1:15" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A694" s="29" t="s">
         <v>290</v>
       </c>
@@ -42746,7 +42672,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="695" spans="1:15" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="695" spans="1:15" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A695" s="29" t="s">
         <v>290</v>
       </c>
@@ -42772,7 +42698,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="696" spans="1:15" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="696" spans="1:15" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A696" s="29" t="s">
         <v>290</v>
       </c>
@@ -42798,7 +42724,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="697" spans="1:15" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="697" spans="1:15" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A697" s="29" t="s">
         <v>290</v>
       </c>
@@ -42824,7 +42750,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="698" spans="1:15" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="698" spans="1:15" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A698" s="29" t="s">
         <v>292</v>
       </c>
@@ -42850,7 +42776,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="699" spans="1:15" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="699" spans="1:15" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A699" s="29" t="s">
         <v>292</v>
       </c>
@@ -42876,7 +42802,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="700" spans="1:15" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="700" spans="1:15" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A700" s="29" t="s">
         <v>292</v>
       </c>
@@ -42902,7 +42828,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="701" spans="1:15" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="701" spans="1:15" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A701" s="29" t="s">
         <v>290</v>
       </c>
@@ -42928,7 +42854,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="702" spans="1:15" s="3" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="702" spans="1:15" s="3" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A702" s="29" t="s">
         <v>24</v>
       </c>
@@ -42955,7 +42881,7 @@
       <c r="L702" s="17"/>
       <c r="O702" s="17"/>
     </row>
-    <row r="703" spans="1:15" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="703" spans="1:15" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A703" s="29" t="s">
         <v>24</v>
       </c>
@@ -42981,7 +42907,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="704" spans="1:15" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="704" spans="1:15" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A704" s="29" t="s">
         <v>24</v>
       </c>
@@ -43007,7 +42933,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="705" spans="1:15" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="705" spans="1:15" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A705" s="29" t="s">
         <v>24</v>
       </c>
@@ -43033,7 +42959,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="706" spans="1:15" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="706" spans="1:15" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A706" s="29" t="s">
         <v>24</v>
       </c>
@@ -43059,7 +42985,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="707" spans="1:15" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="707" spans="1:15" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A707" s="29" t="s">
         <v>24</v>
       </c>
@@ -43085,7 +43011,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="708" spans="1:15" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="708" spans="1:15" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A708" s="29" t="s">
         <v>238</v>
       </c>
@@ -43111,7 +43037,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="709" spans="1:15" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="709" spans="1:15" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A709" s="29" t="s">
         <v>238</v>
       </c>
@@ -43137,7 +43063,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="710" spans="1:15" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="710" spans="1:15" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A710" s="29" t="s">
         <v>238</v>
       </c>
@@ -43163,7 +43089,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="711" spans="1:15" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="711" spans="1:15" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A711" s="29" t="s">
         <v>238</v>
       </c>
@@ -43189,7 +43115,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="712" spans="1:15" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="712" spans="1:15" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A712" s="29" t="s">
         <v>238</v>
       </c>
@@ -43215,7 +43141,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="713" spans="1:15" s="3" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="713" spans="1:15" s="3" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A713" s="29" t="s">
         <v>28</v>
       </c>
@@ -43240,7 +43166,7 @@
       <c r="L713" s="17"/>
       <c r="O713" s="17"/>
     </row>
-    <row r="714" spans="1:15" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="714" spans="1:15" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A714" s="29" t="s">
         <v>28</v>
       </c>
@@ -43266,7 +43192,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="715" spans="1:15" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="715" spans="1:15" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A715" s="29" t="s">
         <v>28</v>
       </c>
@@ -43289,7 +43215,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="716" spans="1:15" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="716" spans="1:15" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A716" s="29" t="s">
         <v>28</v>
       </c>
@@ -43315,7 +43241,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="717" spans="1:15" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="717" spans="1:15" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A717" s="29" t="s">
         <v>28</v>
       </c>
@@ -43341,7 +43267,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="718" spans="1:15" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="718" spans="1:15" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A718" s="29" t="s">
         <v>52</v>
       </c>
@@ -43367,7 +43293,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="719" spans="1:15" s="3" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="719" spans="1:15" s="3" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A719" s="29" t="s">
         <v>32</v>
       </c>
@@ -43394,7 +43320,7 @@
       <c r="L719" s="17"/>
       <c r="O719" s="17"/>
     </row>
-    <row r="720" spans="1:15" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="720" spans="1:15" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A720" s="29" t="s">
         <v>32</v>
       </c>
@@ -43420,7 +43346,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="721" spans="1:15" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="721" spans="1:15" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A721" s="29" t="s">
         <v>32</v>
       </c>
@@ -43446,7 +43372,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="722" spans="1:15" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="722" spans="1:15" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A722" s="29" t="s">
         <v>32</v>
       </c>
@@ -43472,7 +43398,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="723" spans="1:15" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="723" spans="1:15" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A723" s="29" t="s">
         <v>32</v>
       </c>
@@ -43495,7 +43421,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="724" spans="1:15" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="724" spans="1:15" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A724" s="29" t="s">
         <v>32</v>
       </c>
@@ -43521,7 +43447,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="725" spans="1:15" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="725" spans="1:15" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A725" s="29" t="s">
         <v>32</v>
       </c>
@@ -43547,7 +43473,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="726" spans="1:15" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="726" spans="1:15" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A726" s="29" t="s">
         <v>67</v>
       </c>
@@ -43573,7 +43499,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="727" spans="1:15" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="727" spans="1:15" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A727" s="29" t="s">
         <v>28</v>
       </c>
@@ -43599,7 +43525,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="728" spans="1:15" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="728" spans="1:15" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A728" s="29" t="s">
         <v>60</v>
       </c>
@@ -43625,7 +43551,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="729" spans="1:15" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="729" spans="1:15" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A729" s="29" t="s">
         <v>290</v>
       </c>
@@ -43651,7 +43577,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="730" spans="1:15" s="3" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="730" spans="1:15" s="3" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A730" s="29" t="s">
         <v>52</v>
       </c>
@@ -43678,7 +43604,7 @@
       <c r="L730" s="17"/>
       <c r="O730" s="17"/>
     </row>
-    <row r="731" spans="1:15" s="3" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="731" spans="1:15" s="3" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A731" s="29" t="s">
         <v>52</v>
       </c>
@@ -43705,7 +43631,7 @@
       <c r="L731" s="17"/>
       <c r="O731" s="17"/>
     </row>
-    <row r="732" spans="1:15" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="732" spans="1:15" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A732" s="29" t="s">
         <v>52</v>
       </c>
@@ -43737,7 +43663,7 @@
       <c r="N732" s="14"/>
       <c r="O732" s="18"/>
     </row>
-    <row r="733" spans="1:15" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="733" spans="1:15" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A733" s="29" t="s">
         <v>52</v>
       </c>
@@ -43769,7 +43695,7 @@
       <c r="N733" s="14"/>
       <c r="O733" s="18"/>
     </row>
-    <row r="734" spans="1:15" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="734" spans="1:15" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A734" s="29" t="s">
         <v>60</v>
       </c>
@@ -43801,7 +43727,7 @@
       <c r="N734" s="14"/>
       <c r="O734" s="18"/>
     </row>
-    <row r="735" spans="1:15" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="735" spans="1:15" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A735" s="29" t="s">
         <v>60</v>
       </c>
@@ -43833,7 +43759,7 @@
       <c r="N735" s="14"/>
       <c r="O735" s="18"/>
     </row>
-    <row r="736" spans="1:15" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="736" spans="1:15" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A736" s="29" t="s">
         <v>60</v>
       </c>
@@ -43865,7 +43791,7 @@
       <c r="N736" s="14"/>
       <c r="O736" s="18"/>
     </row>
-    <row r="737" spans="1:15" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="737" spans="1:15" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A737" s="29" t="s">
         <v>60</v>
       </c>
@@ -43897,7 +43823,7 @@
       <c r="N737" s="14"/>
       <c r="O737" s="18"/>
     </row>
-    <row r="738" spans="1:15" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="738" spans="1:15" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A738" s="29" t="s">
         <v>15</v>
       </c>
@@ -43929,7 +43855,7 @@
       <c r="N738" s="14"/>
       <c r="O738" s="18"/>
     </row>
-    <row r="739" spans="1:15" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="739" spans="1:15" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A739" s="29" t="s">
         <v>15</v>
       </c>
@@ -43961,7 +43887,7 @@
       <c r="N739" s="14"/>
       <c r="O739" s="18"/>
     </row>
-    <row r="740" spans="1:15" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="740" spans="1:15" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A740" s="29" t="s">
         <v>15</v>
       </c>
@@ -43993,7 +43919,7 @@
       <c r="N740" s="14"/>
       <c r="O740" s="18"/>
     </row>
-    <row r="741" spans="1:15" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="741" spans="1:15" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A741" s="29" t="s">
         <v>67</v>
       </c>
@@ -44025,7 +43951,7 @@
       <c r="N741" s="14"/>
       <c r="O741" s="18"/>
     </row>
-    <row r="742" spans="1:15" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="742" spans="1:15" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A742" s="29" t="s">
         <v>24</v>
       </c>
@@ -44057,7 +43983,7 @@
       <c r="N742" s="14"/>
       <c r="O742" s="18"/>
     </row>
-    <row r="743" spans="1:15" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="743" spans="1:15" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A743" s="29" t="s">
         <v>24</v>
       </c>
@@ -44089,7 +44015,7 @@
       <c r="N743" s="14"/>
       <c r="O743" s="18"/>
     </row>
-    <row r="744" spans="1:15" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="744" spans="1:15" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A744" s="29" t="s">
         <v>28</v>
       </c>
@@ -44121,7 +44047,7 @@
       <c r="N744" s="14"/>
       <c r="O744" s="18"/>
     </row>
-    <row r="745" spans="1:15" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="745" spans="1:15" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A745" s="29" t="s">
         <v>52</v>
       </c>
@@ -44154,7 +44080,7 @@
       <c r="N745" s="9"/>
       <c r="O745" s="18"/>
     </row>
-    <row r="746" spans="1:15" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="746" spans="1:15" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A746" s="29" t="s">
         <v>52</v>
       </c>
@@ -44187,7 +44113,7 @@
       <c r="N746" s="9"/>
       <c r="O746" s="18"/>
     </row>
-    <row r="747" spans="1:15" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="747" spans="1:15" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A747" s="29" t="s">
         <v>52</v>
       </c>
@@ -44220,7 +44146,7 @@
       <c r="N747" s="9"/>
       <c r="O747" s="18"/>
     </row>
-    <row r="748" spans="1:15" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="748" spans="1:15" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A748" s="29" t="s">
         <v>52</v>
       </c>
@@ -44253,7 +44179,7 @@
       <c r="N748" s="9"/>
       <c r="O748" s="18"/>
     </row>
-    <row r="749" spans="1:15" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="749" spans="1:15" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A749" s="29" t="s">
         <v>52</v>
       </c>
@@ -44286,7 +44212,7 @@
       <c r="N749" s="9"/>
       <c r="O749" s="18"/>
     </row>
-    <row r="750" spans="1:15" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="750" spans="1:15" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A750" s="29" t="s">
         <v>60</v>
       </c>
@@ -44319,7 +44245,7 @@
       <c r="N750" s="9"/>
       <c r="O750" s="18"/>
     </row>
-    <row r="751" spans="1:15" s="3" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="751" spans="1:15" s="3" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A751" s="29" t="s">
         <v>52</v>
       </c>
@@ -44348,7 +44274,7 @@
       <c r="L751" s="17"/>
       <c r="O751" s="17"/>
     </row>
-    <row r="752" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="752" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A752" s="29" t="s">
         <v>60</v>
       </c>
@@ -44381,7 +44307,7 @@
       <c r="N752" s="9"/>
       <c r="O752" s="18"/>
     </row>
-    <row r="753" spans="1:15" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="753" spans="1:15" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A753" s="29" t="s">
         <v>60</v>
       </c>
@@ -44414,7 +44340,7 @@
       <c r="N753" s="9"/>
       <c r="O753" s="18"/>
     </row>
-    <row r="754" spans="1:15" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="754" spans="1:15" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A754" s="29" t="s">
         <v>60</v>
       </c>
@@ -44447,7 +44373,7 @@
       <c r="N754" s="9"/>
       <c r="O754" s="18"/>
     </row>
-    <row r="755" spans="1:15" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="755" spans="1:15" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A755" s="29" t="s">
         <v>60</v>
       </c>
@@ -44480,7 +44406,7 @@
       <c r="N755" s="9"/>
       <c r="O755" s="18"/>
     </row>
-    <row r="756" spans="1:15" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="756" spans="1:15" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A756" s="29" t="s">
         <v>60</v>
       </c>
@@ -44513,7 +44439,7 @@
       <c r="N756" s="9"/>
       <c r="O756" s="18"/>
     </row>
-    <row r="757" spans="1:15" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="757" spans="1:15" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A757" s="29" t="s">
         <v>60</v>
       </c>
@@ -44546,7 +44472,7 @@
       <c r="N757" s="9"/>
       <c r="O757" s="18"/>
     </row>
-    <row r="758" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="758" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A758" s="29" t="s">
         <v>15</v>
       </c>
@@ -44579,7 +44505,7 @@
       <c r="N758" s="9"/>
       <c r="O758" s="18"/>
     </row>
-    <row r="759" spans="1:15" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="759" spans="1:15" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A759" s="29" t="s">
         <v>15</v>
       </c>
@@ -44610,7 +44536,7 @@
       <c r="N759" s="9"/>
       <c r="O759" s="18"/>
     </row>
-    <row r="760" spans="1:15" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="760" spans="1:15" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A760" s="29" t="s">
         <v>15</v>
       </c>
@@ -44641,7 +44567,7 @@
       <c r="N760" s="9"/>
       <c r="O760" s="18"/>
     </row>
-    <row r="761" spans="1:15" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="761" spans="1:15" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A761" s="29" t="s">
         <v>15</v>
       </c>
@@ -44674,7 +44600,7 @@
       <c r="N761" s="9"/>
       <c r="O761" s="18"/>
     </row>
-    <row r="762" spans="1:15" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="762" spans="1:15" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A762" s="29" t="s">
         <v>15</v>
       </c>
@@ -44707,7 +44633,7 @@
       <c r="N762" s="9"/>
       <c r="O762" s="18"/>
     </row>
-    <row r="763" spans="1:15" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="763" spans="1:15" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A763" s="29" t="s">
         <v>67</v>
       </c>
@@ -44740,7 +44666,7 @@
       <c r="N763" s="9"/>
       <c r="O763" s="18"/>
     </row>
-    <row r="764" spans="1:15" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="764" spans="1:15" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A764" s="29" t="s">
         <v>67</v>
       </c>
@@ -44773,7 +44699,7 @@
       <c r="N764" s="9"/>
       <c r="O764" s="18"/>
     </row>
-    <row r="765" spans="1:15" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="765" spans="1:15" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A765" s="29" t="s">
         <v>67</v>
       </c>
@@ -44806,7 +44732,7 @@
       <c r="N765" s="9"/>
       <c r="O765" s="18"/>
     </row>
-    <row r="766" spans="1:15" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="766" spans="1:15" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A766" s="29" t="s">
         <v>67</v>
       </c>
@@ -44839,7 +44765,7 @@
       <c r="N766" s="9"/>
       <c r="O766" s="18"/>
     </row>
-    <row r="767" spans="1:15" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="767" spans="1:15" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A767" s="29" t="s">
         <v>67</v>
       </c>
@@ -44872,7 +44798,7 @@
       <c r="N767" s="9"/>
       <c r="O767" s="18"/>
     </row>
-    <row r="768" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="768" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A768" s="29" t="s">
         <v>67</v>
       </c>
@@ -44905,7 +44831,7 @@
       <c r="N768" s="9"/>
       <c r="O768" s="18"/>
     </row>
-    <row r="769" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="769" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A769" s="29" t="s">
         <v>290</v>
       </c>
@@ -44938,7 +44864,7 @@
       <c r="N769" s="9"/>
       <c r="O769" s="18"/>
     </row>
-    <row r="770" spans="1:15" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="770" spans="1:15" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A770" s="29" t="s">
         <v>290</v>
       </c>
@@ -44971,7 +44897,7 @@
       <c r="N770" s="9"/>
       <c r="O770" s="18"/>
     </row>
-    <row r="771" spans="1:15" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="771" spans="1:15" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A771" s="29" t="s">
         <v>290</v>
       </c>
@@ -45004,7 +44930,7 @@
       <c r="N771" s="9"/>
       <c r="O771" s="18"/>
     </row>
-    <row r="772" spans="1:15" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="772" spans="1:15" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A772" s="29" t="s">
         <v>290</v>
       </c>
@@ -45037,7 +44963,7 @@
       <c r="N772" s="9"/>
       <c r="O772" s="18"/>
     </row>
-    <row r="773" spans="1:15" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="773" spans="1:15" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A773" s="29" t="s">
         <v>290</v>
       </c>
@@ -45070,7 +44996,7 @@
       <c r="N773" s="9"/>
       <c r="O773" s="18"/>
     </row>
-    <row r="774" spans="1:15" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="774" spans="1:15" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A774" s="29" t="s">
         <v>290</v>
       </c>
@@ -45103,7 +45029,7 @@
       <c r="N774" s="9"/>
       <c r="O774" s="18"/>
     </row>
-    <row r="775" spans="1:15" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="775" spans="1:15" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A775" s="29" t="s">
         <v>290</v>
       </c>
@@ -45136,7 +45062,7 @@
       <c r="N775" s="9"/>
       <c r="O775" s="18"/>
     </row>
-    <row r="776" spans="1:15" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="776" spans="1:15" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A776" s="29" t="s">
         <v>290</v>
       </c>
@@ -45169,7 +45095,7 @@
       <c r="N776" s="9"/>
       <c r="O776" s="18"/>
     </row>
-    <row r="777" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="777" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A777" s="29" t="s">
         <v>24</v>
       </c>
@@ -45204,7 +45130,7 @@
       <c r="N777" s="9"/>
       <c r="O777" s="18"/>
     </row>
-    <row r="778" spans="1:15" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="778" spans="1:15" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A778" s="29" t="s">
         <v>24</v>
       </c>
@@ -45237,7 +45163,7 @@
       <c r="N778" s="9"/>
       <c r="O778" s="18"/>
     </row>
-    <row r="779" spans="1:15" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="779" spans="1:15" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A779" s="29" t="s">
         <v>24</v>
       </c>
@@ -45268,7 +45194,7 @@
       <c r="N779" s="9"/>
       <c r="O779" s="18"/>
     </row>
-    <row r="780" spans="1:15" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="780" spans="1:15" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A780" s="29" t="s">
         <v>24</v>
       </c>
@@ -45301,7 +45227,7 @@
       <c r="N780" s="9"/>
       <c r="O780" s="18"/>
     </row>
-    <row r="781" spans="1:15" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="781" spans="1:15" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A781" s="29" t="s">
         <v>24</v>
       </c>
@@ -45334,7 +45260,7 @@
       <c r="N781" s="9"/>
       <c r="O781" s="18"/>
     </row>
-    <row r="782" spans="1:15" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="782" spans="1:15" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A782" s="29" t="s">
         <v>24</v>
       </c>
@@ -45367,7 +45293,7 @@
       <c r="N782" s="9"/>
       <c r="O782" s="18"/>
     </row>
-    <row r="783" spans="1:15" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="783" spans="1:15" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A783" s="29" t="s">
         <v>238</v>
       </c>
@@ -45400,7 +45326,7 @@
       <c r="N783" s="9"/>
       <c r="O783" s="18"/>
     </row>
-    <row r="784" spans="1:15" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="784" spans="1:15" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A784" s="29" t="s">
         <v>238</v>
       </c>
@@ -45428,7 +45354,7 @@
       <c r="N784" s="9"/>
       <c r="O784" s="18"/>
     </row>
-    <row r="785" spans="1:15" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="785" spans="1:15" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A785" s="29" t="s">
         <v>238</v>
       </c>
@@ -45461,7 +45387,7 @@
       <c r="N785" s="9"/>
       <c r="O785" s="18"/>
     </row>
-    <row r="786" spans="1:15" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="786" spans="1:15" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A786" s="29" t="s">
         <v>238</v>
       </c>
@@ -45494,7 +45420,7 @@
       <c r="N786" s="9"/>
       <c r="O786" s="18"/>
     </row>
-    <row r="787" spans="1:15" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="787" spans="1:15" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A787" s="29" t="s">
         <v>238</v>
       </c>
@@ -45527,7 +45453,7 @@
       <c r="N787" s="9"/>
       <c r="O787" s="18"/>
     </row>
-    <row r="788" spans="1:15" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="788" spans="1:15" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A788" s="29" t="s">
         <v>238</v>
       </c>
@@ -45558,7 +45484,7 @@
       <c r="N788" s="9"/>
       <c r="O788" s="18"/>
     </row>
-    <row r="789" spans="1:15" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="789" spans="1:15" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A789" s="29" t="s">
         <v>238</v>
       </c>
@@ -45589,7 +45515,7 @@
       <c r="N789" s="9"/>
       <c r="O789" s="18"/>
     </row>
-    <row r="790" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="790" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A790" s="29" t="s">
         <v>28</v>
       </c>
@@ -45622,7 +45548,7 @@
       <c r="N790" s="9"/>
       <c r="O790" s="18"/>
     </row>
-    <row r="791" spans="1:15" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="791" spans="1:15" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A791" s="29" t="s">
         <v>28</v>
       </c>
@@ -45655,7 +45581,7 @@
       <c r="N791" s="9"/>
       <c r="O791" s="18"/>
     </row>
-    <row r="792" spans="1:15" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="792" spans="1:15" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A792" s="29" t="s">
         <v>28</v>
       </c>
@@ -45688,7 +45614,7 @@
       <c r="N792" s="9"/>
       <c r="O792" s="18"/>
     </row>
-    <row r="793" spans="1:15" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="793" spans="1:15" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A793" s="29" t="s">
         <v>28</v>
       </c>
@@ -45721,7 +45647,7 @@
       <c r="N793" s="9"/>
       <c r="O793" s="18"/>
     </row>
-    <row r="794" spans="1:15" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="794" spans="1:15" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A794" s="29" t="s">
         <v>28</v>
       </c>
@@ -45754,7 +45680,7 @@
       <c r="N794" s="9"/>
       <c r="O794" s="18"/>
     </row>
-    <row r="795" spans="1:15" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="795" spans="1:15" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A795" s="29" t="s">
         <v>28</v>
       </c>
@@ -45785,7 +45711,7 @@
       <c r="N795" s="9"/>
       <c r="O795" s="18"/>
     </row>
-    <row r="796" spans="1:15" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="796" spans="1:15" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A796" s="29" t="s">
         <v>28</v>
       </c>
@@ -45816,7 +45742,7 @@
       <c r="N796" s="9"/>
       <c r="O796" s="18"/>
     </row>
-    <row r="797" spans="1:15" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="797" spans="1:15" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A797" s="29" t="s">
         <v>32</v>
       </c>
@@ -45849,7 +45775,7 @@
       <c r="N797" s="9"/>
       <c r="O797" s="18"/>
     </row>
-    <row r="798" spans="1:15" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="798" spans="1:15" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A798" s="29" t="s">
         <v>32</v>
       </c>
@@ -45880,7 +45806,7 @@
       <c r="N798" s="9"/>
       <c r="O798" s="18"/>
     </row>
-    <row r="799" spans="1:15" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="799" spans="1:15" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A799" s="29" t="s">
         <v>32</v>
       </c>
@@ -45911,7 +45837,7 @@
       <c r="N799" s="9"/>
       <c r="O799" s="18"/>
     </row>
-    <row r="800" spans="1:15" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="800" spans="1:15" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A800" s="29" t="s">
         <v>32</v>
       </c>
@@ -45942,7 +45868,7 @@
       <c r="N800" s="9"/>
       <c r="O800" s="18"/>
     </row>
-    <row r="801" spans="1:15" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="801" spans="1:15" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A801" s="29" t="s">
         <v>32</v>
       </c>
@@ -45975,7 +45901,7 @@
       <c r="N801" s="9"/>
       <c r="O801" s="18"/>
     </row>
-    <row r="802" spans="1:15" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="802" spans="1:15" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A802" s="29" t="s">
         <v>32</v>
       </c>
@@ -46008,7 +45934,7 @@
       <c r="N802" s="9"/>
       <c r="O802" s="18"/>
     </row>
-    <row r="803" spans="1:15" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="803" spans="1:15" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A803" s="29" t="s">
         <v>32</v>
       </c>
@@ -46041,7 +45967,7 @@
       <c r="N803" s="9"/>
       <c r="O803" s="18"/>
     </row>
-    <row r="804" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="804" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A804" s="29" t="s">
         <v>32</v>
       </c>
@@ -46067,7 +45993,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="805" spans="1:15" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="805" spans="1:15" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A805" s="29" t="s">
         <v>52</v>
       </c>
@@ -46095,7 +46021,7 @@
       <c r="J805" s="7"/>
       <c r="M805" s="7"/>
     </row>
-    <row r="806" spans="1:15" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="806" spans="1:15" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A806" s="29" t="s">
         <v>52</v>
       </c>
@@ -46123,7 +46049,7 @@
       <c r="J806" s="7"/>
       <c r="M806" s="7"/>
     </row>
-    <row r="807" spans="1:15" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="807" spans="1:15" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A807" s="29" t="s">
         <v>60</v>
       </c>
@@ -46151,7 +46077,7 @@
       <c r="J807" s="7"/>
       <c r="M807" s="7"/>
     </row>
-    <row r="808" spans="1:15" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="808" spans="1:15" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A808" s="29" t="s">
         <v>60</v>
       </c>
@@ -46179,7 +46105,7 @@
       <c r="J808" s="7"/>
       <c r="M808" s="7"/>
     </row>
-    <row r="809" spans="1:15" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="809" spans="1:15" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A809" s="29" t="s">
         <v>60</v>
       </c>
@@ -46207,7 +46133,7 @@
       <c r="J809" s="7"/>
       <c r="M809" s="7"/>
     </row>
-    <row r="810" spans="1:15" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="810" spans="1:15" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A810" s="29" t="s">
         <v>60</v>
       </c>
@@ -46235,7 +46161,7 @@
       <c r="J810" s="7"/>
       <c r="M810" s="7"/>
     </row>
-    <row r="811" spans="1:15" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="811" spans="1:15" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A811" s="29" t="s">
         <v>15</v>
       </c>
@@ -46263,7 +46189,7 @@
       <c r="J811" s="7"/>
       <c r="M811" s="7"/>
     </row>
-    <row r="812" spans="1:15" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="812" spans="1:15" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A812" s="29" t="s">
         <v>15</v>
       </c>
@@ -46291,7 +46217,7 @@
       <c r="J812" s="7"/>
       <c r="M812" s="7"/>
     </row>
-    <row r="813" spans="1:15" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="813" spans="1:15" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A813" s="29" t="s">
         <v>15</v>
       </c>
@@ -46319,7 +46245,7 @@
       <c r="J813" s="7"/>
       <c r="M813" s="7"/>
     </row>
-    <row r="814" spans="1:15" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="814" spans="1:15" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A814" s="29" t="s">
         <v>67</v>
       </c>
@@ -46344,7 +46270,7 @@
       <c r="J814" s="7"/>
       <c r="M814" s="7"/>
     </row>
-    <row r="815" spans="1:15" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="815" spans="1:15" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A815" s="29" t="s">
         <v>259</v>
       </c>
@@ -46364,7 +46290,7 @@
       <c r="J815" s="7"/>
       <c r="M815" s="7"/>
     </row>
-    <row r="816" spans="1:15" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="816" spans="1:15" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A816" s="29" t="s">
         <v>24</v>
       </c>
@@ -46392,7 +46318,7 @@
       <c r="J816" s="7"/>
       <c r="M816" s="7"/>
     </row>
-    <row r="817" spans="1:15" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="817" spans="1:15" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A817" s="29" t="s">
         <v>24</v>
       </c>
@@ -46420,7 +46346,7 @@
       <c r="J817" s="7"/>
       <c r="M817" s="7"/>
     </row>
-    <row r="818" spans="1:15" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="818" spans="1:15" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A818" s="29" t="s">
         <v>28</v>
       </c>
@@ -46448,7 +46374,7 @@
       <c r="J818" s="7"/>
       <c r="M818" s="7"/>
     </row>
-    <row r="819" spans="1:15" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="819" spans="1:15" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A819" s="29" t="s">
         <v>60</v>
       </c>
@@ -46477,7 +46403,7 @@
       <c r="J819" s="7"/>
       <c r="M819" s="7"/>
     </row>
-    <row r="820" spans="1:15" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="820" spans="1:15" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A820" s="29" t="s">
         <v>52</v>
       </c>
@@ -46506,7 +46432,7 @@
       <c r="M820" s="7"/>
       <c r="O820" s="1"/>
     </row>
-    <row r="821" spans="1:15" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="821" spans="1:15" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A821" s="29" t="s">
         <v>52</v>
       </c>
@@ -46535,7 +46461,7 @@
       <c r="M821" s="7"/>
       <c r="O821" s="1"/>
     </row>
-    <row r="822" spans="1:15" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="822" spans="1:15" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A822" s="29" t="s">
         <v>52</v>
       </c>
@@ -46564,7 +46490,7 @@
       <c r="M822" s="7"/>
       <c r="O822" s="1"/>
     </row>
-    <row r="823" spans="1:15" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="823" spans="1:15" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A823" s="29" t="s">
         <v>52</v>
       </c>
@@ -46593,7 +46519,7 @@
       <c r="M823" s="7"/>
       <c r="O823" s="1"/>
     </row>
-    <row r="824" spans="1:15" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="824" spans="1:15" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A824" s="29" t="s">
         <v>52</v>
       </c>
@@ -46619,7 +46545,7 @@
       <c r="M824" s="7"/>
       <c r="O824" s="1"/>
     </row>
-    <row r="825" spans="1:15" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="825" spans="1:15" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A825" s="29" t="s">
         <v>60</v>
       </c>
@@ -46651,7 +46577,7 @@
       <c r="M825" s="7"/>
       <c r="O825" s="1"/>
     </row>
-    <row r="826" spans="1:15" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="826" spans="1:15" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A826" s="29" t="s">
         <v>60</v>
       </c>
@@ -46680,7 +46606,7 @@
       <c r="M826" s="7"/>
       <c r="O826" s="1"/>
     </row>
-    <row r="827" spans="1:15" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="827" spans="1:15" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A827" s="29" t="s">
         <v>60</v>
       </c>
@@ -46710,7 +46636,7 @@
       <c r="M827" s="7"/>
       <c r="O827" s="1"/>
     </row>
-    <row r="828" spans="1:15" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="828" spans="1:15" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A828" s="29" t="s">
         <v>60</v>
       </c>
@@ -46739,7 +46665,7 @@
       <c r="M828" s="7"/>
       <c r="O828" s="1"/>
     </row>
-    <row r="829" spans="1:15" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="829" spans="1:15" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A829" s="29" t="s">
         <v>60</v>
       </c>
@@ -46768,7 +46694,7 @@
       <c r="M829" s="7"/>
       <c r="O829" s="1"/>
     </row>
-    <row r="830" spans="1:15" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="830" spans="1:15" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A830" s="29" t="s">
         <v>60</v>
       </c>
@@ -46797,7 +46723,7 @@
       <c r="M830" s="7"/>
       <c r="O830" s="1"/>
     </row>
-    <row r="831" spans="1:15" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="831" spans="1:15" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A831" s="29" t="s">
         <v>60</v>
       </c>
@@ -46826,7 +46752,7 @@
       <c r="M831" s="7"/>
       <c r="O831" s="1"/>
     </row>
-    <row r="832" spans="1:15" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="832" spans="1:15" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A832" s="29" t="s">
         <v>60</v>
       </c>
@@ -46855,7 +46781,7 @@
       <c r="M832" s="7"/>
       <c r="O832" s="1"/>
     </row>
-    <row r="833" spans="1:15" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="833" spans="1:15" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A833" s="29" t="s">
         <v>60</v>
       </c>
@@ -46879,7 +46805,7 @@
       <c r="M833" s="7"/>
       <c r="O833" s="1"/>
     </row>
-    <row r="834" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="834" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A834" s="29" t="s">
         <v>60</v>
       </c>
@@ -46905,7 +46831,7 @@
       <c r="M834" s="7"/>
       <c r="O834" s="1"/>
     </row>
-    <row r="835" spans="1:15" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="835" spans="1:15" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A835" s="29" t="s">
         <v>60</v>
       </c>
@@ -46934,7 +46860,7 @@
       <c r="M835" s="7"/>
       <c r="O835" s="1"/>
     </row>
-    <row r="836" spans="1:15" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="836" spans="1:15" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A836" s="29" t="s">
         <v>15</v>
       </c>
@@ -46963,7 +46889,7 @@
       <c r="M836" s="7"/>
       <c r="O836" s="1"/>
     </row>
-    <row r="837" spans="1:15" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="837" spans="1:15" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A837" s="29" t="s">
         <v>15</v>
       </c>
@@ -46989,7 +46915,7 @@
       <c r="M837" s="7"/>
       <c r="O837" s="1"/>
     </row>
-    <row r="838" spans="1:15" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="838" spans="1:15" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A838" s="29" t="s">
         <v>15</v>
       </c>
@@ -47018,7 +46944,7 @@
       <c r="M838" s="7"/>
       <c r="O838" s="1"/>
     </row>
-    <row r="839" spans="1:15" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="839" spans="1:15" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A839" s="29" t="s">
         <v>15</v>
       </c>
@@ -47045,7 +46971,7 @@
       <c r="M839" s="7"/>
       <c r="O839" s="1"/>
     </row>
-    <row r="840" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="840" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A840" s="29" t="s">
         <v>15</v>
       </c>
@@ -47068,7 +46994,7 @@
       <c r="M840" s="7"/>
       <c r="O840" s="1"/>
     </row>
-    <row r="841" spans="1:15" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="841" spans="1:15" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A841" s="29" t="s">
         <v>15</v>
       </c>
@@ -47097,7 +47023,7 @@
       <c r="M841" s="7"/>
       <c r="O841" s="1"/>
     </row>
-    <row r="842" spans="1:15" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="842" spans="1:15" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A842" s="29" t="s">
         <v>15</v>
       </c>
@@ -47123,7 +47049,7 @@
       <c r="M842" s="7"/>
       <c r="O842" s="1"/>
     </row>
-    <row r="843" spans="1:15" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="843" spans="1:15" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A843" s="29" t="s">
         <v>67</v>
       </c>
@@ -47152,7 +47078,7 @@
       <c r="M843" s="7"/>
       <c r="O843" s="1"/>
     </row>
-    <row r="844" spans="1:15" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="844" spans="1:15" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A844" s="29" t="s">
         <v>67</v>
       </c>
@@ -47181,7 +47107,7 @@
       <c r="M844" s="7"/>
       <c r="O844" s="1"/>
     </row>
-    <row r="845" spans="1:15" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="845" spans="1:15" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A845" s="29" t="s">
         <v>67</v>
       </c>
@@ -47210,7 +47136,7 @@
       <c r="M845" s="7"/>
       <c r="O845" s="1"/>
     </row>
-    <row r="846" spans="1:15" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="846" spans="1:15" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A846" s="29" t="s">
         <v>67</v>
       </c>
@@ -47239,7 +47165,7 @@
       <c r="M846" s="7"/>
       <c r="O846" s="1"/>
     </row>
-    <row r="847" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="847" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A847" s="29" t="s">
         <v>67</v>
       </c>
@@ -47262,7 +47188,7 @@
       <c r="M847" s="7"/>
       <c r="O847" s="1"/>
     </row>
-    <row r="848" spans="1:15" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="848" spans="1:15" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A848" s="29" t="s">
         <v>540</v>
       </c>
@@ -47289,7 +47215,7 @@
       <c r="M848" s="7"/>
       <c r="O848" s="1"/>
     </row>
-    <row r="849" spans="1:15" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="849" spans="1:15" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A849" s="29" t="s">
         <v>540</v>
       </c>
@@ -47316,7 +47242,7 @@
       <c r="M849" s="7"/>
       <c r="O849" s="1"/>
     </row>
-    <row r="850" spans="1:15" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="850" spans="1:15" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A850" s="29" t="s">
         <v>290</v>
       </c>
@@ -47345,7 +47271,7 @@
       <c r="M850" s="7"/>
       <c r="O850" s="1"/>
     </row>
-    <row r="851" spans="1:15" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="851" spans="1:15" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A851" s="29" t="s">
         <v>290</v>
       </c>
@@ -47374,7 +47300,7 @@
       <c r="M851" s="7"/>
       <c r="O851" s="1"/>
     </row>
-    <row r="852" spans="1:15" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="852" spans="1:15" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A852" s="29" t="s">
         <v>290</v>
       </c>
@@ -47403,7 +47329,7 @@
       <c r="M852" s="7"/>
       <c r="O852" s="1"/>
     </row>
-    <row r="853" spans="1:15" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="853" spans="1:15" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A853" s="29" t="s">
         <v>290</v>
       </c>
@@ -47432,7 +47358,7 @@
       <c r="M853" s="7"/>
       <c r="O853" s="1"/>
     </row>
-    <row r="854" spans="1:15" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="854" spans="1:15" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A854" s="29" t="s">
         <v>290</v>
       </c>
@@ -47461,7 +47387,7 @@
       <c r="M854" s="7"/>
       <c r="O854" s="1"/>
     </row>
-    <row r="855" spans="1:15" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="855" spans="1:15" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A855" s="29" t="s">
         <v>290</v>
       </c>
@@ -47485,7 +47411,7 @@
       <c r="M855" s="7"/>
       <c r="O855" s="1"/>
     </row>
-    <row r="856" spans="1:15" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="856" spans="1:15" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A856" s="29" t="s">
         <v>290</v>
       </c>
@@ -47514,7 +47440,7 @@
       <c r="M856" s="7"/>
       <c r="O856" s="1"/>
     </row>
-    <row r="857" spans="1:15" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="857" spans="1:15" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A857" s="29" t="s">
         <v>24</v>
       </c>
@@ -47543,7 +47469,7 @@
       <c r="M857" s="7"/>
       <c r="O857" s="1"/>
     </row>
-    <row r="858" spans="1:15" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="858" spans="1:15" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A858" s="29" t="s">
         <v>24</v>
       </c>
@@ -47572,7 +47498,7 @@
       <c r="M858" s="7"/>
       <c r="O858" s="1"/>
     </row>
-    <row r="859" spans="1:15" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="859" spans="1:15" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A859" s="29" t="s">
         <v>24</v>
       </c>
@@ -47601,7 +47527,7 @@
       <c r="M859" s="7"/>
       <c r="O859" s="1"/>
     </row>
-    <row r="860" spans="1:15" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="860" spans="1:15" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A860" s="29" t="s">
         <v>24</v>
       </c>
@@ -47630,7 +47556,7 @@
       <c r="M860" s="7"/>
       <c r="O860" s="1"/>
     </row>
-    <row r="861" spans="1:15" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="861" spans="1:15" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A861" s="29" t="s">
         <v>24</v>
       </c>
@@ -47659,7 +47585,7 @@
       <c r="M861" s="7"/>
       <c r="O861" s="1"/>
     </row>
-    <row r="862" spans="1:15" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="862" spans="1:15" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A862" s="29" t="s">
         <v>24</v>
       </c>
@@ -47683,7 +47609,7 @@
       <c r="M862" s="7"/>
       <c r="O862" s="1"/>
     </row>
-    <row r="863" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="863" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A863" s="29" t="s">
         <v>24</v>
       </c>
@@ -47709,7 +47635,7 @@
       <c r="M863" s="7"/>
       <c r="O863" s="1"/>
     </row>
-    <row r="864" spans="1:15" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="864" spans="1:15" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A864" s="29" t="s">
         <v>24</v>
       </c>
@@ -47738,7 +47664,7 @@
       <c r="M864" s="7"/>
       <c r="O864" s="1"/>
     </row>
-    <row r="865" spans="1:15" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="865" spans="1:15" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A865" s="29" t="s">
         <v>238</v>
       </c>
@@ -47767,7 +47693,7 @@
       <c r="M865" s="7"/>
       <c r="O865" s="1"/>
     </row>
-    <row r="866" spans="1:15" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="866" spans="1:15" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A866" s="29" t="s">
         <v>238</v>
       </c>
@@ -47796,7 +47722,7 @@
       <c r="M866" s="7"/>
       <c r="O866" s="1"/>
     </row>
-    <row r="867" spans="1:15" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="867" spans="1:15" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A867" s="29" t="s">
         <v>238</v>
       </c>
@@ -47820,7 +47746,7 @@
       <c r="M867" s="7"/>
       <c r="O867" s="1"/>
     </row>
-    <row r="868" spans="1:15" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="868" spans="1:15" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A868" s="29" t="s">
         <v>238</v>
       </c>
@@ -47849,7 +47775,7 @@
       <c r="M868" s="7"/>
       <c r="O868" s="1"/>
     </row>
-    <row r="869" spans="1:15" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="869" spans="1:15" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A869" s="29" t="s">
         <v>238</v>
       </c>
@@ -47873,7 +47799,7 @@
       <c r="M869" s="7"/>
       <c r="O869" s="1"/>
     </row>
-    <row r="870" spans="1:15" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="870" spans="1:15" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A870" s="29" t="s">
         <v>238</v>
       </c>
@@ -47900,7 +47826,7 @@
       <c r="M870" s="7"/>
       <c r="O870" s="1"/>
     </row>
-    <row r="871" spans="1:15" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="871" spans="1:15" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A871" s="29" t="s">
         <v>238</v>
       </c>
@@ -47929,7 +47855,7 @@
       <c r="M871" s="7"/>
       <c r="O871" s="1"/>
     </row>
-    <row r="872" spans="1:15" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="872" spans="1:15" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A872" s="29" t="s">
         <v>28</v>
       </c>
@@ -47958,7 +47884,7 @@
       <c r="M872" s="7"/>
       <c r="O872" s="1"/>
     </row>
-    <row r="873" spans="1:15" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="873" spans="1:15" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A873" s="29" t="s">
         <v>28</v>
       </c>
@@ -47987,7 +47913,7 @@
       <c r="M873" s="7"/>
       <c r="O873" s="1"/>
     </row>
-    <row r="874" spans="1:15" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="874" spans="1:15" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A874" s="29" t="s">
         <v>28</v>
       </c>
@@ -48016,7 +47942,7 @@
       <c r="M874" s="7"/>
       <c r="O874" s="1"/>
     </row>
-    <row r="875" spans="1:15" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="875" spans="1:15" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A875" s="29" t="s">
         <v>28</v>
       </c>
@@ -48045,7 +47971,7 @@
       <c r="M875" s="7"/>
       <c r="O875" s="1"/>
     </row>
-    <row r="876" spans="1:15" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="876" spans="1:15" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A876" s="29" t="s">
         <v>28</v>
       </c>
@@ -48069,7 +47995,7 @@
       <c r="M876" s="7"/>
       <c r="O876" s="1"/>
     </row>
-    <row r="877" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="877" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A877" s="29" t="s">
         <v>28</v>
       </c>
@@ -48095,7 +48021,7 @@
       <c r="M877" s="7"/>
       <c r="O877" s="1"/>
     </row>
-    <row r="878" spans="1:15" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="878" spans="1:15" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A878" s="29" t="s">
         <v>28</v>
       </c>
@@ -48124,7 +48050,7 @@
       <c r="M878" s="7"/>
       <c r="O878" s="1"/>
     </row>
-    <row r="879" spans="1:15" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="879" spans="1:15" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A879" s="29" t="s">
         <v>32</v>
       </c>
@@ -48153,7 +48079,7 @@
       <c r="M879" s="7"/>
       <c r="O879" s="1"/>
     </row>
-    <row r="880" spans="1:15" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="880" spans="1:15" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A880" s="29" t="s">
         <v>32</v>
       </c>
@@ -48177,7 +48103,7 @@
       <c r="M880" s="7"/>
       <c r="O880" s="1"/>
     </row>
-    <row r="881" spans="1:15" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="881" spans="1:15" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A881" s="29" t="s">
         <v>32</v>
       </c>
@@ -48207,7 +48133,7 @@
       <c r="M881" s="7"/>
       <c r="O881" s="1"/>
     </row>
-    <row r="882" spans="1:15" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="882" spans="1:15" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A882" s="29" t="s">
         <v>32</v>
       </c>
@@ -48236,7 +48162,7 @@
       <c r="M882" s="7"/>
       <c r="O882" s="1"/>
     </row>
-    <row r="883" spans="1:15" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="883" spans="1:15" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A883" s="29" t="s">
         <v>32</v>
       </c>
@@ -48265,7 +48191,7 @@
       <c r="M883" s="7"/>
       <c r="O883" s="1"/>
     </row>
-    <row r="884" spans="1:15" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="884" spans="1:15" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A884" s="29" t="s">
         <v>32</v>
       </c>
@@ -48294,7 +48220,7 @@
       <c r="M884" s="7"/>
       <c r="O884" s="1"/>
     </row>
-    <row r="885" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="885" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A885" s="29" t="s">
         <v>32</v>
       </c>
@@ -48323,7 +48249,7 @@
       <c r="M885" s="7"/>
       <c r="O885" s="1"/>
     </row>
-    <row r="886" spans="1:15" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="886" spans="1:15" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A886" s="29" t="s">
         <v>32</v>
       </c>
@@ -48349,7 +48275,7 @@
       <c r="M886" s="7"/>
       <c r="O886" s="1"/>
     </row>
-    <row r="887" spans="1:15" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="887" spans="1:15" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A887" s="29" t="s">
         <v>32</v>
       </c>
@@ -48379,7 +48305,7 @@
       <c r="M887" s="7"/>
       <c r="O887" s="1"/>
     </row>
-    <row r="888" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="888" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A888" s="29" t="s">
         <v>15</v>
       </c>
@@ -48404,7 +48330,7 @@
       <c r="J888" s="9"/>
       <c r="K888" s="7"/>
     </row>
-    <row r="889" spans="1:15" s="3" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="889" spans="1:15" s="3" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A889" s="29" t="s">
         <v>15</v>
       </c>
@@ -48432,7 +48358,7 @@
       <c r="L889" s="17"/>
       <c r="O889" s="17"/>
     </row>
-    <row r="890" spans="1:15" s="3" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="890" spans="1:15" s="3" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A890" s="29" t="s">
         <v>15</v>
       </c>
@@ -48459,7 +48385,7 @@
       <c r="L890" s="17"/>
       <c r="O890" s="17"/>
     </row>
-    <row r="891" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="891" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A891" s="29" t="s">
         <v>15</v>
       </c>
@@ -48489,7 +48415,7 @@
       <c r="N891" s="9"/>
       <c r="O891" s="18"/>
     </row>
-    <row r="892" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="892" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A892" s="29" t="s">
         <v>67</v>
       </c>
@@ -48514,7 +48440,7 @@
       <c r="J892" s="9"/>
       <c r="K892" s="7"/>
     </row>
-    <row r="893" spans="1:15" s="3" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="893" spans="1:15" s="3" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A893" s="29" t="s">
         <v>67</v>
       </c>
@@ -48542,7 +48468,7 @@
       <c r="L893" s="17"/>
       <c r="O893" s="17"/>
     </row>
-    <row r="894" spans="1:15" s="3" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="894" spans="1:15" s="3" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A894" s="29" t="s">
         <v>67</v>
       </c>
@@ -48569,7 +48495,7 @@
       <c r="L894" s="17"/>
       <c r="O894" s="17"/>
     </row>
-    <row r="895" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="895" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A895" s="29" t="s">
         <v>67</v>
       </c>
@@ -48600,7 +48526,7 @@
       <c r="N895" s="9"/>
       <c r="O895" s="18"/>
     </row>
-    <row r="896" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="896" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A896" s="29" t="s">
         <v>28</v>
       </c>
@@ -48622,7 +48548,7 @@
       <c r="J896" s="9"/>
       <c r="K896" s="7"/>
     </row>
-    <row r="897" spans="1:15" s="3" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="897" spans="1:15" s="3" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A897" s="29" t="s">
         <v>28</v>
       </c>
@@ -48648,7 +48574,7 @@
       <c r="L897" s="17"/>
       <c r="O897" s="17"/>
     </row>
-    <row r="898" spans="1:15" s="3" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="898" spans="1:15" s="3" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A898" s="29" t="s">
         <v>28</v>
       </c>
@@ -48673,7 +48599,7 @@
       <c r="L898" s="17"/>
       <c r="O898" s="17"/>
     </row>
-    <row r="899" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="899" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A899" s="29" t="s">
         <v>28</v>
       </c>
@@ -48701,7 +48627,7 @@
       <c r="N899" s="9"/>
       <c r="O899" s="18"/>
     </row>
-    <row r="900" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="900" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A900" s="29" t="s">
         <v>290</v>
       </c>
@@ -48726,7 +48652,7 @@
       <c r="M900" s="7"/>
       <c r="O900" s="1"/>
     </row>
-    <row r="901" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="901" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A901" s="29" t="s">
         <v>24</v>
       </c>
@@ -48754,7 +48680,7 @@
       <c r="M901" s="7"/>
       <c r="O901" s="1"/>
     </row>
-    <row r="902" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="902" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A902" s="29" t="s">
         <v>60</v>
       </c>
@@ -48782,7 +48708,7 @@
       <c r="M902" s="7"/>
       <c r="O902" s="1"/>
     </row>
-    <row r="903" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="903" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A903" s="29" t="s">
         <v>60</v>
       </c>
@@ -48807,7 +48733,7 @@
       <c r="M903" s="7"/>
       <c r="O903" s="1"/>
     </row>
-    <row r="904" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="904" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A904" s="29" t="s">
         <v>67</v>
       </c>
@@ -48832,7 +48758,7 @@
       <c r="M904" s="7"/>
       <c r="O904" s="1"/>
     </row>
-    <row r="905" spans="1:15" ht="29" x14ac:dyDescent="0.35">
+    <row r="905" spans="1:15" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A905" s="29" t="s">
         <v>60</v>
       </c>
@@ -48859,7 +48785,7 @@
       </c>
       <c r="M905" s="7"/>
     </row>
-    <row r="906" spans="1:15" ht="29" x14ac:dyDescent="0.35">
+    <row r="906" spans="1:15" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A906" s="29" t="s">
         <v>52</v>
       </c>
@@ -48886,7 +48812,7 @@
       </c>
       <c r="M906" s="7"/>
     </row>
-    <row r="907" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="907" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A907" s="29" t="s">
         <v>52</v>
       </c>
@@ -48913,7 +48839,7 @@
       </c>
       <c r="M907" s="7"/>
     </row>
-    <row r="908" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="908" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A908" s="29" t="s">
         <v>52</v>
       </c>
@@ -48940,7 +48866,7 @@
       </c>
       <c r="M908" s="7"/>
     </row>
-    <row r="909" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="909" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A909" s="29" t="s">
         <v>52</v>
       </c>
@@ -48967,7 +48893,7 @@
       </c>
       <c r="M909" s="7"/>
     </row>
-    <row r="910" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="910" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A910" s="29" t="s">
         <v>52</v>
       </c>
@@ -48988,7 +48914,7 @@
       </c>
       <c r="M910" s="7"/>
     </row>
-    <row r="911" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="911" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A911" s="29" t="s">
         <v>52</v>
       </c>
@@ -49012,7 +48938,7 @@
       </c>
       <c r="M911" s="7"/>
     </row>
-    <row r="912" spans="1:15" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="912" spans="1:15" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A912" s="29" t="s">
         <v>52</v>
       </c>
@@ -49035,7 +48961,7 @@
       <c r="M912" s="7"/>
       <c r="O912" s="1"/>
     </row>
-    <row r="913" spans="1:15" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="913" spans="1:15" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A913" s="29" t="s">
         <v>52</v>
       </c>
@@ -49058,7 +48984,7 @@
       <c r="M913" s="7"/>
       <c r="O913" s="1"/>
     </row>
-    <row r="914" spans="1:15" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="914" spans="1:15" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A914" s="29" t="s">
         <v>52</v>
       </c>
@@ -49087,7 +49013,7 @@
       <c r="M914" s="7"/>
       <c r="O914" s="1"/>
     </row>
-    <row r="915" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="915" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A915" s="29" t="s">
         <v>60</v>
       </c>
@@ -49114,7 +49040,7 @@
       </c>
       <c r="M915" s="7"/>
     </row>
-    <row r="916" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="916" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A916" s="29" t="s">
         <v>60</v>
       </c>
@@ -49141,7 +49067,7 @@
       </c>
       <c r="M916" s="7"/>
     </row>
-    <row r="917" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="917" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A917" s="29" t="s">
         <v>60</v>
       </c>
@@ -49168,7 +49094,7 @@
       </c>
       <c r="M917" s="7"/>
     </row>
-    <row r="918" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="918" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A918" s="29" t="s">
         <v>60</v>
       </c>
@@ -49198,7 +49124,7 @@
       </c>
       <c r="M918" s="7"/>
     </row>
-    <row r="919" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="919" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A919" s="29" t="s">
         <v>60</v>
       </c>
@@ -49226,7 +49152,7 @@
       <c r="I919" s="27"/>
       <c r="M919" s="7"/>
     </row>
-    <row r="920" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="920" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A920" s="29" t="s">
         <v>60</v>
       </c>
@@ -49254,7 +49180,7 @@
       <c r="I920" s="27"/>
       <c r="M920" s="7"/>
     </row>
-    <row r="921" spans="1:15" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="921" spans="1:15" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A921" s="29" t="s">
         <v>60</v>
       </c>
@@ -49277,7 +49203,7 @@
       <c r="M921" s="7"/>
       <c r="O921" s="1"/>
     </row>
-    <row r="922" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="922" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A922" s="29" t="s">
         <v>60</v>
       </c>
@@ -49300,7 +49226,7 @@
       <c r="M922" s="7"/>
       <c r="O922" s="1"/>
     </row>
-    <row r="923" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="923" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A923" s="29" t="s">
         <v>60</v>
       </c>
@@ -49329,7 +49255,7 @@
       <c r="M923" s="7"/>
       <c r="O923" s="1"/>
     </row>
-    <row r="924" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="924" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A924" s="29" t="s">
         <v>60</v>
       </c>
@@ -49358,7 +49284,7 @@
       <c r="M924" s="7"/>
       <c r="O924" s="1"/>
     </row>
-    <row r="925" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="925" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A925" s="29" t="s">
         <v>60</v>
       </c>
@@ -49387,7 +49313,7 @@
       <c r="M925" s="7"/>
       <c r="O925" s="1"/>
     </row>
-    <row r="926" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="926" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A926" s="29" t="s">
         <v>15</v>
       </c>
@@ -49409,7 +49335,7 @@
       <c r="I926" s="27"/>
       <c r="M926" s="7"/>
     </row>
-    <row r="927" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="927" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A927" s="29" t="s">
         <v>15</v>
       </c>
@@ -49437,7 +49363,7 @@
       <c r="M927" s="7"/>
       <c r="O927" s="1"/>
     </row>
-    <row r="928" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="928" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A928" s="29" t="s">
         <v>15</v>
       </c>
@@ -49466,7 +49392,7 @@
       <c r="M928" s="7"/>
       <c r="O928" s="1"/>
     </row>
-    <row r="929" spans="1:15" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="929" spans="1:15" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A929" s="29" t="s">
         <v>15</v>
       </c>
@@ -49489,7 +49415,7 @@
       <c r="M929" s="7"/>
       <c r="O929" s="1"/>
     </row>
-    <row r="930" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="930" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A930" s="29" t="s">
         <v>15</v>
       </c>
@@ -49512,7 +49438,7 @@
       <c r="M930" s="7"/>
       <c r="O930" s="1"/>
     </row>
-    <row r="931" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="931" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A931" s="29" t="s">
         <v>15</v>
       </c>
@@ -49541,7 +49467,7 @@
       <c r="M931" s="7"/>
       <c r="O931" s="1"/>
     </row>
-    <row r="932" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="932" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A932" s="29" t="s">
         <v>15</v>
       </c>
@@ -49570,7 +49496,7 @@
       <c r="M932" s="7"/>
       <c r="O932" s="1"/>
     </row>
-    <row r="933" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="933" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A933" s="29" t="s">
         <v>67</v>
       </c>
@@ -49599,7 +49525,7 @@
       <c r="M933" s="7"/>
       <c r="O933" s="1"/>
     </row>
-    <row r="934" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="934" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A934" s="29" t="s">
         <v>67</v>
       </c>
@@ -49622,7 +49548,7 @@
       <c r="M934" s="7"/>
       <c r="O934" s="1"/>
     </row>
-    <row r="935" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="935" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A935" s="29" t="s">
         <v>67</v>
       </c>
@@ -49645,7 +49571,7 @@
       <c r="M935" s="7"/>
       <c r="O935" s="1"/>
     </row>
-    <row r="936" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="936" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A936" s="29" t="s">
         <v>67</v>
       </c>
@@ -49668,7 +49594,7 @@
       <c r="M936" s="7"/>
       <c r="O936" s="1"/>
     </row>
-    <row r="937" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="937" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A937" s="29" t="s">
         <v>67</v>
       </c>
@@ -49691,7 +49617,7 @@
       <c r="M937" s="7"/>
       <c r="O937" s="1"/>
     </row>
-    <row r="938" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="938" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A938" s="29" t="s">
         <v>67</v>
       </c>
@@ -49720,7 +49646,7 @@
       <c r="M938" s="7"/>
       <c r="O938" s="1"/>
     </row>
-    <row r="939" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="939" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A939" s="29" t="s">
         <v>290</v>
       </c>
@@ -49749,7 +49675,7 @@
       <c r="M939" s="7"/>
       <c r="O939" s="1"/>
     </row>
-    <row r="940" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="940" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A940" s="29" t="s">
         <v>290</v>
       </c>
@@ -49778,7 +49704,7 @@
       <c r="M940" s="7"/>
       <c r="O940" s="1"/>
     </row>
-    <row r="941" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="941" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A941" s="29" t="s">
         <v>290</v>
       </c>
@@ -49801,7 +49727,7 @@
       <c r="M941" s="7"/>
       <c r="O941" s="1"/>
     </row>
-    <row r="942" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="942" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A942" s="29" t="s">
         <v>290</v>
       </c>
@@ -49824,7 +49750,7 @@
       <c r="M942" s="7"/>
       <c r="O942" s="1"/>
     </row>
-    <row r="943" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="943" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A943" s="29" t="s">
         <v>290</v>
       </c>
@@ -49847,7 +49773,7 @@
       <c r="M943" s="7"/>
       <c r="O943" s="1"/>
     </row>
-    <row r="944" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="944" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A944" s="29" t="s">
         <v>290</v>
       </c>
@@ -49870,7 +49796,7 @@
       <c r="M944" s="7"/>
       <c r="O944" s="1"/>
     </row>
-    <row r="945" spans="1:15" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="945" spans="1:15" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A945" s="29" t="s">
         <v>290</v>
       </c>
@@ -49893,7 +49819,7 @@
       <c r="M945" s="7"/>
       <c r="O945" s="1"/>
     </row>
-    <row r="946" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="946" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A946" s="29" t="s">
         <v>24</v>
       </c>
@@ -49919,7 +49845,7 @@
       <c r="M946" s="7"/>
       <c r="O946" s="1"/>
     </row>
-    <row r="947" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="947" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A947" s="29" t="s">
         <v>24</v>
       </c>
@@ -49945,7 +49871,7 @@
       <c r="M947" s="7"/>
       <c r="O947" s="1"/>
     </row>
-    <row r="948" spans="1:15" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="948" spans="1:15" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A948" s="29" t="s">
         <v>24</v>
       </c>
@@ -49968,7 +49894,7 @@
       <c r="M948" s="7"/>
       <c r="O948" s="1"/>
     </row>
-    <row r="949" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="949" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A949" s="29" t="s">
         <v>24</v>
       </c>
@@ -49994,7 +49920,7 @@
       <c r="M949" s="7"/>
       <c r="O949" s="1"/>
     </row>
-    <row r="950" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="950" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A950" s="29" t="s">
         <v>24</v>
       </c>
@@ -50023,7 +49949,7 @@
       <c r="M950" s="7"/>
       <c r="O950" s="1"/>
     </row>
-    <row r="951" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="951" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A951" s="29" t="s">
         <v>24</v>
       </c>
@@ -50046,7 +49972,7 @@
       <c r="M951" s="7"/>
       <c r="O951" s="1"/>
     </row>
-    <row r="952" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="952" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A952" s="29" t="s">
         <v>238</v>
       </c>
@@ -50069,7 +49995,7 @@
       <c r="M952" s="7"/>
       <c r="O952" s="1"/>
     </row>
-    <row r="953" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="953" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A953" s="29" t="s">
         <v>238</v>
       </c>
@@ -50092,7 +50018,7 @@
       <c r="M953" s="7"/>
       <c r="O953" s="1"/>
     </row>
-    <row r="954" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="954" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A954" s="29" t="s">
         <v>238</v>
       </c>
@@ -50120,7 +50046,7 @@
       <c r="M954" s="7"/>
       <c r="O954" s="1"/>
     </row>
-    <row r="955" spans="1:15" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="955" spans="1:15" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A955" s="29" t="s">
         <v>238</v>
       </c>
@@ -50146,7 +50072,7 @@
       <c r="M955" s="7"/>
       <c r="O955" s="1"/>
     </row>
-    <row r="956" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="956" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A956" s="29" t="s">
         <v>28</v>
       </c>
@@ -50173,7 +50099,7 @@
       </c>
       <c r="M956" s="7"/>
     </row>
-    <row r="957" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="957" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A957" s="29" t="s">
         <v>28</v>
       </c>
@@ -50197,7 +50123,7 @@
       </c>
       <c r="M957" s="7"/>
     </row>
-    <row r="958" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="958" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A958" s="29" t="s">
         <v>28</v>
       </c>
@@ -50218,7 +50144,7 @@
       </c>
       <c r="M958" s="7"/>
     </row>
-    <row r="959" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="959" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A959" s="29" t="s">
         <v>28</v>
       </c>
@@ -50245,7 +50171,7 @@
       </c>
       <c r="M959" s="7"/>
     </row>
-    <row r="960" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="960" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A960" s="29" t="s">
         <v>28</v>
       </c>
@@ -50272,7 +50198,7 @@
       </c>
       <c r="M960" s="7"/>
     </row>
-    <row r="961" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="961" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A961" s="29" t="s">
         <v>32</v>
       </c>
@@ -50299,7 +50225,7 @@
       </c>
       <c r="M961" s="7"/>
     </row>
-    <row r="962" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="962" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A962" s="29" t="s">
         <v>32</v>
       </c>
@@ -50323,7 +50249,7 @@
       </c>
       <c r="M962" s="7"/>
     </row>
-    <row r="963" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="963" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A963" s="29" t="s">
         <v>32</v>
       </c>
@@ -50347,7 +50273,7 @@
       </c>
       <c r="M963" s="7"/>
     </row>
-    <row r="964" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="964" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A964" s="29" t="s">
         <v>32</v>
       </c>
@@ -50368,7 +50294,7 @@
       </c>
       <c r="M964" s="7"/>
     </row>
-    <row r="965" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="965" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A965" s="29" t="s">
         <v>32</v>
       </c>
@@ -50391,7 +50317,7 @@
       <c r="M965" s="7"/>
       <c r="O965" s="1"/>
     </row>
-    <row r="966" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="966" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A966" s="29" t="s">
         <v>52</v>
       </c>
@@ -50411,7 +50337,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="967" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="967" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A967" s="29" t="s">
         <v>60</v>
       </c>
@@ -50431,7 +50357,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="968" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="968" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A968" s="29" t="s">
         <v>60</v>
       </c>
@@ -50454,7 +50380,7 @@
         <v>585</v>
       </c>
     </row>
-    <row r="969" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="969" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A969" s="29" t="s">
         <v>15</v>
       </c>
@@ -50474,7 +50400,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="970" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="970" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A970" s="29" t="s">
         <v>67</v>
       </c>
@@ -50494,7 +50420,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="971" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="971" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A971" s="29" t="s">
         <v>24</v>
       </c>
@@ -50514,7 +50440,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="972" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="972" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A972" s="29" t="s">
         <v>28</v>
       </c>
@@ -50534,7 +50460,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="973" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="973" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A973" s="29" t="s">
         <v>32</v>
       </c>
@@ -50564,74 +50490,74 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:BG46"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="31.54296875" customWidth="1"/>
-    <col min="2" max="2" width="21.26953125" customWidth="1"/>
-    <col min="3" max="7" width="1.81640625" customWidth="1"/>
-    <col min="8" max="8" width="9.81640625" customWidth="1"/>
-    <col min="9" max="13" width="1.81640625" customWidth="1"/>
-    <col min="14" max="14" width="15.7265625" customWidth="1"/>
-    <col min="15" max="17" width="1.81640625" customWidth="1"/>
-    <col min="18" max="18" width="6.90625" customWidth="1"/>
-    <col min="19" max="23" width="1.81640625" customWidth="1"/>
-    <col min="24" max="24" width="9.1796875" customWidth="1"/>
-    <col min="25" max="29" width="1.81640625" customWidth="1"/>
-    <col min="30" max="30" width="13.81640625" customWidth="1"/>
-    <col min="31" max="35" width="1.81640625" customWidth="1"/>
-    <col min="36" max="36" width="14.08984375" customWidth="1"/>
-    <col min="37" max="37" width="10.81640625" customWidth="1"/>
-    <col min="38" max="42" width="10.08984375" bestFit="1" customWidth="1"/>
-    <col min="43" max="43" width="17.54296875" customWidth="1"/>
-    <col min="44" max="48" width="1.81640625" customWidth="1"/>
-    <col min="49" max="49" width="13.54296875" customWidth="1"/>
-    <col min="50" max="53" width="1.81640625" customWidth="1"/>
-    <col min="54" max="54" width="11.26953125" customWidth="1"/>
-    <col min="55" max="57" width="1.81640625" customWidth="1"/>
+    <col min="1" max="1" width="31.5546875" customWidth="1"/>
+    <col min="2" max="2" width="21.21875" customWidth="1"/>
+    <col min="3" max="7" width="1.77734375" customWidth="1"/>
+    <col min="8" max="8" width="9.77734375" customWidth="1"/>
+    <col min="9" max="13" width="1.77734375" customWidth="1"/>
+    <col min="14" max="14" width="15.77734375" customWidth="1"/>
+    <col min="15" max="17" width="1.77734375" customWidth="1"/>
+    <col min="18" max="18" width="6.88671875" customWidth="1"/>
+    <col min="19" max="23" width="1.77734375" customWidth="1"/>
+    <col min="24" max="24" width="9.21875" customWidth="1"/>
+    <col min="25" max="29" width="1.77734375" customWidth="1"/>
+    <col min="30" max="30" width="13.77734375" customWidth="1"/>
+    <col min="31" max="35" width="1.77734375" customWidth="1"/>
+    <col min="36" max="36" width="14.109375" customWidth="1"/>
+    <col min="37" max="37" width="10.77734375" customWidth="1"/>
+    <col min="38" max="42" width="10.109375" bestFit="1" customWidth="1"/>
+    <col min="43" max="43" width="17.5546875" customWidth="1"/>
+    <col min="44" max="48" width="1.77734375" customWidth="1"/>
+    <col min="49" max="49" width="13.5546875" customWidth="1"/>
+    <col min="50" max="53" width="1.77734375" customWidth="1"/>
+    <col min="54" max="54" width="11.21875" customWidth="1"/>
+    <col min="55" max="57" width="1.77734375" customWidth="1"/>
     <col min="58" max="58" width="12" customWidth="1"/>
-    <col min="59" max="61" width="1.81640625" customWidth="1"/>
-    <col min="62" max="64" width="2.81640625" customWidth="1"/>
-    <col min="65" max="65" width="1.81640625" customWidth="1"/>
-    <col min="66" max="66" width="14.08984375" customWidth="1"/>
-    <col min="67" max="67" width="2.81640625" customWidth="1"/>
-    <col min="68" max="68" width="10.81640625" customWidth="1"/>
-    <col min="69" max="75" width="1.81640625" customWidth="1"/>
-    <col min="76" max="78" width="2.81640625" customWidth="1"/>
-    <col min="79" max="79" width="1.81640625" customWidth="1"/>
-    <col min="80" max="80" width="17.54296875" customWidth="1"/>
-    <col min="81" max="85" width="1.81640625" customWidth="1"/>
-    <col min="86" max="88" width="2.81640625" customWidth="1"/>
-    <col min="89" max="89" width="1.81640625" customWidth="1"/>
+    <col min="59" max="61" width="1.77734375" customWidth="1"/>
+    <col min="62" max="64" width="2.77734375" customWidth="1"/>
+    <col min="65" max="65" width="1.77734375" customWidth="1"/>
+    <col min="66" max="66" width="14.109375" customWidth="1"/>
+    <col min="67" max="67" width="2.77734375" customWidth="1"/>
+    <col min="68" max="68" width="10.77734375" customWidth="1"/>
+    <col min="69" max="75" width="1.77734375" customWidth="1"/>
+    <col min="76" max="78" width="2.77734375" customWidth="1"/>
+    <col min="79" max="79" width="1.77734375" customWidth="1"/>
+    <col min="80" max="80" width="17.5546875" customWidth="1"/>
+    <col min="81" max="85" width="1.77734375" customWidth="1"/>
+    <col min="86" max="88" width="2.77734375" customWidth="1"/>
+    <col min="89" max="89" width="1.77734375" customWidth="1"/>
     <col min="90" max="90" width="20" bestFit="1" customWidth="1"/>
-    <col min="91" max="91" width="13.54296875" customWidth="1"/>
-    <col min="92" max="97" width="1.81640625" customWidth="1"/>
-    <col min="98" max="100" width="2.81640625" customWidth="1"/>
-    <col min="101" max="101" width="1.81640625" customWidth="1"/>
-    <col min="102" max="102" width="11.1796875" customWidth="1"/>
-    <col min="103" max="105" width="1.81640625" customWidth="1"/>
-    <col min="106" max="108" width="2.81640625" customWidth="1"/>
-    <col min="109" max="109" width="1.81640625" customWidth="1"/>
+    <col min="91" max="91" width="13.5546875" customWidth="1"/>
+    <col min="92" max="97" width="1.77734375" customWidth="1"/>
+    <col min="98" max="100" width="2.77734375" customWidth="1"/>
+    <col min="101" max="101" width="1.77734375" customWidth="1"/>
+    <col min="102" max="102" width="11.21875" customWidth="1"/>
+    <col min="103" max="105" width="1.77734375" customWidth="1"/>
+    <col min="106" max="108" width="2.77734375" customWidth="1"/>
+    <col min="109" max="109" width="1.77734375" customWidth="1"/>
     <col min="110" max="110" width="12" customWidth="1"/>
-    <col min="111" max="111" width="1.81640625" customWidth="1"/>
-    <col min="112" max="113" width="2.81640625" customWidth="1"/>
-    <col min="114" max="114" width="20.54296875" bestFit="1" customWidth="1"/>
+    <col min="111" max="111" width="1.77734375" customWidth="1"/>
+    <col min="112" max="113" width="2.77734375" customWidth="1"/>
+    <col min="114" max="114" width="20.5546875" bestFit="1" customWidth="1"/>
     <col min="115" max="115" width="20" bestFit="1" customWidth="1"/>
     <col min="116" max="116" width="23" bestFit="1" customWidth="1"/>
-    <col min="117" max="117" width="13.54296875" bestFit="1" customWidth="1"/>
-    <col min="118" max="123" width="1.81640625" customWidth="1"/>
-    <col min="124" max="126" width="2.81640625" customWidth="1"/>
-    <col min="127" max="127" width="16.54296875" bestFit="1" customWidth="1"/>
-    <col min="128" max="128" width="11.1796875" bestFit="1" customWidth="1"/>
-    <col min="129" max="131" width="1.81640625" customWidth="1"/>
-    <col min="132" max="134" width="2.81640625" customWidth="1"/>
-    <col min="135" max="135" width="14.1796875" bestFit="1" customWidth="1"/>
+    <col min="117" max="117" width="13.5546875" bestFit="1" customWidth="1"/>
+    <col min="118" max="123" width="1.77734375" customWidth="1"/>
+    <col min="124" max="126" width="2.77734375" customWidth="1"/>
+    <col min="127" max="127" width="16.5546875" bestFit="1" customWidth="1"/>
+    <col min="128" max="128" width="11.21875" bestFit="1" customWidth="1"/>
+    <col min="129" max="131" width="1.77734375" customWidth="1"/>
+    <col min="132" max="134" width="2.77734375" customWidth="1"/>
+    <col min="135" max="135" width="14.21875" bestFit="1" customWidth="1"/>
     <col min="136" max="136" width="12" bestFit="1" customWidth="1"/>
-    <col min="137" max="137" width="1.81640625" customWidth="1"/>
-    <col min="138" max="138" width="14.90625" bestFit="1" customWidth="1"/>
-    <col min="139" max="139" width="11.81640625" bestFit="1" customWidth="1"/>
+    <col min="137" max="137" width="1.77734375" customWidth="1"/>
+    <col min="138" max="138" width="14.88671875" bestFit="1" customWidth="1"/>
+    <col min="139" max="139" width="11.77734375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:59" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A1" s="4" t="s">
         <v>311</v>
       </c>
@@ -50639,7 +50565,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="3" spans="1:59" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A3" s="4" t="s">
         <v>119</v>
       </c>
@@ -50647,7 +50573,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="4" spans="1:59" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:59" x14ac:dyDescent="0.3">
       <c r="B4" t="s">
         <v>3</v>
       </c>
@@ -50685,7 +50611,7 @@
         <v>467</v>
       </c>
     </row>
-    <row r="5" spans="1:59" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A5" s="4" t="s">
         <v>11</v>
       </c>
@@ -50864,7 +50790,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="6" spans="1:59" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
         <v>52</v>
       </c>
@@ -50989,7 +50915,7 @@
       <c r="BF6" s="5"/>
       <c r="BG6" s="5"/>
     </row>
-    <row r="7" spans="1:59" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="s">
         <v>60</v>
       </c>
@@ -51142,7 +51068,7 @@
       <c r="BF7" s="5"/>
       <c r="BG7" s="5"/>
     </row>
-    <row r="8" spans="1:59" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
         <v>15</v>
       </c>
@@ -51281,7 +51207,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:59" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A9" s="2" t="s">
         <v>67</v>
       </c>
@@ -51396,7 +51322,7 @@
       </c>
       <c r="BG9" s="5"/>
     </row>
-    <row r="10" spans="1:59" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A10" s="2" t="s">
         <v>259</v>
       </c>
@@ -51467,7 +51393,7 @@
       <c r="BF10" s="5"/>
       <c r="BG10" s="5"/>
     </row>
-    <row r="11" spans="1:59" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A11" s="2" t="s">
         <v>290</v>
       </c>
@@ -51570,7 +51496,7 @@
       <c r="BF11" s="5"/>
       <c r="BG11" s="5"/>
     </row>
-    <row r="12" spans="1:59" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A12" s="2" t="s">
         <v>292</v>
       </c>
@@ -51641,7 +51567,7 @@
       <c r="BF12" s="5"/>
       <c r="BG12" s="5"/>
     </row>
-    <row r="13" spans="1:59" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A13" s="2" t="s">
         <v>24</v>
       </c>
@@ -51772,7 +51698,7 @@
       <c r="BF13" s="5"/>
       <c r="BG13" s="5"/>
     </row>
-    <row r="14" spans="1:59" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A14" s="2" t="s">
         <v>238</v>
       </c>
@@ -51863,7 +51789,7 @@
       <c r="BF14" s="5"/>
       <c r="BG14" s="5"/>
     </row>
-    <row r="15" spans="1:59" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A15" s="2" t="s">
         <v>28</v>
       </c>
@@ -51986,7 +51912,7 @@
       <c r="BF15" s="5"/>
       <c r="BG15" s="5"/>
     </row>
-    <row r="16" spans="1:59" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A16" s="2" t="s">
         <v>32</v>
       </c>
@@ -52107,7 +52033,7 @@
       </c>
       <c r="BG16" s="5"/>
     </row>
-    <row r="18" spans="1:59" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A18" s="2"/>
       <c r="B18" s="5"/>
       <c r="C18" s="5"/>
@@ -52147,7 +52073,7 @@
       <c r="AK18" s="5"/>
       <c r="AL18" s="5"/>
     </row>
-    <row r="19" spans="1:59" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A19" s="2"/>
       <c r="B19" s="5"/>
       <c r="C19" s="5"/>
@@ -52187,7 +52113,7 @@
       <c r="AK19" s="5"/>
       <c r="AL19" s="5"/>
     </row>
-    <row r="20" spans="1:59" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A20" s="4" t="s">
         <v>311</v>
       </c>
@@ -52195,7 +52121,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="22" spans="1:59" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A22" s="4" t="s">
         <v>121</v>
       </c>
@@ -52203,7 +52129,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="23" spans="1:59" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:59" x14ac:dyDescent="0.3">
       <c r="B23" t="s">
         <v>3</v>
       </c>
@@ -52241,7 +52167,7 @@
         <v>467</v>
       </c>
     </row>
-    <row r="24" spans="1:59" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A24" s="4" t="s">
         <v>11</v>
       </c>
@@ -52420,7 +52346,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="25" spans="1:59" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A25" s="2" t="s">
         <v>313</v>
       </c>
@@ -52485,7 +52411,7 @@
       <c r="BF25" s="6"/>
       <c r="BG25" s="6"/>
     </row>
-    <row r="26" spans="1:59" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A26" s="2" t="s">
         <v>52</v>
       </c>
@@ -52610,7 +52536,7 @@
       <c r="BF26" s="6"/>
       <c r="BG26" s="6"/>
     </row>
-    <row r="27" spans="1:59" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A27" s="2" t="s">
         <v>60</v>
       </c>
@@ -52763,7 +52689,7 @@
       <c r="BF27" s="6"/>
       <c r="BG27" s="6"/>
     </row>
-    <row r="28" spans="1:59" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A28" s="2" t="s">
         <v>15</v>
       </c>
@@ -52902,7 +52828,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:59" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A29" s="2" t="s">
         <v>67</v>
       </c>
@@ -53017,7 +52943,7 @@
       </c>
       <c r="BG29" s="6"/>
     </row>
-    <row r="30" spans="1:59" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A30" s="2" t="s">
         <v>290</v>
       </c>
@@ -53120,7 +53046,7 @@
       <c r="BF30" s="6"/>
       <c r="BG30" s="6"/>
     </row>
-    <row r="31" spans="1:59" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A31" s="2" t="s">
         <v>24</v>
       </c>
@@ -53251,7 +53177,7 @@
       <c r="BF31" s="6"/>
       <c r="BG31" s="6"/>
     </row>
-    <row r="32" spans="1:59" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A32" s="2" t="s">
         <v>238</v>
       </c>
@@ -53342,7 +53268,7 @@
       <c r="BF32" s="6"/>
       <c r="BG32" s="6"/>
     </row>
-    <row r="33" spans="1:59" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A33" s="2" t="s">
         <v>28</v>
       </c>
@@ -53465,7 +53391,7 @@
       <c r="BF33" s="6"/>
       <c r="BG33" s="6"/>
     </row>
-    <row r="34" spans="1:59" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A34" s="2" t="s">
         <v>32</v>
       </c>
@@ -53586,7 +53512,7 @@
       </c>
       <c r="BG34" s="6"/>
     </row>
-    <row r="35" spans="1:59" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A35" s="2" t="s">
         <v>468</v>
       </c>
@@ -53761,7 +53687,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="43" spans="1:59" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A43" s="2" t="s">
         <v>124</v>
       </c>
@@ -53772,7 +53698,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="44" spans="1:59" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A44" s="2" t="s">
         <v>120</v>
       </c>
@@ -53783,7 +53709,7 @@
       <c r="E44" s="1"/>
       <c r="F44" s="1"/>
     </row>
-    <row r="45" spans="1:59" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A45" s="2" t="s">
         <v>126</v>
       </c>
@@ -53791,7 +53717,7 @@
       <c r="E45" s="1"/>
       <c r="F45" s="1"/>
     </row>
-    <row r="46" spans="1:59" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:59" x14ac:dyDescent="0.3">
       <c r="A46" s="2" t="s">
         <v>127</v>
       </c>
@@ -53808,60 +53734,60 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:M16"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="31.6328125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="21.453125" bestFit="1" customWidth="1"/>
-    <col min="3" max="13" width="11.90625" bestFit="1" customWidth="1"/>
-    <col min="14" max="23" width="11.6328125" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="5.453125" customWidth="1"/>
-    <col min="25" max="25" width="7.6328125" customWidth="1"/>
-    <col min="26" max="26" width="9.81640625" customWidth="1"/>
-    <col min="27" max="27" width="12.36328125" customWidth="1"/>
-    <col min="28" max="28" width="9.36328125" customWidth="1"/>
-    <col min="29" max="29" width="16.36328125" customWidth="1"/>
-    <col min="30" max="30" width="6.6328125" customWidth="1"/>
-    <col min="31" max="31" width="4.1796875" customWidth="1"/>
-    <col min="32" max="32" width="8.453125" customWidth="1"/>
-    <col min="33" max="33" width="9.36328125" customWidth="1"/>
-    <col min="34" max="34" width="5.453125" customWidth="1"/>
-    <col min="35" max="35" width="7.6328125" customWidth="1"/>
-    <col min="36" max="36" width="9.81640625" customWidth="1"/>
-    <col min="37" max="37" width="12.36328125" customWidth="1"/>
-    <col min="38" max="38" width="9.36328125" customWidth="1"/>
-    <col min="39" max="39" width="16.36328125" customWidth="1"/>
-    <col min="40" max="40" width="18.6328125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="31.6640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="21.44140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="13" width="11.88671875" bestFit="1" customWidth="1"/>
+    <col min="14" max="23" width="11.6640625" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="5.44140625" customWidth="1"/>
+    <col min="25" max="25" width="7.6640625" customWidth="1"/>
+    <col min="26" max="26" width="9.77734375" customWidth="1"/>
+    <col min="27" max="27" width="12.33203125" customWidth="1"/>
+    <col min="28" max="28" width="9.33203125" customWidth="1"/>
+    <col min="29" max="29" width="16.33203125" customWidth="1"/>
+    <col min="30" max="30" width="6.6640625" customWidth="1"/>
+    <col min="31" max="31" width="4.21875" customWidth="1"/>
+    <col min="32" max="32" width="8.44140625" customWidth="1"/>
+    <col min="33" max="33" width="9.33203125" customWidth="1"/>
+    <col min="34" max="34" width="5.44140625" customWidth="1"/>
+    <col min="35" max="35" width="7.6640625" customWidth="1"/>
+    <col min="36" max="36" width="9.77734375" customWidth="1"/>
+    <col min="37" max="37" width="12.33203125" customWidth="1"/>
+    <col min="38" max="38" width="9.33203125" customWidth="1"/>
+    <col min="39" max="39" width="16.33203125" customWidth="1"/>
+    <col min="40" max="40" width="18.6640625" bestFit="1" customWidth="1"/>
     <col min="41" max="41" width="12" customWidth="1"/>
-    <col min="42" max="42" width="9.90625" customWidth="1"/>
-    <col min="43" max="43" width="6.6328125" customWidth="1"/>
-    <col min="44" max="44" width="4.1796875" customWidth="1"/>
-    <col min="45" max="45" width="8.453125" customWidth="1"/>
-    <col min="46" max="46" width="9.36328125" customWidth="1"/>
-    <col min="47" max="47" width="5.453125" customWidth="1"/>
-    <col min="48" max="48" width="7.6328125" customWidth="1"/>
-    <col min="49" max="49" width="9.81640625" customWidth="1"/>
-    <col min="50" max="50" width="12.36328125" customWidth="1"/>
-    <col min="51" max="51" width="9.36328125" customWidth="1"/>
-    <col min="52" max="52" width="16.36328125" bestFit="1" customWidth="1"/>
+    <col min="42" max="42" width="9.88671875" customWidth="1"/>
+    <col min="43" max="43" width="6.6640625" customWidth="1"/>
+    <col min="44" max="44" width="4.21875" customWidth="1"/>
+    <col min="45" max="45" width="8.44140625" customWidth="1"/>
+    <col min="46" max="46" width="9.33203125" customWidth="1"/>
+    <col min="47" max="47" width="5.44140625" customWidth="1"/>
+    <col min="48" max="48" width="7.6640625" customWidth="1"/>
+    <col min="49" max="49" width="9.77734375" customWidth="1"/>
+    <col min="50" max="50" width="12.33203125" customWidth="1"/>
+    <col min="51" max="51" width="9.33203125" customWidth="1"/>
+    <col min="52" max="52" width="16.33203125" bestFit="1" customWidth="1"/>
     <col min="53" max="53" width="12" customWidth="1"/>
-    <col min="54" max="54" width="9.90625" customWidth="1"/>
-    <col min="55" max="55" width="6.6328125" customWidth="1"/>
+    <col min="54" max="54" width="9.88671875" customWidth="1"/>
+    <col min="55" max="55" width="6.6640625" customWidth="1"/>
     <col min="56" max="56" width="5" customWidth="1"/>
-    <col min="57" max="57" width="8.453125" customWidth="1"/>
-    <col min="58" max="58" width="9.36328125" customWidth="1"/>
-    <col min="59" max="59" width="5.453125" customWidth="1"/>
-    <col min="60" max="60" width="7.6328125" customWidth="1"/>
-    <col min="61" max="61" width="9.81640625" customWidth="1"/>
-    <col min="62" max="62" width="12.36328125" customWidth="1"/>
-    <col min="63" max="63" width="9.36328125" customWidth="1"/>
-    <col min="64" max="64" width="16.36328125" bestFit="1" customWidth="1"/>
+    <col min="57" max="57" width="8.44140625" customWidth="1"/>
+    <col min="58" max="58" width="9.33203125" customWidth="1"/>
+    <col min="59" max="59" width="5.44140625" customWidth="1"/>
+    <col min="60" max="60" width="7.6640625" customWidth="1"/>
+    <col min="61" max="61" width="9.77734375" customWidth="1"/>
+    <col min="62" max="62" width="12.33203125" customWidth="1"/>
+    <col min="63" max="63" width="9.33203125" customWidth="1"/>
+    <col min="64" max="64" width="16.33203125" bestFit="1" customWidth="1"/>
     <col min="65" max="65" width="12" customWidth="1"/>
-    <col min="66" max="66" width="9.90625" customWidth="1"/>
-    <col min="67" max="67" width="7.6328125" customWidth="1"/>
-    <col min="68" max="68" width="11.90625" bestFit="1" customWidth="1"/>
+    <col min="66" max="66" width="9.88671875" customWidth="1"/>
+    <col min="67" max="67" width="7.6640625" customWidth="1"/>
+    <col min="68" max="68" width="11.88671875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A1" s="4" t="s">
         <v>242</v>
       </c>
@@ -53869,7 +53795,7 @@
         <v>241</v>
       </c>
     </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A2" s="4" t="s">
         <v>311</v>
       </c>
@@ -53877,7 +53803,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A4" s="4" t="s">
         <v>121</v>
       </c>
@@ -53885,7 +53811,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.3">
       <c r="B5" t="s">
         <v>12</v>
       </c>
@@ -53893,7 +53819,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A6" s="4" t="s">
         <v>11</v>
       </c>
@@ -53934,7 +53860,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="s">
         <v>52</v>
       </c>
@@ -53975,7 +53901,7 @@
         <v>1345400.72</v>
       </c>
     </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
         <v>60</v>
       </c>
@@ -54016,7 +53942,7 @@
         <v>482850.5</v>
       </c>
     </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A9" s="2" t="s">
         <v>15</v>
       </c>
@@ -54057,7 +53983,7 @@
         <v>300750</v>
       </c>
     </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A10" s="2" t="s">
         <v>67</v>
       </c>
@@ -54098,7 +54024,7 @@
         <v>372568.23</v>
       </c>
     </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A11" s="2" t="s">
         <v>24</v>
       </c>
@@ -54139,7 +54065,7 @@
         <v>2407649.61</v>
       </c>
     </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A12" s="2" t="s">
         <v>238</v>
       </c>
@@ -54180,7 +54106,7 @@
         <v>184127.32</v>
       </c>
     </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A13" s="2" t="s">
         <v>28</v>
       </c>
@@ -54221,7 +54147,7 @@
         <v>672700.36</v>
       </c>
     </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A14" s="2" t="s">
         <v>32</v>
       </c>
@@ -54262,7 +54188,7 @@
         <v>672700.36</v>
       </c>
     </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A15" s="2" t="s">
         <v>259</v>
       </c>
@@ -54291,7 +54217,7 @@
       <c r="L15" s="6"/>
       <c r="M15" s="6"/>
     </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A16" s="2" t="s">
         <v>290</v>
       </c>

--- a/Reporte_gastos/gastos desde 2025-05.xlsx
+++ b/Reporte_gastos/gastos desde 2025-05.xlsx
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3888" uniqueCount="600">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4044" uniqueCount="627">
   <si>
     <t>ITEM</t>
   </si>
@@ -1833,6 +1833,87 @@
   </si>
   <si>
     <t>FA 4264-06570964</t>
+  </si>
+  <si>
+    <t>FA 0501-04153384 17</t>
+  </si>
+  <si>
+    <t>FA 0501-04151853 17</t>
+  </si>
+  <si>
+    <t>FA 9904-02696683 17</t>
+  </si>
+  <si>
+    <t>FA 4264-06648409</t>
+  </si>
+  <si>
+    <t>FA 0501-04170985 17</t>
+  </si>
+  <si>
+    <t>FA 0501-04170984 17</t>
+  </si>
+  <si>
+    <t>FA4264-06626415</t>
+  </si>
+  <si>
+    <t>FA 4264-06613632</t>
+  </si>
+  <si>
+    <t>FA 0501-04153383 17</t>
+  </si>
+  <si>
+    <t>FA 4264-06662548</t>
+  </si>
+  <si>
+    <t>FA 0501-04172617</t>
+  </si>
+  <si>
+    <t>COM LUCERO GUEMES GONDOLA 7 (LC 2)</t>
+  </si>
+  <si>
+    <t>FA 00003-00021003</t>
+  </si>
+  <si>
+    <t>FA 00003-00009355</t>
+  </si>
+  <si>
+    <t>FA 03950-07350318</t>
+  </si>
+  <si>
+    <t>ND 00002-00000090</t>
+  </si>
+  <si>
+    <t>FA 00002-00000265</t>
+  </si>
+  <si>
+    <t>FA 00003-00020948</t>
+  </si>
+  <si>
+    <t>FA 00003-00020949</t>
+  </si>
+  <si>
+    <t>FA 03950-07449267</t>
+  </si>
+  <si>
+    <t>FA 0030-00095439</t>
+  </si>
+  <si>
+    <t>FA 0030-00095357</t>
+  </si>
+  <si>
+    <t>FA 0030-00095558</t>
+  </si>
+  <si>
+    <t>FA 03950-07531510</t>
+  </si>
+  <si>
+    <t>FA 00003-00009353</t>
+  </si>
+  <si>
+    <t>FA 00003-00009352</t>
+  </si>
+  <si>
+    <t>FA 00003-00009354</t>
   </si>
 </sst>
 </file>
@@ -1948,7 +2029,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="57">
+  <cellXfs count="59">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -2072,6 +2153,10 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="14" fontId="2" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="8" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="169" fontId="2" fillId="6" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
   </cellXfs>
@@ -23368,7 +23453,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:AQ973"/>
+  <dimension ref="A1:AQ1014"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="12.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="35.5546875" style="29" customWidth="1"/>
@@ -23433,7 +23518,7 @@
       <c r="E1" s="56" t="s">
         <v>246</v>
       </c>
-      <c r="F1" s="56" t="s">
+      <c r="F1" s="58" t="s">
         <v>2</v>
       </c>
       <c r="G1" s="35" t="s">
@@ -50479,6 +50564,1088 @@
       <c r="H973" s="37">
         <v>2026</v>
       </c>
+    </row>
+    <row r="976" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A976" s="29" t="s">
+        <v>60</v>
+      </c>
+      <c r="B976" s="29" t="s">
+        <v>16</v>
+      </c>
+      <c r="C976" s="29" t="s">
+        <v>16</v>
+      </c>
+      <c r="D976" s="29" t="s">
+        <v>600</v>
+      </c>
+      <c r="E976" s="38">
+        <v>46209</v>
+      </c>
+      <c r="F976" s="43">
+        <v>35184.92</v>
+      </c>
+      <c r="G976" s="36">
+        <v>7</v>
+      </c>
+      <c r="H976" s="36">
+        <v>2026</v>
+      </c>
+      <c r="I976" s="30"/>
+      <c r="K976" s="7"/>
+    </row>
+    <row r="977" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A977" s="29" t="s">
+        <v>60</v>
+      </c>
+      <c r="B977" s="29" t="s">
+        <v>16</v>
+      </c>
+      <c r="C977" s="29" t="s">
+        <v>16</v>
+      </c>
+      <c r="D977" s="29" t="s">
+        <v>601</v>
+      </c>
+      <c r="E977" s="38">
+        <v>46209</v>
+      </c>
+      <c r="F977" s="43">
+        <v>239857.69</v>
+      </c>
+      <c r="G977" s="36">
+        <v>7</v>
+      </c>
+      <c r="H977" s="36">
+        <v>2026</v>
+      </c>
+      <c r="I977" s="30"/>
+      <c r="K977" s="7"/>
+    </row>
+    <row r="978" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A978" s="29" t="s">
+        <v>60</v>
+      </c>
+      <c r="B978" s="29" t="s">
+        <v>16</v>
+      </c>
+      <c r="C978" s="29" t="s">
+        <v>16</v>
+      </c>
+      <c r="D978" s="29" t="s">
+        <v>602</v>
+      </c>
+      <c r="E978" s="38">
+        <v>46210</v>
+      </c>
+      <c r="F978" s="43">
+        <v>654167.75</v>
+      </c>
+      <c r="G978" s="36">
+        <v>7</v>
+      </c>
+      <c r="H978" s="36">
+        <v>2026</v>
+      </c>
+      <c r="I978" s="30"/>
+      <c r="K978" s="7"/>
+    </row>
+    <row r="979" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A979" s="29" t="s">
+        <v>60</v>
+      </c>
+      <c r="B979" s="29" t="s">
+        <v>25</v>
+      </c>
+      <c r="C979" s="29" t="s">
+        <v>26</v>
+      </c>
+      <c r="D979" s="29" t="s">
+        <v>603</v>
+      </c>
+      <c r="E979" s="38">
+        <v>46190</v>
+      </c>
+      <c r="F979" s="43">
+        <v>54187.5</v>
+      </c>
+      <c r="G979" s="36">
+        <v>7</v>
+      </c>
+      <c r="H979" s="36">
+        <v>2026</v>
+      </c>
+      <c r="I979" s="30"/>
+      <c r="K979" s="7"/>
+    </row>
+    <row r="980" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A980" s="29" t="s">
+        <v>15</v>
+      </c>
+      <c r="B980" s="29" t="s">
+        <v>16</v>
+      </c>
+      <c r="C980" s="29" t="s">
+        <v>16</v>
+      </c>
+      <c r="D980" s="29" t="s">
+        <v>604</v>
+      </c>
+      <c r="E980" s="38">
+        <v>46211</v>
+      </c>
+      <c r="F980" s="43">
+        <v>169022.28</v>
+      </c>
+      <c r="G980" s="36">
+        <v>7</v>
+      </c>
+      <c r="H980" s="36">
+        <v>2026</v>
+      </c>
+      <c r="I980" s="30"/>
+      <c r="K980" s="7"/>
+    </row>
+    <row r="981" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A981" s="29" t="s">
+        <v>15</v>
+      </c>
+      <c r="B981" s="29" t="s">
+        <v>16</v>
+      </c>
+      <c r="C981" s="29" t="s">
+        <v>16</v>
+      </c>
+      <c r="D981" s="29" t="s">
+        <v>605</v>
+      </c>
+      <c r="E981" s="38">
+        <v>46211</v>
+      </c>
+      <c r="F981" s="43">
+        <v>54884.78</v>
+      </c>
+      <c r="G981" s="36">
+        <v>7</v>
+      </c>
+      <c r="H981" s="36">
+        <v>2026</v>
+      </c>
+      <c r="I981" s="30"/>
+      <c r="K981" s="7"/>
+    </row>
+    <row r="982" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A982" s="29" t="s">
+        <v>15</v>
+      </c>
+      <c r="B982" s="29" t="s">
+        <v>25</v>
+      </c>
+      <c r="C982" s="29" t="s">
+        <v>26</v>
+      </c>
+      <c r="D982" s="29" t="s">
+        <v>606</v>
+      </c>
+      <c r="E982" s="38">
+        <v>46190</v>
+      </c>
+      <c r="G982" s="36">
+        <v>7</v>
+      </c>
+      <c r="H982" s="36">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="983" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A983" s="29" t="s">
+        <v>67</v>
+      </c>
+      <c r="B983" s="29" t="s">
+        <v>25</v>
+      </c>
+      <c r="C983" s="29" t="s">
+        <v>26</v>
+      </c>
+      <c r="D983" s="29" t="s">
+        <v>607</v>
+      </c>
+      <c r="E983" s="38">
+        <v>46190</v>
+      </c>
+      <c r="F983" s="43">
+        <v>18980</v>
+      </c>
+      <c r="G983" s="36">
+        <v>7</v>
+      </c>
+      <c r="H983" s="36">
+        <v>2026</v>
+      </c>
+      <c r="I983" s="30"/>
+      <c r="K983" s="7"/>
+    </row>
+    <row r="984" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A984" s="29" t="s">
+        <v>24</v>
+      </c>
+      <c r="B984" s="29" t="s">
+        <v>16</v>
+      </c>
+      <c r="C984" s="29" t="s">
+        <v>16</v>
+      </c>
+      <c r="D984" s="29" t="s">
+        <v>608</v>
+      </c>
+      <c r="E984" s="38">
+        <v>46209</v>
+      </c>
+      <c r="F984" s="43">
+        <v>146046.85</v>
+      </c>
+      <c r="G984" s="36">
+        <v>7</v>
+      </c>
+      <c r="H984" s="36">
+        <v>2026</v>
+      </c>
+      <c r="I984" s="30"/>
+      <c r="K984" s="7"/>
+    </row>
+    <row r="985" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A985" s="29" t="s">
+        <v>24</v>
+      </c>
+      <c r="B985" s="29" t="s">
+        <v>25</v>
+      </c>
+      <c r="C985" s="29" t="s">
+        <v>26</v>
+      </c>
+      <c r="D985" s="29" t="s">
+        <v>609</v>
+      </c>
+      <c r="E985" s="38">
+        <v>46190</v>
+      </c>
+      <c r="F985" s="43">
+        <v>21932.560000000001</v>
+      </c>
+      <c r="G985" s="36">
+        <v>7</v>
+      </c>
+      <c r="H985" s="36">
+        <v>2026</v>
+      </c>
+      <c r="I985" s="30"/>
+      <c r="K985" s="7"/>
+    </row>
+    <row r="986" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A986" s="29" t="s">
+        <v>28</v>
+      </c>
+      <c r="B986" s="29" t="s">
+        <v>16</v>
+      </c>
+      <c r="C986" s="29" t="s">
+        <v>16</v>
+      </c>
+      <c r="D986" s="29" t="s">
+        <v>610</v>
+      </c>
+      <c r="E986" s="38">
+        <v>46211</v>
+      </c>
+      <c r="F986" s="43">
+        <v>94666.45</v>
+      </c>
+      <c r="G986" s="36">
+        <v>7</v>
+      </c>
+      <c r="H986" s="36">
+        <v>2026</v>
+      </c>
+      <c r="I986" s="30"/>
+      <c r="K986" s="7"/>
+    </row>
+    <row r="987" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A987" s="29" t="s">
+        <v>611</v>
+      </c>
+      <c r="B987" s="29" t="s">
+        <v>12</v>
+      </c>
+      <c r="C987" s="29" t="s">
+        <v>40</v>
+      </c>
+      <c r="D987" s="29" t="s">
+        <v>612</v>
+      </c>
+      <c r="E987" s="38">
+        <v>46216</v>
+      </c>
+      <c r="F987" s="43">
+        <v>63106.18</v>
+      </c>
+      <c r="G987" s="36">
+        <v>7</v>
+      </c>
+      <c r="H987" s="36">
+        <v>2026</v>
+      </c>
+      <c r="I987" s="30"/>
+      <c r="J987" s="57"/>
+      <c r="M987" s="7"/>
+    </row>
+    <row r="988" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A988" s="29" t="s">
+        <v>52</v>
+      </c>
+      <c r="B988" s="29" t="s">
+        <v>12</v>
+      </c>
+      <c r="C988" s="29" t="s">
+        <v>48</v>
+      </c>
+      <c r="D988" s="29" t="s">
+        <v>613</v>
+      </c>
+      <c r="E988" s="38">
+        <v>46216</v>
+      </c>
+      <c r="F988" s="43">
+        <v>1047092</v>
+      </c>
+      <c r="G988" s="36">
+        <v>7</v>
+      </c>
+      <c r="H988" s="36">
+        <v>2026</v>
+      </c>
+      <c r="I988" s="30"/>
+      <c r="M988" s="7"/>
+    </row>
+    <row r="989" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A989" s="29" t="s">
+        <v>52</v>
+      </c>
+      <c r="B989" s="29" t="s">
+        <v>20</v>
+      </c>
+      <c r="C989" s="29" t="s">
+        <v>48</v>
+      </c>
+      <c r="D989" s="29" t="s">
+        <v>56</v>
+      </c>
+      <c r="E989" s="38">
+        <v>46204</v>
+      </c>
+      <c r="F989" s="42">
+        <v>1529082.56</v>
+      </c>
+      <c r="G989" s="36">
+        <v>7</v>
+      </c>
+      <c r="H989" s="36">
+        <v>2026</v>
+      </c>
+      <c r="I989" s="30"/>
+      <c r="J989" s="57"/>
+      <c r="M989" s="7"/>
+    </row>
+    <row r="990" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A990" s="29" t="s">
+        <v>52</v>
+      </c>
+      <c r="B990" s="29" t="s">
+        <v>25</v>
+      </c>
+      <c r="C990" s="29" t="s">
+        <v>26</v>
+      </c>
+      <c r="D990" s="29" t="s">
+        <v>614</v>
+      </c>
+      <c r="E990" s="38">
+        <v>46180</v>
+      </c>
+      <c r="F990" s="42">
+        <v>45953.4</v>
+      </c>
+      <c r="G990" s="36">
+        <v>7</v>
+      </c>
+      <c r="H990" s="36">
+        <v>2026</v>
+      </c>
+      <c r="M990" s="7"/>
+    </row>
+    <row r="991" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A991" s="29" t="s">
+        <v>60</v>
+      </c>
+      <c r="B991" s="29" t="s">
+        <v>3</v>
+      </c>
+      <c r="C991" s="29" t="s">
+        <v>4</v>
+      </c>
+      <c r="D991" s="29" t="s">
+        <v>615</v>
+      </c>
+      <c r="E991" s="38">
+        <v>46216</v>
+      </c>
+      <c r="F991" s="42">
+        <v>705333.96</v>
+      </c>
+      <c r="G991" s="36">
+        <v>7</v>
+      </c>
+      <c r="H991" s="36">
+        <v>2026</v>
+      </c>
+      <c r="I991" s="30"/>
+      <c r="M991" s="7"/>
+    </row>
+    <row r="992" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A992" s="29" t="s">
+        <v>60</v>
+      </c>
+      <c r="B992" s="29" t="s">
+        <v>12</v>
+      </c>
+      <c r="C992" s="29" t="s">
+        <v>4</v>
+      </c>
+      <c r="D992" s="29" t="s">
+        <v>616</v>
+      </c>
+      <c r="E992" s="38">
+        <v>46216</v>
+      </c>
+      <c r="F992" s="43">
+        <v>7500000</v>
+      </c>
+      <c r="G992" s="36">
+        <v>7</v>
+      </c>
+      <c r="H992" s="36">
+        <v>2026</v>
+      </c>
+      <c r="I992" s="30"/>
+      <c r="J992" s="57"/>
+      <c r="M992" s="7"/>
+    </row>
+    <row r="993" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A993" s="29" t="s">
+        <v>60</v>
+      </c>
+      <c r="B993" s="29" t="s">
+        <v>14</v>
+      </c>
+      <c r="C993" s="29" t="s">
+        <v>4</v>
+      </c>
+      <c r="D993" s="29" t="s">
+        <v>615</v>
+      </c>
+      <c r="E993" s="38">
+        <v>46216</v>
+      </c>
+      <c r="F993" s="43">
+        <v>522241.21</v>
+      </c>
+      <c r="G993" s="36">
+        <v>7</v>
+      </c>
+      <c r="H993" s="36">
+        <v>2026</v>
+      </c>
+      <c r="I993" s="30"/>
+      <c r="M993" s="7"/>
+    </row>
+    <row r="994" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A994" s="29" t="s">
+        <v>60</v>
+      </c>
+      <c r="B994" s="29" t="s">
+        <v>20</v>
+      </c>
+      <c r="C994" s="29" t="s">
+        <v>4</v>
+      </c>
+      <c r="D994" s="29" t="s">
+        <v>615</v>
+      </c>
+      <c r="E994" s="38">
+        <v>46216</v>
+      </c>
+      <c r="F994" s="42">
+        <v>482850.5</v>
+      </c>
+      <c r="G994" s="36">
+        <v>7</v>
+      </c>
+      <c r="H994" s="36">
+        <v>2026</v>
+      </c>
+      <c r="I994" s="30"/>
+      <c r="J994" s="57"/>
+      <c r="M994" s="7"/>
+    </row>
+    <row r="995" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A995" s="29" t="s">
+        <v>15</v>
+      </c>
+      <c r="B995" s="29" t="s">
+        <v>12</v>
+      </c>
+      <c r="C995" s="29" t="s">
+        <v>321</v>
+      </c>
+      <c r="D995" s="29" t="s">
+        <v>575</v>
+      </c>
+      <c r="F995" s="43">
+        <v>1002486.6</v>
+      </c>
+      <c r="G995" s="36">
+        <v>7</v>
+      </c>
+      <c r="H995" s="36">
+        <v>2026</v>
+      </c>
+      <c r="I995" s="30"/>
+      <c r="J995" s="57"/>
+      <c r="M995" s="7"/>
+    </row>
+    <row r="996" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A996" s="29" t="s">
+        <v>15</v>
+      </c>
+      <c r="B996" s="29" t="s">
+        <v>20</v>
+      </c>
+      <c r="C996" s="29" t="s">
+        <v>37</v>
+      </c>
+      <c r="D996" s="29" t="s">
+        <v>56</v>
+      </c>
+      <c r="F996" s="42">
+        <v>332322.90000000002</v>
+      </c>
+      <c r="G996" s="36">
+        <v>7</v>
+      </c>
+      <c r="H996" s="36">
+        <v>2026</v>
+      </c>
+      <c r="M996" s="7"/>
+    </row>
+    <row r="997" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A997" s="29" t="s">
+        <v>67</v>
+      </c>
+      <c r="B997" s="29" t="s">
+        <v>12</v>
+      </c>
+      <c r="C997" s="29" t="s">
+        <v>40</v>
+      </c>
+      <c r="D997" s="29" t="s">
+        <v>617</v>
+      </c>
+      <c r="E997" s="38">
+        <v>46204</v>
+      </c>
+      <c r="F997" s="43">
+        <v>798015.19</v>
+      </c>
+      <c r="G997" s="36">
+        <v>7</v>
+      </c>
+      <c r="H997" s="36">
+        <v>2026</v>
+      </c>
+      <c r="I997" s="30"/>
+      <c r="M997" s="7"/>
+    </row>
+    <row r="998" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A998" s="29" t="s">
+        <v>67</v>
+      </c>
+      <c r="B998" s="29" t="s">
+        <v>20</v>
+      </c>
+      <c r="C998" s="29" t="s">
+        <v>40</v>
+      </c>
+      <c r="D998" s="29" t="s">
+        <v>617</v>
+      </c>
+      <c r="E998" s="38">
+        <v>46204</v>
+      </c>
+      <c r="F998" s="42">
+        <v>432974.31</v>
+      </c>
+      <c r="G998" s="36">
+        <v>7</v>
+      </c>
+      <c r="H998" s="36">
+        <v>2026</v>
+      </c>
+      <c r="J998" s="57"/>
+      <c r="M998" s="7"/>
+    </row>
+    <row r="999" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A999" s="29" t="s">
+        <v>611</v>
+      </c>
+      <c r="B999" s="29" t="s">
+        <v>12</v>
+      </c>
+      <c r="C999" s="29" t="s">
+        <v>40</v>
+      </c>
+      <c r="D999" s="29" t="s">
+        <v>618</v>
+      </c>
+      <c r="E999" s="38">
+        <v>46204</v>
+      </c>
+      <c r="F999" s="43">
+        <v>570010.85</v>
+      </c>
+      <c r="G999" s="36">
+        <v>7</v>
+      </c>
+      <c r="H999" s="36">
+        <v>2026</v>
+      </c>
+      <c r="I999" s="30"/>
+      <c r="M999" s="7"/>
+    </row>
+    <row r="1000" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A1000" s="29" t="s">
+        <v>611</v>
+      </c>
+      <c r="B1000" s="29" t="s">
+        <v>16</v>
+      </c>
+      <c r="C1000" s="29" t="s">
+        <v>40</v>
+      </c>
+      <c r="D1000" s="29" t="s">
+        <v>618</v>
+      </c>
+      <c r="E1000" s="38">
+        <v>46204</v>
+      </c>
+      <c r="F1000" s="43">
+        <v>82244.25</v>
+      </c>
+      <c r="G1000" s="36">
+        <v>7</v>
+      </c>
+      <c r="H1000" s="36">
+        <v>2026</v>
+      </c>
+      <c r="I1000" s="30"/>
+      <c r="M1000" s="7"/>
+    </row>
+    <row r="1001" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A1001" s="29" t="s">
+        <v>611</v>
+      </c>
+      <c r="B1001" s="29" t="s">
+        <v>20</v>
+      </c>
+      <c r="C1001" s="29" t="s">
+        <v>40</v>
+      </c>
+      <c r="D1001" s="29" t="s">
+        <v>618</v>
+      </c>
+      <c r="E1001" s="38">
+        <v>46204</v>
+      </c>
+      <c r="F1001" s="42">
+        <v>66242.19</v>
+      </c>
+      <c r="G1001" s="36">
+        <v>7</v>
+      </c>
+      <c r="H1001" s="36">
+        <v>2026</v>
+      </c>
+      <c r="J1001" s="57"/>
+      <c r="M1001" s="7"/>
+    </row>
+    <row r="1002" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A1002" s="29" t="s">
+        <v>292</v>
+      </c>
+      <c r="B1002" s="29" t="s">
+        <v>25</v>
+      </c>
+      <c r="C1002" s="29" t="s">
+        <v>26</v>
+      </c>
+      <c r="D1002" s="29" t="s">
+        <v>619</v>
+      </c>
+      <c r="F1002" s="42">
+        <v>37610.86</v>
+      </c>
+      <c r="G1002" s="36">
+        <v>7</v>
+      </c>
+      <c r="H1002" s="36">
+        <v>2026</v>
+      </c>
+      <c r="M1002" s="7"/>
+    </row>
+    <row r="1003" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A1003" s="29" t="s">
+        <v>24</v>
+      </c>
+      <c r="B1003" s="29" t="s">
+        <v>12</v>
+      </c>
+      <c r="C1003" s="29" t="s">
+        <v>43</v>
+      </c>
+      <c r="D1003" s="29" t="s">
+        <v>620</v>
+      </c>
+      <c r="E1003" s="38">
+        <v>46209</v>
+      </c>
+      <c r="F1003" s="43">
+        <v>2712733.69</v>
+      </c>
+      <c r="G1003" s="36">
+        <v>7</v>
+      </c>
+      <c r="H1003" s="36">
+        <v>2026</v>
+      </c>
+      <c r="I1003" s="30"/>
+      <c r="J1003" s="57"/>
+      <c r="M1003" s="7"/>
+    </row>
+    <row r="1004" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A1004" s="29" t="s">
+        <v>24</v>
+      </c>
+      <c r="B1004" s="29" t="s">
+        <v>20</v>
+      </c>
+      <c r="C1004" s="29" t="s">
+        <v>43</v>
+      </c>
+      <c r="D1004" s="29" t="s">
+        <v>621</v>
+      </c>
+      <c r="E1004" s="38">
+        <v>46209</v>
+      </c>
+      <c r="F1004" s="43">
+        <v>2418017.23</v>
+      </c>
+      <c r="G1004" s="36">
+        <v>7</v>
+      </c>
+      <c r="H1004" s="36">
+        <v>2026</v>
+      </c>
+      <c r="I1004" s="30"/>
+      <c r="J1004" s="57"/>
+      <c r="M1004" s="7"/>
+    </row>
+    <row r="1005" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A1005" s="29" t="s">
+        <v>238</v>
+      </c>
+      <c r="B1005" s="29" t="s">
+        <v>12</v>
+      </c>
+      <c r="C1005" s="29" t="s">
+        <v>43</v>
+      </c>
+      <c r="D1005" s="29" t="s">
+        <v>622</v>
+      </c>
+      <c r="E1005" s="38">
+        <v>46211</v>
+      </c>
+      <c r="F1005" s="43">
+        <v>1736485.35</v>
+      </c>
+      <c r="G1005" s="36">
+        <v>7</v>
+      </c>
+      <c r="H1005" s="36">
+        <v>2026</v>
+      </c>
+      <c r="I1005" s="30"/>
+      <c r="M1005" s="7"/>
+    </row>
+    <row r="1006" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A1006" s="29" t="s">
+        <v>238</v>
+      </c>
+      <c r="B1006" s="29" t="s">
+        <v>12</v>
+      </c>
+      <c r="C1006" s="29" t="s">
+        <v>43</v>
+      </c>
+      <c r="D1006" s="29" t="s">
+        <v>622</v>
+      </c>
+      <c r="E1006" s="38">
+        <v>46211</v>
+      </c>
+      <c r="F1006" s="43">
+        <v>173648.54</v>
+      </c>
+      <c r="G1006" s="36">
+        <v>7</v>
+      </c>
+      <c r="H1006" s="36">
+        <v>2026</v>
+      </c>
+      <c r="I1006" s="30"/>
+      <c r="M1006" s="7"/>
+    </row>
+    <row r="1007" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A1007" s="29" t="s">
+        <v>238</v>
+      </c>
+      <c r="B1007" s="29" t="s">
+        <v>20</v>
+      </c>
+      <c r="C1007" s="29" t="s">
+        <v>43</v>
+      </c>
+      <c r="D1007" s="29" t="s">
+        <v>622</v>
+      </c>
+      <c r="E1007" s="38">
+        <v>46211</v>
+      </c>
+      <c r="F1007" s="43">
+        <v>192942.82</v>
+      </c>
+      <c r="G1007" s="36">
+        <v>7</v>
+      </c>
+      <c r="H1007" s="36">
+        <v>2026</v>
+      </c>
+      <c r="I1007" s="30"/>
+      <c r="J1007" s="57"/>
+      <c r="M1007" s="7"/>
+    </row>
+    <row r="1008" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A1008" s="29" t="s">
+        <v>238</v>
+      </c>
+      <c r="B1008" s="29" t="s">
+        <v>25</v>
+      </c>
+      <c r="C1008" s="29" t="s">
+        <v>26</v>
+      </c>
+      <c r="D1008" s="29" t="s">
+        <v>623</v>
+      </c>
+      <c r="F1008" s="42">
+        <v>31992.91</v>
+      </c>
+      <c r="G1008" s="36">
+        <v>7</v>
+      </c>
+      <c r="H1008" s="36">
+        <v>2026</v>
+      </c>
+      <c r="M1008" s="7"/>
+    </row>
+    <row r="1009" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A1009" s="29" t="s">
+        <v>28</v>
+      </c>
+      <c r="B1009" s="29" t="s">
+        <v>12</v>
+      </c>
+      <c r="C1009" s="29" t="s">
+        <v>48</v>
+      </c>
+      <c r="D1009" s="29" t="s">
+        <v>624</v>
+      </c>
+      <c r="E1009" s="38">
+        <v>46216</v>
+      </c>
+      <c r="F1009" s="43">
+        <v>1162515</v>
+      </c>
+      <c r="G1009" s="36">
+        <v>7</v>
+      </c>
+      <c r="H1009" s="36">
+        <v>2026</v>
+      </c>
+      <c r="I1009" s="30"/>
+      <c r="M1009" s="7"/>
+    </row>
+    <row r="1010" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A1010" s="29" t="s">
+        <v>28</v>
+      </c>
+      <c r="B1010" s="29" t="s">
+        <v>20</v>
+      </c>
+      <c r="C1010" s="29" t="s">
+        <v>48</v>
+      </c>
+      <c r="D1010" s="29" t="s">
+        <v>56</v>
+      </c>
+      <c r="E1010" s="38">
+        <v>46204</v>
+      </c>
+      <c r="F1010" s="42">
+        <v>764541.28</v>
+      </c>
+      <c r="G1010" s="36">
+        <v>7</v>
+      </c>
+      <c r="H1010" s="36">
+        <v>2026</v>
+      </c>
+      <c r="I1010" s="30"/>
+      <c r="J1010" s="57"/>
+      <c r="M1010" s="7"/>
+    </row>
+    <row r="1011" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A1011" s="29" t="s">
+        <v>32</v>
+      </c>
+      <c r="B1011" s="29" t="s">
+        <v>12</v>
+      </c>
+      <c r="C1011" s="29" t="s">
+        <v>48</v>
+      </c>
+      <c r="D1011" s="29" t="s">
+        <v>625</v>
+      </c>
+      <c r="E1011" s="38">
+        <v>46216</v>
+      </c>
+      <c r="F1011" s="43">
+        <v>1175096</v>
+      </c>
+      <c r="G1011" s="36">
+        <v>7</v>
+      </c>
+      <c r="H1011" s="36">
+        <v>2026</v>
+      </c>
+      <c r="I1011" s="30"/>
+      <c r="M1011" s="7"/>
+    </row>
+    <row r="1012" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A1012" s="29" t="s">
+        <v>32</v>
+      </c>
+      <c r="B1012" s="29" t="s">
+        <v>16</v>
+      </c>
+      <c r="C1012" s="29" t="s">
+        <v>130</v>
+      </c>
+      <c r="D1012" s="29" t="s">
+        <v>56</v>
+      </c>
+      <c r="E1012" s="38">
+        <v>46211</v>
+      </c>
+      <c r="F1012" s="42">
+        <v>183054.02</v>
+      </c>
+      <c r="G1012" s="36">
+        <v>7</v>
+      </c>
+      <c r="H1012" s="36">
+        <v>2026</v>
+      </c>
+      <c r="I1012" s="30"/>
+      <c r="M1012" s="7"/>
+    </row>
+    <row r="1013" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A1013" s="29" t="s">
+        <v>32</v>
+      </c>
+      <c r="B1013" s="29" t="s">
+        <v>20</v>
+      </c>
+      <c r="C1013" s="29" t="s">
+        <v>48</v>
+      </c>
+      <c r="D1013" s="29" t="s">
+        <v>56</v>
+      </c>
+      <c r="E1013" s="38">
+        <v>46204</v>
+      </c>
+      <c r="F1013" s="42">
+        <v>764541.28</v>
+      </c>
+      <c r="G1013" s="36">
+        <v>7</v>
+      </c>
+      <c r="H1013" s="36">
+        <v>2026</v>
+      </c>
+      <c r="I1013" s="30"/>
+      <c r="J1013" s="57"/>
+      <c r="M1013" s="7"/>
+    </row>
+    <row r="1014" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A1014" s="29" t="s">
+        <v>28</v>
+      </c>
+      <c r="B1014" s="29" t="s">
+        <v>12</v>
+      </c>
+      <c r="C1014" s="29" t="s">
+        <v>48</v>
+      </c>
+      <c r="D1014" s="29" t="s">
+        <v>626</v>
+      </c>
+      <c r="E1014" s="38">
+        <v>46216</v>
+      </c>
+      <c r="F1014" s="43">
+        <v>478188.84</v>
+      </c>
+      <c r="G1014" s="36">
+        <v>7</v>
+      </c>
+      <c r="H1014" s="36">
+        <v>2026</v>
+      </c>
+      <c r="I1014" s="30"/>
+      <c r="J1014" s="57"/>
+      <c r="M1014" s="7"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:I973"/>
